--- a/ava-break-even-check.xlsx
+++ b/ava-break-even-check.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -597,7 +597,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IVR cost per call</t>
+          <t>IVR cost per call (only calls that never reach AVA)</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -607,11 +607,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AVA cost per call</t>
+          <t>AVA cost per call (replaces the IVR fee)</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="16">
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="C37" s="16">
-        <f>(1-$B$11)*$B$5*$B$14</f>
+        <f>$B$12*$B$5*$B$14</f>
         <v/>
       </c>
       <c r="D37" s="16">
@@ -1078,80 +1078,96 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AVA cost (per-call + fixed)</t>
+          <t>IVR fees avoided</t>
         </is>
       </c>
       <c r="B50" s="16">
-        <f>C38+C39</f>
-        <v/>
-      </c>
-      <c r="E50" s="11" t="inlineStr"/>
+        <f>B37-C37</f>
+        <v/>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>calls reaching AVA × IVR cost per call (they pay the AVA fee instead)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>AVA cost (per-call + fixed)</t>
+        </is>
+      </c>
+      <c r="B51" s="16">
+        <f>C38+C39</f>
+        <v/>
+      </c>
+      <c r="E51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Net monthly savings</t>
         </is>
       </c>
-      <c r="B51" s="16">
-        <f>B49-B50</f>
-        <v/>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="B52" s="16">
+        <f>B49+B50-B51</f>
+        <v/>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>labor saved − AVA cost; must equal monthly savings above</t>
+          <t>labor saved + IVR fees avoided − AVA cost; must equal monthly savings above</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Break-even AVA containment (% of all calls)</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>First 0.1% step at or above break-even (works with or without rounding)</t>
         </is>
       </c>
-      <c r="B54" s="15">
+      <c r="B55" s="15">
         <f>_xlfn.MINIFS(Ladder!A:A,Ladder!H:H,"&gt;=0")</f>
         <v/>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E55" s="11" t="inlineStr">
         <is>
           <t>lowest containment in the Ladder sheet with savings ≥ 0</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Same, as % of calls reaching AVA</t>
         </is>
       </c>
-      <c r="B55" s="15">
-        <f>B54/B27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="B56" s="15">
+        <f>B55/B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Closed form, fractional agents (cross-check)</t>
         </is>
       </c>
-      <c r="B56" s="20">
-        <f>IF($B$16=1,(B27*$B$5*$B$15+B30)/($B$5*B26),B30/($B$5*(B26-$B$15)))</f>
-        <v/>
-      </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="B57" s="20">
+        <f>MAX(0,IF($B$16=1,(B27*$B$5*($B$15-$B$14)+B30)/($B$5*B26),(B30-B27*$B$5*$B$14)/($B$5*(B26-$B$15))))</f>
+        <v/>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
         <is>
           <t>charged: (AVA calls × AVA cost + fixed) ÷ (calls × agent cost per call); not charged: fixed ÷ (calls × (agent cost per call − AVA cost))</t>
         </is>
@@ -1261,7 +1277,7 @@
         <v/>
       </c>
       <c r="G2" s="16">
-        <f>IF(A2="","",E2*Calculator!$B$6+Calculator!$B$37+F2+Calculator!$B$30)</f>
+        <f>IF(A2="","",E2*Calculator!$B$6+Calculator!$C$37+F2+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H2" s="16">
@@ -1303,7 +1319,7 @@
         <v/>
       </c>
       <c r="G3" s="16">
-        <f>IF(A3="","",E3*Calculator!$B$6+Calculator!$B$37+F3+Calculator!$B$30)</f>
+        <f>IF(A3="","",E3*Calculator!$B$6+Calculator!$C$37+F3+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H3" s="16">
@@ -1345,7 +1361,7 @@
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>IF(A4="","",E4*Calculator!$B$6+Calculator!$B$37+F4+Calculator!$B$30)</f>
+        <f>IF(A4="","",E4*Calculator!$B$6+Calculator!$C$37+F4+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H4" s="16">
@@ -1387,7 +1403,7 @@
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>IF(A5="","",E5*Calculator!$B$6+Calculator!$B$37+F5+Calculator!$B$30)</f>
+        <f>IF(A5="","",E5*Calculator!$B$6+Calculator!$C$37+F5+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H5" s="16">
@@ -1429,7 +1445,7 @@
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>IF(A6="","",E6*Calculator!$B$6+Calculator!$B$37+F6+Calculator!$B$30)</f>
+        <f>IF(A6="","",E6*Calculator!$B$6+Calculator!$C$37+F6+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H6" s="16">
@@ -1471,7 +1487,7 @@
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>IF(A7="","",E7*Calculator!$B$6+Calculator!$B$37+F7+Calculator!$B$30)</f>
+        <f>IF(A7="","",E7*Calculator!$B$6+Calculator!$C$37+F7+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H7" s="16">
@@ -1513,7 +1529,7 @@
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>IF(A8="","",E8*Calculator!$B$6+Calculator!$B$37+F8+Calculator!$B$30)</f>
+        <f>IF(A8="","",E8*Calculator!$B$6+Calculator!$C$37+F8+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H8" s="16">
@@ -1555,7 +1571,7 @@
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>IF(A9="","",E9*Calculator!$B$6+Calculator!$B$37+F9+Calculator!$B$30)</f>
+        <f>IF(A9="","",E9*Calculator!$B$6+Calculator!$C$37+F9+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H9" s="16">
@@ -1597,7 +1613,7 @@
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>IF(A10="","",E10*Calculator!$B$6+Calculator!$B$37+F10+Calculator!$B$30)</f>
+        <f>IF(A10="","",E10*Calculator!$B$6+Calculator!$C$37+F10+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H10" s="16">
@@ -1639,7 +1655,7 @@
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>IF(A11="","",E11*Calculator!$B$6+Calculator!$B$37+F11+Calculator!$B$30)</f>
+        <f>IF(A11="","",E11*Calculator!$B$6+Calculator!$C$37+F11+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H11" s="16">
@@ -1681,7 +1697,7 @@
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>IF(A12="","",E12*Calculator!$B$6+Calculator!$B$37+F12+Calculator!$B$30)</f>
+        <f>IF(A12="","",E12*Calculator!$B$6+Calculator!$C$37+F12+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H12" s="16">
@@ -1723,7 +1739,7 @@
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>IF(A13="","",E13*Calculator!$B$6+Calculator!$B$37+F13+Calculator!$B$30)</f>
+        <f>IF(A13="","",E13*Calculator!$B$6+Calculator!$C$37+F13+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H13" s="16">
@@ -1765,7 +1781,7 @@
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IF(A14="","",E14*Calculator!$B$6+Calculator!$B$37+F14+Calculator!$B$30)</f>
+        <f>IF(A14="","",E14*Calculator!$B$6+Calculator!$C$37+F14+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H14" s="16">
@@ -1807,7 +1823,7 @@
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>IF(A15="","",E15*Calculator!$B$6+Calculator!$B$37+F15+Calculator!$B$30)</f>
+        <f>IF(A15="","",E15*Calculator!$B$6+Calculator!$C$37+F15+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H15" s="16">
@@ -1849,7 +1865,7 @@
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IF(A16="","",E16*Calculator!$B$6+Calculator!$B$37+F16+Calculator!$B$30)</f>
+        <f>IF(A16="","",E16*Calculator!$B$6+Calculator!$C$37+F16+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H16" s="16">
@@ -1891,7 +1907,7 @@
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>IF(A17="","",E17*Calculator!$B$6+Calculator!$B$37+F17+Calculator!$B$30)</f>
+        <f>IF(A17="","",E17*Calculator!$B$6+Calculator!$C$37+F17+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H17" s="16">
@@ -1933,7 +1949,7 @@
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>IF(A18="","",E18*Calculator!$B$6+Calculator!$B$37+F18+Calculator!$B$30)</f>
+        <f>IF(A18="","",E18*Calculator!$B$6+Calculator!$C$37+F18+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H18" s="16">
@@ -1975,7 +1991,7 @@
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>IF(A19="","",E19*Calculator!$B$6+Calculator!$B$37+F19+Calculator!$B$30)</f>
+        <f>IF(A19="","",E19*Calculator!$B$6+Calculator!$C$37+F19+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H19" s="16">
@@ -2017,7 +2033,7 @@
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>IF(A20="","",E20*Calculator!$B$6+Calculator!$B$37+F20+Calculator!$B$30)</f>
+        <f>IF(A20="","",E20*Calculator!$B$6+Calculator!$C$37+F20+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H20" s="16">
@@ -2059,7 +2075,7 @@
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>IF(A21="","",E21*Calculator!$B$6+Calculator!$B$37+F21+Calculator!$B$30)</f>
+        <f>IF(A21="","",E21*Calculator!$B$6+Calculator!$C$37+F21+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H21" s="16">
@@ -2101,7 +2117,7 @@
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>IF(A22="","",E22*Calculator!$B$6+Calculator!$B$37+F22+Calculator!$B$30)</f>
+        <f>IF(A22="","",E22*Calculator!$B$6+Calculator!$C$37+F22+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H22" s="16">
@@ -2143,7 +2159,7 @@
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>IF(A23="","",E23*Calculator!$B$6+Calculator!$B$37+F23+Calculator!$B$30)</f>
+        <f>IF(A23="","",E23*Calculator!$B$6+Calculator!$C$37+F23+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H23" s="16">
@@ -2185,7 +2201,7 @@
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>IF(A24="","",E24*Calculator!$B$6+Calculator!$B$37+F24+Calculator!$B$30)</f>
+        <f>IF(A24="","",E24*Calculator!$B$6+Calculator!$C$37+F24+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H24" s="16">
@@ -2227,7 +2243,7 @@
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>IF(A25="","",E25*Calculator!$B$6+Calculator!$B$37+F25+Calculator!$B$30)</f>
+        <f>IF(A25="","",E25*Calculator!$B$6+Calculator!$C$37+F25+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H25" s="16">
@@ -2269,7 +2285,7 @@
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>IF(A26="","",E26*Calculator!$B$6+Calculator!$B$37+F26+Calculator!$B$30)</f>
+        <f>IF(A26="","",E26*Calculator!$B$6+Calculator!$C$37+F26+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H26" s="16">
@@ -2311,7 +2327,7 @@
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>IF(A27="","",E27*Calculator!$B$6+Calculator!$B$37+F27+Calculator!$B$30)</f>
+        <f>IF(A27="","",E27*Calculator!$B$6+Calculator!$C$37+F27+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H27" s="16">
@@ -2353,7 +2369,7 @@
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>IF(A28="","",E28*Calculator!$B$6+Calculator!$B$37+F28+Calculator!$B$30)</f>
+        <f>IF(A28="","",E28*Calculator!$B$6+Calculator!$C$37+F28+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H28" s="16">
@@ -2395,7 +2411,7 @@
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>IF(A29="","",E29*Calculator!$B$6+Calculator!$B$37+F29+Calculator!$B$30)</f>
+        <f>IF(A29="","",E29*Calculator!$B$6+Calculator!$C$37+F29+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H29" s="16">
@@ -2437,7 +2453,7 @@
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>IF(A30="","",E30*Calculator!$B$6+Calculator!$B$37+F30+Calculator!$B$30)</f>
+        <f>IF(A30="","",E30*Calculator!$B$6+Calculator!$C$37+F30+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H30" s="16">
@@ -2479,7 +2495,7 @@
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>IF(A31="","",E31*Calculator!$B$6+Calculator!$B$37+F31+Calculator!$B$30)</f>
+        <f>IF(A31="","",E31*Calculator!$B$6+Calculator!$C$37+F31+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H31" s="16">
@@ -2521,7 +2537,7 @@
         <v/>
       </c>
       <c r="G32" s="16">
-        <f>IF(A32="","",E32*Calculator!$B$6+Calculator!$B$37+F32+Calculator!$B$30)</f>
+        <f>IF(A32="","",E32*Calculator!$B$6+Calculator!$C$37+F32+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H32" s="16">
@@ -2563,7 +2579,7 @@
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>IF(A33="","",E33*Calculator!$B$6+Calculator!$B$37+F33+Calculator!$B$30)</f>
+        <f>IF(A33="","",E33*Calculator!$B$6+Calculator!$C$37+F33+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H33" s="16">
@@ -2605,7 +2621,7 @@
         <v/>
       </c>
       <c r="G34" s="16">
-        <f>IF(A34="","",E34*Calculator!$B$6+Calculator!$B$37+F34+Calculator!$B$30)</f>
+        <f>IF(A34="","",E34*Calculator!$B$6+Calculator!$C$37+F34+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H34" s="16">
@@ -2647,7 +2663,7 @@
         <v/>
       </c>
       <c r="G35" s="16">
-        <f>IF(A35="","",E35*Calculator!$B$6+Calculator!$B$37+F35+Calculator!$B$30)</f>
+        <f>IF(A35="","",E35*Calculator!$B$6+Calculator!$C$37+F35+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H35" s="16">
@@ -2689,7 +2705,7 @@
         <v/>
       </c>
       <c r="G36" s="16">
-        <f>IF(A36="","",E36*Calculator!$B$6+Calculator!$B$37+F36+Calculator!$B$30)</f>
+        <f>IF(A36="","",E36*Calculator!$B$6+Calculator!$C$37+F36+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H36" s="16">
@@ -2731,7 +2747,7 @@
         <v/>
       </c>
       <c r="G37" s="16">
-        <f>IF(A37="","",E37*Calculator!$B$6+Calculator!$B$37+F37+Calculator!$B$30)</f>
+        <f>IF(A37="","",E37*Calculator!$B$6+Calculator!$C$37+F37+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H37" s="16">
@@ -2773,7 +2789,7 @@
         <v/>
       </c>
       <c r="G38" s="16">
-        <f>IF(A38="","",E38*Calculator!$B$6+Calculator!$B$37+F38+Calculator!$B$30)</f>
+        <f>IF(A38="","",E38*Calculator!$B$6+Calculator!$C$37+F38+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H38" s="16">
@@ -2815,7 +2831,7 @@
         <v/>
       </c>
       <c r="G39" s="16">
-        <f>IF(A39="","",E39*Calculator!$B$6+Calculator!$B$37+F39+Calculator!$B$30)</f>
+        <f>IF(A39="","",E39*Calculator!$B$6+Calculator!$C$37+F39+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H39" s="16">
@@ -2857,7 +2873,7 @@
         <v/>
       </c>
       <c r="G40" s="16">
-        <f>IF(A40="","",E40*Calculator!$B$6+Calculator!$B$37+F40+Calculator!$B$30)</f>
+        <f>IF(A40="","",E40*Calculator!$B$6+Calculator!$C$37+F40+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H40" s="16">
@@ -2899,7 +2915,7 @@
         <v/>
       </c>
       <c r="G41" s="16">
-        <f>IF(A41="","",E41*Calculator!$B$6+Calculator!$B$37+F41+Calculator!$B$30)</f>
+        <f>IF(A41="","",E41*Calculator!$B$6+Calculator!$C$37+F41+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H41" s="16">
@@ -2941,7 +2957,7 @@
         <v/>
       </c>
       <c r="G42" s="16">
-        <f>IF(A42="","",E42*Calculator!$B$6+Calculator!$B$37+F42+Calculator!$B$30)</f>
+        <f>IF(A42="","",E42*Calculator!$B$6+Calculator!$C$37+F42+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H42" s="16">
@@ -2983,7 +2999,7 @@
         <v/>
       </c>
       <c r="G43" s="16">
-        <f>IF(A43="","",E43*Calculator!$B$6+Calculator!$B$37+F43+Calculator!$B$30)</f>
+        <f>IF(A43="","",E43*Calculator!$B$6+Calculator!$C$37+F43+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H43" s="16">
@@ -3025,7 +3041,7 @@
         <v/>
       </c>
       <c r="G44" s="16">
-        <f>IF(A44="","",E44*Calculator!$B$6+Calculator!$B$37+F44+Calculator!$B$30)</f>
+        <f>IF(A44="","",E44*Calculator!$B$6+Calculator!$C$37+F44+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H44" s="16">
@@ -3067,7 +3083,7 @@
         <v/>
       </c>
       <c r="G45" s="16">
-        <f>IF(A45="","",E45*Calculator!$B$6+Calculator!$B$37+F45+Calculator!$B$30)</f>
+        <f>IF(A45="","",E45*Calculator!$B$6+Calculator!$C$37+F45+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H45" s="16">
@@ -3109,7 +3125,7 @@
         <v/>
       </c>
       <c r="G46" s="16">
-        <f>IF(A46="","",E46*Calculator!$B$6+Calculator!$B$37+F46+Calculator!$B$30)</f>
+        <f>IF(A46="","",E46*Calculator!$B$6+Calculator!$C$37+F46+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H46" s="16">
@@ -3151,7 +3167,7 @@
         <v/>
       </c>
       <c r="G47" s="16">
-        <f>IF(A47="","",E47*Calculator!$B$6+Calculator!$B$37+F47+Calculator!$B$30)</f>
+        <f>IF(A47="","",E47*Calculator!$B$6+Calculator!$C$37+F47+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H47" s="16">
@@ -3193,7 +3209,7 @@
         <v/>
       </c>
       <c r="G48" s="16">
-        <f>IF(A48="","",E48*Calculator!$B$6+Calculator!$B$37+F48+Calculator!$B$30)</f>
+        <f>IF(A48="","",E48*Calculator!$B$6+Calculator!$C$37+F48+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H48" s="16">
@@ -3235,7 +3251,7 @@
         <v/>
       </c>
       <c r="G49" s="16">
-        <f>IF(A49="","",E49*Calculator!$B$6+Calculator!$B$37+F49+Calculator!$B$30)</f>
+        <f>IF(A49="","",E49*Calculator!$B$6+Calculator!$C$37+F49+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H49" s="16">
@@ -3277,7 +3293,7 @@
         <v/>
       </c>
       <c r="G50" s="16">
-        <f>IF(A50="","",E50*Calculator!$B$6+Calculator!$B$37+F50+Calculator!$B$30)</f>
+        <f>IF(A50="","",E50*Calculator!$B$6+Calculator!$C$37+F50+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H50" s="16">
@@ -3319,7 +3335,7 @@
         <v/>
       </c>
       <c r="G51" s="16">
-        <f>IF(A51="","",E51*Calculator!$B$6+Calculator!$B$37+F51+Calculator!$B$30)</f>
+        <f>IF(A51="","",E51*Calculator!$B$6+Calculator!$C$37+F51+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H51" s="16">
@@ -3361,7 +3377,7 @@
         <v/>
       </c>
       <c r="G52" s="16">
-        <f>IF(A52="","",E52*Calculator!$B$6+Calculator!$B$37+F52+Calculator!$B$30)</f>
+        <f>IF(A52="","",E52*Calculator!$B$6+Calculator!$C$37+F52+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H52" s="16">
@@ -3403,7 +3419,7 @@
         <v/>
       </c>
       <c r="G53" s="16">
-        <f>IF(A53="","",E53*Calculator!$B$6+Calculator!$B$37+F53+Calculator!$B$30)</f>
+        <f>IF(A53="","",E53*Calculator!$B$6+Calculator!$C$37+F53+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H53" s="16">
@@ -3445,7 +3461,7 @@
         <v/>
       </c>
       <c r="G54" s="16">
-        <f>IF(A54="","",E54*Calculator!$B$6+Calculator!$B$37+F54+Calculator!$B$30)</f>
+        <f>IF(A54="","",E54*Calculator!$B$6+Calculator!$C$37+F54+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H54" s="16">
@@ -3487,7 +3503,7 @@
         <v/>
       </c>
       <c r="G55" s="16">
-        <f>IF(A55="","",E55*Calculator!$B$6+Calculator!$B$37+F55+Calculator!$B$30)</f>
+        <f>IF(A55="","",E55*Calculator!$B$6+Calculator!$C$37+F55+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H55" s="16">
@@ -3529,7 +3545,7 @@
         <v/>
       </c>
       <c r="G56" s="16">
-        <f>IF(A56="","",E56*Calculator!$B$6+Calculator!$B$37+F56+Calculator!$B$30)</f>
+        <f>IF(A56="","",E56*Calculator!$B$6+Calculator!$C$37+F56+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H56" s="16">
@@ -3571,7 +3587,7 @@
         <v/>
       </c>
       <c r="G57" s="16">
-        <f>IF(A57="","",E57*Calculator!$B$6+Calculator!$B$37+F57+Calculator!$B$30)</f>
+        <f>IF(A57="","",E57*Calculator!$B$6+Calculator!$C$37+F57+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H57" s="16">
@@ -3613,7 +3629,7 @@
         <v/>
       </c>
       <c r="G58" s="16">
-        <f>IF(A58="","",E58*Calculator!$B$6+Calculator!$B$37+F58+Calculator!$B$30)</f>
+        <f>IF(A58="","",E58*Calculator!$B$6+Calculator!$C$37+F58+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H58" s="16">
@@ -3655,7 +3671,7 @@
         <v/>
       </c>
       <c r="G59" s="16">
-        <f>IF(A59="","",E59*Calculator!$B$6+Calculator!$B$37+F59+Calculator!$B$30)</f>
+        <f>IF(A59="","",E59*Calculator!$B$6+Calculator!$C$37+F59+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H59" s="16">
@@ -3697,7 +3713,7 @@
         <v/>
       </c>
       <c r="G60" s="16">
-        <f>IF(A60="","",E60*Calculator!$B$6+Calculator!$B$37+F60+Calculator!$B$30)</f>
+        <f>IF(A60="","",E60*Calculator!$B$6+Calculator!$C$37+F60+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H60" s="16">
@@ -3739,7 +3755,7 @@
         <v/>
       </c>
       <c r="G61" s="16">
-        <f>IF(A61="","",E61*Calculator!$B$6+Calculator!$B$37+F61+Calculator!$B$30)</f>
+        <f>IF(A61="","",E61*Calculator!$B$6+Calculator!$C$37+F61+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H61" s="16">
@@ -3781,7 +3797,7 @@
         <v/>
       </c>
       <c r="G62" s="16">
-        <f>IF(A62="","",E62*Calculator!$B$6+Calculator!$B$37+F62+Calculator!$B$30)</f>
+        <f>IF(A62="","",E62*Calculator!$B$6+Calculator!$C$37+F62+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H62" s="16">
@@ -3823,7 +3839,7 @@
         <v/>
       </c>
       <c r="G63" s="16">
-        <f>IF(A63="","",E63*Calculator!$B$6+Calculator!$B$37+F63+Calculator!$B$30)</f>
+        <f>IF(A63="","",E63*Calculator!$B$6+Calculator!$C$37+F63+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H63" s="16">
@@ -3865,7 +3881,7 @@
         <v/>
       </c>
       <c r="G64" s="16">
-        <f>IF(A64="","",E64*Calculator!$B$6+Calculator!$B$37+F64+Calculator!$B$30)</f>
+        <f>IF(A64="","",E64*Calculator!$B$6+Calculator!$C$37+F64+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H64" s="16">
@@ -3907,7 +3923,7 @@
         <v/>
       </c>
       <c r="G65" s="16">
-        <f>IF(A65="","",E65*Calculator!$B$6+Calculator!$B$37+F65+Calculator!$B$30)</f>
+        <f>IF(A65="","",E65*Calculator!$B$6+Calculator!$C$37+F65+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H65" s="16">
@@ -3949,7 +3965,7 @@
         <v/>
       </c>
       <c r="G66" s="16">
-        <f>IF(A66="","",E66*Calculator!$B$6+Calculator!$B$37+F66+Calculator!$B$30)</f>
+        <f>IF(A66="","",E66*Calculator!$B$6+Calculator!$C$37+F66+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H66" s="16">
@@ -3991,7 +4007,7 @@
         <v/>
       </c>
       <c r="G67" s="16">
-        <f>IF(A67="","",E67*Calculator!$B$6+Calculator!$B$37+F67+Calculator!$B$30)</f>
+        <f>IF(A67="","",E67*Calculator!$B$6+Calculator!$C$37+F67+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H67" s="16">
@@ -4033,7 +4049,7 @@
         <v/>
       </c>
       <c r="G68" s="16">
-        <f>IF(A68="","",E68*Calculator!$B$6+Calculator!$B$37+F68+Calculator!$B$30)</f>
+        <f>IF(A68="","",E68*Calculator!$B$6+Calculator!$C$37+F68+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H68" s="16">
@@ -4075,7 +4091,7 @@
         <v/>
       </c>
       <c r="G69" s="16">
-        <f>IF(A69="","",E69*Calculator!$B$6+Calculator!$B$37+F69+Calculator!$B$30)</f>
+        <f>IF(A69="","",E69*Calculator!$B$6+Calculator!$C$37+F69+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H69" s="16">
@@ -4117,7 +4133,7 @@
         <v/>
       </c>
       <c r="G70" s="16">
-        <f>IF(A70="","",E70*Calculator!$B$6+Calculator!$B$37+F70+Calculator!$B$30)</f>
+        <f>IF(A70="","",E70*Calculator!$B$6+Calculator!$C$37+F70+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H70" s="16">
@@ -4159,7 +4175,7 @@
         <v/>
       </c>
       <c r="G71" s="16">
-        <f>IF(A71="","",E71*Calculator!$B$6+Calculator!$B$37+F71+Calculator!$B$30)</f>
+        <f>IF(A71="","",E71*Calculator!$B$6+Calculator!$C$37+F71+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H71" s="16">
@@ -4201,7 +4217,7 @@
         <v/>
       </c>
       <c r="G72" s="16">
-        <f>IF(A72="","",E72*Calculator!$B$6+Calculator!$B$37+F72+Calculator!$B$30)</f>
+        <f>IF(A72="","",E72*Calculator!$B$6+Calculator!$C$37+F72+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H72" s="16">
@@ -4243,7 +4259,7 @@
         <v/>
       </c>
       <c r="G73" s="16">
-        <f>IF(A73="","",E73*Calculator!$B$6+Calculator!$B$37+F73+Calculator!$B$30)</f>
+        <f>IF(A73="","",E73*Calculator!$B$6+Calculator!$C$37+F73+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H73" s="16">
@@ -4285,7 +4301,7 @@
         <v/>
       </c>
       <c r="G74" s="16">
-        <f>IF(A74="","",E74*Calculator!$B$6+Calculator!$B$37+F74+Calculator!$B$30)</f>
+        <f>IF(A74="","",E74*Calculator!$B$6+Calculator!$C$37+F74+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H74" s="16">
@@ -4327,7 +4343,7 @@
         <v/>
       </c>
       <c r="G75" s="16">
-        <f>IF(A75="","",E75*Calculator!$B$6+Calculator!$B$37+F75+Calculator!$B$30)</f>
+        <f>IF(A75="","",E75*Calculator!$B$6+Calculator!$C$37+F75+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H75" s="16">
@@ -4369,7 +4385,7 @@
         <v/>
       </c>
       <c r="G76" s="16">
-        <f>IF(A76="","",E76*Calculator!$B$6+Calculator!$B$37+F76+Calculator!$B$30)</f>
+        <f>IF(A76="","",E76*Calculator!$B$6+Calculator!$C$37+F76+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H76" s="16">
@@ -4411,7 +4427,7 @@
         <v/>
       </c>
       <c r="G77" s="16">
-        <f>IF(A77="","",E77*Calculator!$B$6+Calculator!$B$37+F77+Calculator!$B$30)</f>
+        <f>IF(A77="","",E77*Calculator!$B$6+Calculator!$C$37+F77+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H77" s="16">
@@ -4453,7 +4469,7 @@
         <v/>
       </c>
       <c r="G78" s="16">
-        <f>IF(A78="","",E78*Calculator!$B$6+Calculator!$B$37+F78+Calculator!$B$30)</f>
+        <f>IF(A78="","",E78*Calculator!$B$6+Calculator!$C$37+F78+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H78" s="16">
@@ -4495,7 +4511,7 @@
         <v/>
       </c>
       <c r="G79" s="16">
-        <f>IF(A79="","",E79*Calculator!$B$6+Calculator!$B$37+F79+Calculator!$B$30)</f>
+        <f>IF(A79="","",E79*Calculator!$B$6+Calculator!$C$37+F79+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H79" s="16">
@@ -4537,7 +4553,7 @@
         <v/>
       </c>
       <c r="G80" s="16">
-        <f>IF(A80="","",E80*Calculator!$B$6+Calculator!$B$37+F80+Calculator!$B$30)</f>
+        <f>IF(A80="","",E80*Calculator!$B$6+Calculator!$C$37+F80+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H80" s="16">
@@ -4579,7 +4595,7 @@
         <v/>
       </c>
       <c r="G81" s="16">
-        <f>IF(A81="","",E81*Calculator!$B$6+Calculator!$B$37+F81+Calculator!$B$30)</f>
+        <f>IF(A81="","",E81*Calculator!$B$6+Calculator!$C$37+F81+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H81" s="16">
@@ -4621,7 +4637,7 @@
         <v/>
       </c>
       <c r="G82" s="16">
-        <f>IF(A82="","",E82*Calculator!$B$6+Calculator!$B$37+F82+Calculator!$B$30)</f>
+        <f>IF(A82="","",E82*Calculator!$B$6+Calculator!$C$37+F82+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H82" s="16">
@@ -4663,7 +4679,7 @@
         <v/>
       </c>
       <c r="G83" s="16">
-        <f>IF(A83="","",E83*Calculator!$B$6+Calculator!$B$37+F83+Calculator!$B$30)</f>
+        <f>IF(A83="","",E83*Calculator!$B$6+Calculator!$C$37+F83+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H83" s="16">
@@ -4705,7 +4721,7 @@
         <v/>
       </c>
       <c r="G84" s="16">
-        <f>IF(A84="","",E84*Calculator!$B$6+Calculator!$B$37+F84+Calculator!$B$30)</f>
+        <f>IF(A84="","",E84*Calculator!$B$6+Calculator!$C$37+F84+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H84" s="16">
@@ -4747,7 +4763,7 @@
         <v/>
       </c>
       <c r="G85" s="16">
-        <f>IF(A85="","",E85*Calculator!$B$6+Calculator!$B$37+F85+Calculator!$B$30)</f>
+        <f>IF(A85="","",E85*Calculator!$B$6+Calculator!$C$37+F85+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H85" s="16">
@@ -4789,7 +4805,7 @@
         <v/>
       </c>
       <c r="G86" s="16">
-        <f>IF(A86="","",E86*Calculator!$B$6+Calculator!$B$37+F86+Calculator!$B$30)</f>
+        <f>IF(A86="","",E86*Calculator!$B$6+Calculator!$C$37+F86+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H86" s="16">
@@ -4831,7 +4847,7 @@
         <v/>
       </c>
       <c r="G87" s="16">
-        <f>IF(A87="","",E87*Calculator!$B$6+Calculator!$B$37+F87+Calculator!$B$30)</f>
+        <f>IF(A87="","",E87*Calculator!$B$6+Calculator!$C$37+F87+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H87" s="16">
@@ -4873,7 +4889,7 @@
         <v/>
       </c>
       <c r="G88" s="16">
-        <f>IF(A88="","",E88*Calculator!$B$6+Calculator!$B$37+F88+Calculator!$B$30)</f>
+        <f>IF(A88="","",E88*Calculator!$B$6+Calculator!$C$37+F88+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H88" s="16">
@@ -4915,7 +4931,7 @@
         <v/>
       </c>
       <c r="G89" s="16">
-        <f>IF(A89="","",E89*Calculator!$B$6+Calculator!$B$37+F89+Calculator!$B$30)</f>
+        <f>IF(A89="","",E89*Calculator!$B$6+Calculator!$C$37+F89+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H89" s="16">
@@ -4957,7 +4973,7 @@
         <v/>
       </c>
       <c r="G90" s="16">
-        <f>IF(A90="","",E90*Calculator!$B$6+Calculator!$B$37+F90+Calculator!$B$30)</f>
+        <f>IF(A90="","",E90*Calculator!$B$6+Calculator!$C$37+F90+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H90" s="16">
@@ -4999,7 +5015,7 @@
         <v/>
       </c>
       <c r="G91" s="16">
-        <f>IF(A91="","",E91*Calculator!$B$6+Calculator!$B$37+F91+Calculator!$B$30)</f>
+        <f>IF(A91="","",E91*Calculator!$B$6+Calculator!$C$37+F91+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H91" s="16">
@@ -5041,7 +5057,7 @@
         <v/>
       </c>
       <c r="G92" s="16">
-        <f>IF(A92="","",E92*Calculator!$B$6+Calculator!$B$37+F92+Calculator!$B$30)</f>
+        <f>IF(A92="","",E92*Calculator!$B$6+Calculator!$C$37+F92+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H92" s="16">
@@ -5083,7 +5099,7 @@
         <v/>
       </c>
       <c r="G93" s="16">
-        <f>IF(A93="","",E93*Calculator!$B$6+Calculator!$B$37+F93+Calculator!$B$30)</f>
+        <f>IF(A93="","",E93*Calculator!$B$6+Calculator!$C$37+F93+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H93" s="16">
@@ -5125,7 +5141,7 @@
         <v/>
       </c>
       <c r="G94" s="16">
-        <f>IF(A94="","",E94*Calculator!$B$6+Calculator!$B$37+F94+Calculator!$B$30)</f>
+        <f>IF(A94="","",E94*Calculator!$B$6+Calculator!$C$37+F94+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H94" s="16">
@@ -5167,7 +5183,7 @@
         <v/>
       </c>
       <c r="G95" s="16">
-        <f>IF(A95="","",E95*Calculator!$B$6+Calculator!$B$37+F95+Calculator!$B$30)</f>
+        <f>IF(A95="","",E95*Calculator!$B$6+Calculator!$C$37+F95+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H95" s="16">
@@ -5209,7 +5225,7 @@
         <v/>
       </c>
       <c r="G96" s="16">
-        <f>IF(A96="","",E96*Calculator!$B$6+Calculator!$B$37+F96+Calculator!$B$30)</f>
+        <f>IF(A96="","",E96*Calculator!$B$6+Calculator!$C$37+F96+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H96" s="16">
@@ -5251,7 +5267,7 @@
         <v/>
       </c>
       <c r="G97" s="16">
-        <f>IF(A97="","",E97*Calculator!$B$6+Calculator!$B$37+F97+Calculator!$B$30)</f>
+        <f>IF(A97="","",E97*Calculator!$B$6+Calculator!$C$37+F97+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H97" s="16">
@@ -5293,7 +5309,7 @@
         <v/>
       </c>
       <c r="G98" s="16">
-        <f>IF(A98="","",E98*Calculator!$B$6+Calculator!$B$37+F98+Calculator!$B$30)</f>
+        <f>IF(A98="","",E98*Calculator!$B$6+Calculator!$C$37+F98+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H98" s="16">
@@ -5335,7 +5351,7 @@
         <v/>
       </c>
       <c r="G99" s="16">
-        <f>IF(A99="","",E99*Calculator!$B$6+Calculator!$B$37+F99+Calculator!$B$30)</f>
+        <f>IF(A99="","",E99*Calculator!$B$6+Calculator!$C$37+F99+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H99" s="16">
@@ -5377,7 +5393,7 @@
         <v/>
       </c>
       <c r="G100" s="16">
-        <f>IF(A100="","",E100*Calculator!$B$6+Calculator!$B$37+F100+Calculator!$B$30)</f>
+        <f>IF(A100="","",E100*Calculator!$B$6+Calculator!$C$37+F100+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H100" s="16">
@@ -5419,7 +5435,7 @@
         <v/>
       </c>
       <c r="G101" s="16">
-        <f>IF(A101="","",E101*Calculator!$B$6+Calculator!$B$37+F101+Calculator!$B$30)</f>
+        <f>IF(A101="","",E101*Calculator!$B$6+Calculator!$C$37+F101+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H101" s="16">
@@ -5461,7 +5477,7 @@
         <v/>
       </c>
       <c r="G102" s="16">
-        <f>IF(A102="","",E102*Calculator!$B$6+Calculator!$B$37+F102+Calculator!$B$30)</f>
+        <f>IF(A102="","",E102*Calculator!$B$6+Calculator!$C$37+F102+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H102" s="16">
@@ -5503,7 +5519,7 @@
         <v/>
       </c>
       <c r="G103" s="16">
-        <f>IF(A103="","",E103*Calculator!$B$6+Calculator!$B$37+F103+Calculator!$B$30)</f>
+        <f>IF(A103="","",E103*Calculator!$B$6+Calculator!$C$37+F103+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H103" s="16">
@@ -5545,7 +5561,7 @@
         <v/>
       </c>
       <c r="G104" s="16">
-        <f>IF(A104="","",E104*Calculator!$B$6+Calculator!$B$37+F104+Calculator!$B$30)</f>
+        <f>IF(A104="","",E104*Calculator!$B$6+Calculator!$C$37+F104+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H104" s="16">
@@ -5587,7 +5603,7 @@
         <v/>
       </c>
       <c r="G105" s="16">
-        <f>IF(A105="","",E105*Calculator!$B$6+Calculator!$B$37+F105+Calculator!$B$30)</f>
+        <f>IF(A105="","",E105*Calculator!$B$6+Calculator!$C$37+F105+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H105" s="16">
@@ -5629,7 +5645,7 @@
         <v/>
       </c>
       <c r="G106" s="16">
-        <f>IF(A106="","",E106*Calculator!$B$6+Calculator!$B$37+F106+Calculator!$B$30)</f>
+        <f>IF(A106="","",E106*Calculator!$B$6+Calculator!$C$37+F106+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H106" s="16">
@@ -5671,7 +5687,7 @@
         <v/>
       </c>
       <c r="G107" s="16">
-        <f>IF(A107="","",E107*Calculator!$B$6+Calculator!$B$37+F107+Calculator!$B$30)</f>
+        <f>IF(A107="","",E107*Calculator!$B$6+Calculator!$C$37+F107+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H107" s="16">
@@ -5713,7 +5729,7 @@
         <v/>
       </c>
       <c r="G108" s="16">
-        <f>IF(A108="","",E108*Calculator!$B$6+Calculator!$B$37+F108+Calculator!$B$30)</f>
+        <f>IF(A108="","",E108*Calculator!$B$6+Calculator!$C$37+F108+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H108" s="16">
@@ -5755,7 +5771,7 @@
         <v/>
       </c>
       <c r="G109" s="16">
-        <f>IF(A109="","",E109*Calculator!$B$6+Calculator!$B$37+F109+Calculator!$B$30)</f>
+        <f>IF(A109="","",E109*Calculator!$B$6+Calculator!$C$37+F109+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H109" s="16">
@@ -5797,7 +5813,7 @@
         <v/>
       </c>
       <c r="G110" s="16">
-        <f>IF(A110="","",E110*Calculator!$B$6+Calculator!$B$37+F110+Calculator!$B$30)</f>
+        <f>IF(A110="","",E110*Calculator!$B$6+Calculator!$C$37+F110+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H110" s="16">
@@ -5839,7 +5855,7 @@
         <v/>
       </c>
       <c r="G111" s="16">
-        <f>IF(A111="","",E111*Calculator!$B$6+Calculator!$B$37+F111+Calculator!$B$30)</f>
+        <f>IF(A111="","",E111*Calculator!$B$6+Calculator!$C$37+F111+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H111" s="16">
@@ -5881,7 +5897,7 @@
         <v/>
       </c>
       <c r="G112" s="16">
-        <f>IF(A112="","",E112*Calculator!$B$6+Calculator!$B$37+F112+Calculator!$B$30)</f>
+        <f>IF(A112="","",E112*Calculator!$B$6+Calculator!$C$37+F112+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H112" s="16">
@@ -5923,7 +5939,7 @@
         <v/>
       </c>
       <c r="G113" s="16">
-        <f>IF(A113="","",E113*Calculator!$B$6+Calculator!$B$37+F113+Calculator!$B$30)</f>
+        <f>IF(A113="","",E113*Calculator!$B$6+Calculator!$C$37+F113+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H113" s="16">
@@ -5965,7 +5981,7 @@
         <v/>
       </c>
       <c r="G114" s="16">
-        <f>IF(A114="","",E114*Calculator!$B$6+Calculator!$B$37+F114+Calculator!$B$30)</f>
+        <f>IF(A114="","",E114*Calculator!$B$6+Calculator!$C$37+F114+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H114" s="16">
@@ -6007,7 +6023,7 @@
         <v/>
       </c>
       <c r="G115" s="16">
-        <f>IF(A115="","",E115*Calculator!$B$6+Calculator!$B$37+F115+Calculator!$B$30)</f>
+        <f>IF(A115="","",E115*Calculator!$B$6+Calculator!$C$37+F115+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H115" s="16">
@@ -6049,7 +6065,7 @@
         <v/>
       </c>
       <c r="G116" s="16">
-        <f>IF(A116="","",E116*Calculator!$B$6+Calculator!$B$37+F116+Calculator!$B$30)</f>
+        <f>IF(A116="","",E116*Calculator!$B$6+Calculator!$C$37+F116+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H116" s="16">
@@ -6091,7 +6107,7 @@
         <v/>
       </c>
       <c r="G117" s="16">
-        <f>IF(A117="","",E117*Calculator!$B$6+Calculator!$B$37+F117+Calculator!$B$30)</f>
+        <f>IF(A117="","",E117*Calculator!$B$6+Calculator!$C$37+F117+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H117" s="16">
@@ -6133,7 +6149,7 @@
         <v/>
       </c>
       <c r="G118" s="16">
-        <f>IF(A118="","",E118*Calculator!$B$6+Calculator!$B$37+F118+Calculator!$B$30)</f>
+        <f>IF(A118="","",E118*Calculator!$B$6+Calculator!$C$37+F118+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H118" s="16">
@@ -6175,7 +6191,7 @@
         <v/>
       </c>
       <c r="G119" s="16">
-        <f>IF(A119="","",E119*Calculator!$B$6+Calculator!$B$37+F119+Calculator!$B$30)</f>
+        <f>IF(A119="","",E119*Calculator!$B$6+Calculator!$C$37+F119+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H119" s="16">
@@ -6217,7 +6233,7 @@
         <v/>
       </c>
       <c r="G120" s="16">
-        <f>IF(A120="","",E120*Calculator!$B$6+Calculator!$B$37+F120+Calculator!$B$30)</f>
+        <f>IF(A120="","",E120*Calculator!$B$6+Calculator!$C$37+F120+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H120" s="16">
@@ -6259,7 +6275,7 @@
         <v/>
       </c>
       <c r="G121" s="16">
-        <f>IF(A121="","",E121*Calculator!$B$6+Calculator!$B$37+F121+Calculator!$B$30)</f>
+        <f>IF(A121="","",E121*Calculator!$B$6+Calculator!$C$37+F121+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H121" s="16">
@@ -6301,7 +6317,7 @@
         <v/>
       </c>
       <c r="G122" s="16">
-        <f>IF(A122="","",E122*Calculator!$B$6+Calculator!$B$37+F122+Calculator!$B$30)</f>
+        <f>IF(A122="","",E122*Calculator!$B$6+Calculator!$C$37+F122+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H122" s="16">
@@ -6343,7 +6359,7 @@
         <v/>
       </c>
       <c r="G123" s="16">
-        <f>IF(A123="","",E123*Calculator!$B$6+Calculator!$B$37+F123+Calculator!$B$30)</f>
+        <f>IF(A123="","",E123*Calculator!$B$6+Calculator!$C$37+F123+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H123" s="16">
@@ -6385,7 +6401,7 @@
         <v/>
       </c>
       <c r="G124" s="16">
-        <f>IF(A124="","",E124*Calculator!$B$6+Calculator!$B$37+F124+Calculator!$B$30)</f>
+        <f>IF(A124="","",E124*Calculator!$B$6+Calculator!$C$37+F124+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H124" s="16">
@@ -6427,7 +6443,7 @@
         <v/>
       </c>
       <c r="G125" s="16">
-        <f>IF(A125="","",E125*Calculator!$B$6+Calculator!$B$37+F125+Calculator!$B$30)</f>
+        <f>IF(A125="","",E125*Calculator!$B$6+Calculator!$C$37+F125+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H125" s="16">
@@ -6469,7 +6485,7 @@
         <v/>
       </c>
       <c r="G126" s="16">
-        <f>IF(A126="","",E126*Calculator!$B$6+Calculator!$B$37+F126+Calculator!$B$30)</f>
+        <f>IF(A126="","",E126*Calculator!$B$6+Calculator!$C$37+F126+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H126" s="16">
@@ -6511,7 +6527,7 @@
         <v/>
       </c>
       <c r="G127" s="16">
-        <f>IF(A127="","",E127*Calculator!$B$6+Calculator!$B$37+F127+Calculator!$B$30)</f>
+        <f>IF(A127="","",E127*Calculator!$B$6+Calculator!$C$37+F127+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H127" s="16">
@@ -6553,7 +6569,7 @@
         <v/>
       </c>
       <c r="G128" s="16">
-        <f>IF(A128="","",E128*Calculator!$B$6+Calculator!$B$37+F128+Calculator!$B$30)</f>
+        <f>IF(A128="","",E128*Calculator!$B$6+Calculator!$C$37+F128+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H128" s="16">
@@ -6595,7 +6611,7 @@
         <v/>
       </c>
       <c r="G129" s="16">
-        <f>IF(A129="","",E129*Calculator!$B$6+Calculator!$B$37+F129+Calculator!$B$30)</f>
+        <f>IF(A129="","",E129*Calculator!$B$6+Calculator!$C$37+F129+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H129" s="16">
@@ -6637,7 +6653,7 @@
         <v/>
       </c>
       <c r="G130" s="16">
-        <f>IF(A130="","",E130*Calculator!$B$6+Calculator!$B$37+F130+Calculator!$B$30)</f>
+        <f>IF(A130="","",E130*Calculator!$B$6+Calculator!$C$37+F130+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H130" s="16">
@@ -6679,7 +6695,7 @@
         <v/>
       </c>
       <c r="G131" s="16">
-        <f>IF(A131="","",E131*Calculator!$B$6+Calculator!$B$37+F131+Calculator!$B$30)</f>
+        <f>IF(A131="","",E131*Calculator!$B$6+Calculator!$C$37+F131+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H131" s="16">
@@ -6721,7 +6737,7 @@
         <v/>
       </c>
       <c r="G132" s="16">
-        <f>IF(A132="","",E132*Calculator!$B$6+Calculator!$B$37+F132+Calculator!$B$30)</f>
+        <f>IF(A132="","",E132*Calculator!$B$6+Calculator!$C$37+F132+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H132" s="16">
@@ -6763,7 +6779,7 @@
         <v/>
       </c>
       <c r="G133" s="16">
-        <f>IF(A133="","",E133*Calculator!$B$6+Calculator!$B$37+F133+Calculator!$B$30)</f>
+        <f>IF(A133="","",E133*Calculator!$B$6+Calculator!$C$37+F133+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H133" s="16">
@@ -6805,7 +6821,7 @@
         <v/>
       </c>
       <c r="G134" s="16">
-        <f>IF(A134="","",E134*Calculator!$B$6+Calculator!$B$37+F134+Calculator!$B$30)</f>
+        <f>IF(A134="","",E134*Calculator!$B$6+Calculator!$C$37+F134+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H134" s="16">
@@ -6847,7 +6863,7 @@
         <v/>
       </c>
       <c r="G135" s="16">
-        <f>IF(A135="","",E135*Calculator!$B$6+Calculator!$B$37+F135+Calculator!$B$30)</f>
+        <f>IF(A135="","",E135*Calculator!$B$6+Calculator!$C$37+F135+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H135" s="16">
@@ -6889,7 +6905,7 @@
         <v/>
       </c>
       <c r="G136" s="16">
-        <f>IF(A136="","",E136*Calculator!$B$6+Calculator!$B$37+F136+Calculator!$B$30)</f>
+        <f>IF(A136="","",E136*Calculator!$B$6+Calculator!$C$37+F136+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H136" s="16">
@@ -6931,7 +6947,7 @@
         <v/>
       </c>
       <c r="G137" s="16">
-        <f>IF(A137="","",E137*Calculator!$B$6+Calculator!$B$37+F137+Calculator!$B$30)</f>
+        <f>IF(A137="","",E137*Calculator!$B$6+Calculator!$C$37+F137+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H137" s="16">
@@ -6973,7 +6989,7 @@
         <v/>
       </c>
       <c r="G138" s="16">
-        <f>IF(A138="","",E138*Calculator!$B$6+Calculator!$B$37+F138+Calculator!$B$30)</f>
+        <f>IF(A138="","",E138*Calculator!$B$6+Calculator!$C$37+F138+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H138" s="16">
@@ -7015,7 +7031,7 @@
         <v/>
       </c>
       <c r="G139" s="16">
-        <f>IF(A139="","",E139*Calculator!$B$6+Calculator!$B$37+F139+Calculator!$B$30)</f>
+        <f>IF(A139="","",E139*Calculator!$B$6+Calculator!$C$37+F139+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H139" s="16">
@@ -7057,7 +7073,7 @@
         <v/>
       </c>
       <c r="G140" s="16">
-        <f>IF(A140="","",E140*Calculator!$B$6+Calculator!$B$37+F140+Calculator!$B$30)</f>
+        <f>IF(A140="","",E140*Calculator!$B$6+Calculator!$C$37+F140+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H140" s="16">
@@ -7099,7 +7115,7 @@
         <v/>
       </c>
       <c r="G141" s="16">
-        <f>IF(A141="","",E141*Calculator!$B$6+Calculator!$B$37+F141+Calculator!$B$30)</f>
+        <f>IF(A141="","",E141*Calculator!$B$6+Calculator!$C$37+F141+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H141" s="16">
@@ -7141,7 +7157,7 @@
         <v/>
       </c>
       <c r="G142" s="16">
-        <f>IF(A142="","",E142*Calculator!$B$6+Calculator!$B$37+F142+Calculator!$B$30)</f>
+        <f>IF(A142="","",E142*Calculator!$B$6+Calculator!$C$37+F142+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H142" s="16">
@@ -7183,7 +7199,7 @@
         <v/>
       </c>
       <c r="G143" s="16">
-        <f>IF(A143="","",E143*Calculator!$B$6+Calculator!$B$37+F143+Calculator!$B$30)</f>
+        <f>IF(A143="","",E143*Calculator!$B$6+Calculator!$C$37+F143+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H143" s="16">
@@ -7225,7 +7241,7 @@
         <v/>
       </c>
       <c r="G144" s="16">
-        <f>IF(A144="","",E144*Calculator!$B$6+Calculator!$B$37+F144+Calculator!$B$30)</f>
+        <f>IF(A144="","",E144*Calculator!$B$6+Calculator!$C$37+F144+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H144" s="16">
@@ -7267,7 +7283,7 @@
         <v/>
       </c>
       <c r="G145" s="16">
-        <f>IF(A145="","",E145*Calculator!$B$6+Calculator!$B$37+F145+Calculator!$B$30)</f>
+        <f>IF(A145="","",E145*Calculator!$B$6+Calculator!$C$37+F145+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H145" s="16">
@@ -7309,7 +7325,7 @@
         <v/>
       </c>
       <c r="G146" s="16">
-        <f>IF(A146="","",E146*Calculator!$B$6+Calculator!$B$37+F146+Calculator!$B$30)</f>
+        <f>IF(A146="","",E146*Calculator!$B$6+Calculator!$C$37+F146+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H146" s="16">
@@ -7351,7 +7367,7 @@
         <v/>
       </c>
       <c r="G147" s="16">
-        <f>IF(A147="","",E147*Calculator!$B$6+Calculator!$B$37+F147+Calculator!$B$30)</f>
+        <f>IF(A147="","",E147*Calculator!$B$6+Calculator!$C$37+F147+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H147" s="16">
@@ -7393,7 +7409,7 @@
         <v/>
       </c>
       <c r="G148" s="16">
-        <f>IF(A148="","",E148*Calculator!$B$6+Calculator!$B$37+F148+Calculator!$B$30)</f>
+        <f>IF(A148="","",E148*Calculator!$B$6+Calculator!$C$37+F148+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H148" s="16">
@@ -7435,7 +7451,7 @@
         <v/>
       </c>
       <c r="G149" s="16">
-        <f>IF(A149="","",E149*Calculator!$B$6+Calculator!$B$37+F149+Calculator!$B$30)</f>
+        <f>IF(A149="","",E149*Calculator!$B$6+Calculator!$C$37+F149+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H149" s="16">
@@ -7477,7 +7493,7 @@
         <v/>
       </c>
       <c r="G150" s="16">
-        <f>IF(A150="","",E150*Calculator!$B$6+Calculator!$B$37+F150+Calculator!$B$30)</f>
+        <f>IF(A150="","",E150*Calculator!$B$6+Calculator!$C$37+F150+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H150" s="16">
@@ -7519,7 +7535,7 @@
         <v/>
       </c>
       <c r="G151" s="16">
-        <f>IF(A151="","",E151*Calculator!$B$6+Calculator!$B$37+F151+Calculator!$B$30)</f>
+        <f>IF(A151="","",E151*Calculator!$B$6+Calculator!$C$37+F151+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H151" s="16">
@@ -7561,7 +7577,7 @@
         <v/>
       </c>
       <c r="G152" s="16">
-        <f>IF(A152="","",E152*Calculator!$B$6+Calculator!$B$37+F152+Calculator!$B$30)</f>
+        <f>IF(A152="","",E152*Calculator!$B$6+Calculator!$C$37+F152+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H152" s="16">
@@ -7603,7 +7619,7 @@
         <v/>
       </c>
       <c r="G153" s="16">
-        <f>IF(A153="","",E153*Calculator!$B$6+Calculator!$B$37+F153+Calculator!$B$30)</f>
+        <f>IF(A153="","",E153*Calculator!$B$6+Calculator!$C$37+F153+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H153" s="16">
@@ -7645,7 +7661,7 @@
         <v/>
       </c>
       <c r="G154" s="16">
-        <f>IF(A154="","",E154*Calculator!$B$6+Calculator!$B$37+F154+Calculator!$B$30)</f>
+        <f>IF(A154="","",E154*Calculator!$B$6+Calculator!$C$37+F154+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H154" s="16">
@@ -7687,7 +7703,7 @@
         <v/>
       </c>
       <c r="G155" s="16">
-        <f>IF(A155="","",E155*Calculator!$B$6+Calculator!$B$37+F155+Calculator!$B$30)</f>
+        <f>IF(A155="","",E155*Calculator!$B$6+Calculator!$C$37+F155+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H155" s="16">
@@ -7729,7 +7745,7 @@
         <v/>
       </c>
       <c r="G156" s="16">
-        <f>IF(A156="","",E156*Calculator!$B$6+Calculator!$B$37+F156+Calculator!$B$30)</f>
+        <f>IF(A156="","",E156*Calculator!$B$6+Calculator!$C$37+F156+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H156" s="16">
@@ -7771,7 +7787,7 @@
         <v/>
       </c>
       <c r="G157" s="16">
-        <f>IF(A157="","",E157*Calculator!$B$6+Calculator!$B$37+F157+Calculator!$B$30)</f>
+        <f>IF(A157="","",E157*Calculator!$B$6+Calculator!$C$37+F157+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H157" s="16">
@@ -7813,7 +7829,7 @@
         <v/>
       </c>
       <c r="G158" s="16">
-        <f>IF(A158="","",E158*Calculator!$B$6+Calculator!$B$37+F158+Calculator!$B$30)</f>
+        <f>IF(A158="","",E158*Calculator!$B$6+Calculator!$C$37+F158+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H158" s="16">
@@ -7855,7 +7871,7 @@
         <v/>
       </c>
       <c r="G159" s="16">
-        <f>IF(A159="","",E159*Calculator!$B$6+Calculator!$B$37+F159+Calculator!$B$30)</f>
+        <f>IF(A159="","",E159*Calculator!$B$6+Calculator!$C$37+F159+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H159" s="16">
@@ -7897,7 +7913,7 @@
         <v/>
       </c>
       <c r="G160" s="16">
-        <f>IF(A160="","",E160*Calculator!$B$6+Calculator!$B$37+F160+Calculator!$B$30)</f>
+        <f>IF(A160="","",E160*Calculator!$B$6+Calculator!$C$37+F160+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H160" s="16">
@@ -7939,7 +7955,7 @@
         <v/>
       </c>
       <c r="G161" s="16">
-        <f>IF(A161="","",E161*Calculator!$B$6+Calculator!$B$37+F161+Calculator!$B$30)</f>
+        <f>IF(A161="","",E161*Calculator!$B$6+Calculator!$C$37+F161+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H161" s="16">
@@ -7981,7 +7997,7 @@
         <v/>
       </c>
       <c r="G162" s="16">
-        <f>IF(A162="","",E162*Calculator!$B$6+Calculator!$B$37+F162+Calculator!$B$30)</f>
+        <f>IF(A162="","",E162*Calculator!$B$6+Calculator!$C$37+F162+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H162" s="16">
@@ -8023,7 +8039,7 @@
         <v/>
       </c>
       <c r="G163" s="16">
-        <f>IF(A163="","",E163*Calculator!$B$6+Calculator!$B$37+F163+Calculator!$B$30)</f>
+        <f>IF(A163="","",E163*Calculator!$B$6+Calculator!$C$37+F163+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H163" s="16">
@@ -8065,7 +8081,7 @@
         <v/>
       </c>
       <c r="G164" s="16">
-        <f>IF(A164="","",E164*Calculator!$B$6+Calculator!$B$37+F164+Calculator!$B$30)</f>
+        <f>IF(A164="","",E164*Calculator!$B$6+Calculator!$C$37+F164+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H164" s="16">
@@ -8107,7 +8123,7 @@
         <v/>
       </c>
       <c r="G165" s="16">
-        <f>IF(A165="","",E165*Calculator!$B$6+Calculator!$B$37+F165+Calculator!$B$30)</f>
+        <f>IF(A165="","",E165*Calculator!$B$6+Calculator!$C$37+F165+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H165" s="16">
@@ -8149,7 +8165,7 @@
         <v/>
       </c>
       <c r="G166" s="16">
-        <f>IF(A166="","",E166*Calculator!$B$6+Calculator!$B$37+F166+Calculator!$B$30)</f>
+        <f>IF(A166="","",E166*Calculator!$B$6+Calculator!$C$37+F166+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H166" s="16">
@@ -8191,7 +8207,7 @@
         <v/>
       </c>
       <c r="G167" s="16">
-        <f>IF(A167="","",E167*Calculator!$B$6+Calculator!$B$37+F167+Calculator!$B$30)</f>
+        <f>IF(A167="","",E167*Calculator!$B$6+Calculator!$C$37+F167+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H167" s="16">
@@ -8233,7 +8249,7 @@
         <v/>
       </c>
       <c r="G168" s="16">
-        <f>IF(A168="","",E168*Calculator!$B$6+Calculator!$B$37+F168+Calculator!$B$30)</f>
+        <f>IF(A168="","",E168*Calculator!$B$6+Calculator!$C$37+F168+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H168" s="16">
@@ -8275,7 +8291,7 @@
         <v/>
       </c>
       <c r="G169" s="16">
-        <f>IF(A169="","",E169*Calculator!$B$6+Calculator!$B$37+F169+Calculator!$B$30)</f>
+        <f>IF(A169="","",E169*Calculator!$B$6+Calculator!$C$37+F169+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H169" s="16">
@@ -8317,7 +8333,7 @@
         <v/>
       </c>
       <c r="G170" s="16">
-        <f>IF(A170="","",E170*Calculator!$B$6+Calculator!$B$37+F170+Calculator!$B$30)</f>
+        <f>IF(A170="","",E170*Calculator!$B$6+Calculator!$C$37+F170+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H170" s="16">
@@ -8359,7 +8375,7 @@
         <v/>
       </c>
       <c r="G171" s="16">
-        <f>IF(A171="","",E171*Calculator!$B$6+Calculator!$B$37+F171+Calculator!$B$30)</f>
+        <f>IF(A171="","",E171*Calculator!$B$6+Calculator!$C$37+F171+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H171" s="16">
@@ -8401,7 +8417,7 @@
         <v/>
       </c>
       <c r="G172" s="16">
-        <f>IF(A172="","",E172*Calculator!$B$6+Calculator!$B$37+F172+Calculator!$B$30)</f>
+        <f>IF(A172="","",E172*Calculator!$B$6+Calculator!$C$37+F172+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H172" s="16">
@@ -8443,7 +8459,7 @@
         <v/>
       </c>
       <c r="G173" s="16">
-        <f>IF(A173="","",E173*Calculator!$B$6+Calculator!$B$37+F173+Calculator!$B$30)</f>
+        <f>IF(A173="","",E173*Calculator!$B$6+Calculator!$C$37+F173+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H173" s="16">
@@ -8485,7 +8501,7 @@
         <v/>
       </c>
       <c r="G174" s="16">
-        <f>IF(A174="","",E174*Calculator!$B$6+Calculator!$B$37+F174+Calculator!$B$30)</f>
+        <f>IF(A174="","",E174*Calculator!$B$6+Calculator!$C$37+F174+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H174" s="16">
@@ -8527,7 +8543,7 @@
         <v/>
       </c>
       <c r="G175" s="16">
-        <f>IF(A175="","",E175*Calculator!$B$6+Calculator!$B$37+F175+Calculator!$B$30)</f>
+        <f>IF(A175="","",E175*Calculator!$B$6+Calculator!$C$37+F175+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H175" s="16">
@@ -8569,7 +8585,7 @@
         <v/>
       </c>
       <c r="G176" s="16">
-        <f>IF(A176="","",E176*Calculator!$B$6+Calculator!$B$37+F176+Calculator!$B$30)</f>
+        <f>IF(A176="","",E176*Calculator!$B$6+Calculator!$C$37+F176+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H176" s="16">
@@ -8611,7 +8627,7 @@
         <v/>
       </c>
       <c r="G177" s="16">
-        <f>IF(A177="","",E177*Calculator!$B$6+Calculator!$B$37+F177+Calculator!$B$30)</f>
+        <f>IF(A177="","",E177*Calculator!$B$6+Calculator!$C$37+F177+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H177" s="16">
@@ -8653,7 +8669,7 @@
         <v/>
       </c>
       <c r="G178" s="16">
-        <f>IF(A178="","",E178*Calculator!$B$6+Calculator!$B$37+F178+Calculator!$B$30)</f>
+        <f>IF(A178="","",E178*Calculator!$B$6+Calculator!$C$37+F178+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H178" s="16">
@@ -8695,7 +8711,7 @@
         <v/>
       </c>
       <c r="G179" s="16">
-        <f>IF(A179="","",E179*Calculator!$B$6+Calculator!$B$37+F179+Calculator!$B$30)</f>
+        <f>IF(A179="","",E179*Calculator!$B$6+Calculator!$C$37+F179+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H179" s="16">
@@ -8737,7 +8753,7 @@
         <v/>
       </c>
       <c r="G180" s="16">
-        <f>IF(A180="","",E180*Calculator!$B$6+Calculator!$B$37+F180+Calculator!$B$30)</f>
+        <f>IF(A180="","",E180*Calculator!$B$6+Calculator!$C$37+F180+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H180" s="16">
@@ -8779,7 +8795,7 @@
         <v/>
       </c>
       <c r="G181" s="16">
-        <f>IF(A181="","",E181*Calculator!$B$6+Calculator!$B$37+F181+Calculator!$B$30)</f>
+        <f>IF(A181="","",E181*Calculator!$B$6+Calculator!$C$37+F181+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H181" s="16">
@@ -8821,7 +8837,7 @@
         <v/>
       </c>
       <c r="G182" s="16">
-        <f>IF(A182="","",E182*Calculator!$B$6+Calculator!$B$37+F182+Calculator!$B$30)</f>
+        <f>IF(A182="","",E182*Calculator!$B$6+Calculator!$C$37+F182+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H182" s="16">
@@ -8863,7 +8879,7 @@
         <v/>
       </c>
       <c r="G183" s="16">
-        <f>IF(A183="","",E183*Calculator!$B$6+Calculator!$B$37+F183+Calculator!$B$30)</f>
+        <f>IF(A183="","",E183*Calculator!$B$6+Calculator!$C$37+F183+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H183" s="16">
@@ -8905,7 +8921,7 @@
         <v/>
       </c>
       <c r="G184" s="16">
-        <f>IF(A184="","",E184*Calculator!$B$6+Calculator!$B$37+F184+Calculator!$B$30)</f>
+        <f>IF(A184="","",E184*Calculator!$B$6+Calculator!$C$37+F184+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H184" s="16">
@@ -8947,7 +8963,7 @@
         <v/>
       </c>
       <c r="G185" s="16">
-        <f>IF(A185="","",E185*Calculator!$B$6+Calculator!$B$37+F185+Calculator!$B$30)</f>
+        <f>IF(A185="","",E185*Calculator!$B$6+Calculator!$C$37+F185+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H185" s="16">
@@ -8989,7 +9005,7 @@
         <v/>
       </c>
       <c r="G186" s="16">
-        <f>IF(A186="","",E186*Calculator!$B$6+Calculator!$B$37+F186+Calculator!$B$30)</f>
+        <f>IF(A186="","",E186*Calculator!$B$6+Calculator!$C$37+F186+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H186" s="16">
@@ -9031,7 +9047,7 @@
         <v/>
       </c>
       <c r="G187" s="16">
-        <f>IF(A187="","",E187*Calculator!$B$6+Calculator!$B$37+F187+Calculator!$B$30)</f>
+        <f>IF(A187="","",E187*Calculator!$B$6+Calculator!$C$37+F187+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H187" s="16">
@@ -9073,7 +9089,7 @@
         <v/>
       </c>
       <c r="G188" s="16">
-        <f>IF(A188="","",E188*Calculator!$B$6+Calculator!$B$37+F188+Calculator!$B$30)</f>
+        <f>IF(A188="","",E188*Calculator!$B$6+Calculator!$C$37+F188+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H188" s="16">
@@ -9115,7 +9131,7 @@
         <v/>
       </c>
       <c r="G189" s="16">
-        <f>IF(A189="","",E189*Calculator!$B$6+Calculator!$B$37+F189+Calculator!$B$30)</f>
+        <f>IF(A189="","",E189*Calculator!$B$6+Calculator!$C$37+F189+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H189" s="16">
@@ -9157,7 +9173,7 @@
         <v/>
       </c>
       <c r="G190" s="16">
-        <f>IF(A190="","",E190*Calculator!$B$6+Calculator!$B$37+F190+Calculator!$B$30)</f>
+        <f>IF(A190="","",E190*Calculator!$B$6+Calculator!$C$37+F190+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H190" s="16">
@@ -9199,7 +9215,7 @@
         <v/>
       </c>
       <c r="G191" s="16">
-        <f>IF(A191="","",E191*Calculator!$B$6+Calculator!$B$37+F191+Calculator!$B$30)</f>
+        <f>IF(A191="","",E191*Calculator!$B$6+Calculator!$C$37+F191+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H191" s="16">
@@ -9241,7 +9257,7 @@
         <v/>
       </c>
       <c r="G192" s="16">
-        <f>IF(A192="","",E192*Calculator!$B$6+Calculator!$B$37+F192+Calculator!$B$30)</f>
+        <f>IF(A192="","",E192*Calculator!$B$6+Calculator!$C$37+F192+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H192" s="16">
@@ -9283,7 +9299,7 @@
         <v/>
       </c>
       <c r="G193" s="16">
-        <f>IF(A193="","",E193*Calculator!$B$6+Calculator!$B$37+F193+Calculator!$B$30)</f>
+        <f>IF(A193="","",E193*Calculator!$B$6+Calculator!$C$37+F193+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H193" s="16">
@@ -9325,7 +9341,7 @@
         <v/>
       </c>
       <c r="G194" s="16">
-        <f>IF(A194="","",E194*Calculator!$B$6+Calculator!$B$37+F194+Calculator!$B$30)</f>
+        <f>IF(A194="","",E194*Calculator!$B$6+Calculator!$C$37+F194+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H194" s="16">
@@ -9367,7 +9383,7 @@
         <v/>
       </c>
       <c r="G195" s="16">
-        <f>IF(A195="","",E195*Calculator!$B$6+Calculator!$B$37+F195+Calculator!$B$30)</f>
+        <f>IF(A195="","",E195*Calculator!$B$6+Calculator!$C$37+F195+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H195" s="16">
@@ -9409,7 +9425,7 @@
         <v/>
       </c>
       <c r="G196" s="16">
-        <f>IF(A196="","",E196*Calculator!$B$6+Calculator!$B$37+F196+Calculator!$B$30)</f>
+        <f>IF(A196="","",E196*Calculator!$B$6+Calculator!$C$37+F196+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H196" s="16">
@@ -9451,7 +9467,7 @@
         <v/>
       </c>
       <c r="G197" s="16">
-        <f>IF(A197="","",E197*Calculator!$B$6+Calculator!$B$37+F197+Calculator!$B$30)</f>
+        <f>IF(A197="","",E197*Calculator!$B$6+Calculator!$C$37+F197+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H197" s="16">
@@ -9493,7 +9509,7 @@
         <v/>
       </c>
       <c r="G198" s="16">
-        <f>IF(A198="","",E198*Calculator!$B$6+Calculator!$B$37+F198+Calculator!$B$30)</f>
+        <f>IF(A198="","",E198*Calculator!$B$6+Calculator!$C$37+F198+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H198" s="16">
@@ -9535,7 +9551,7 @@
         <v/>
       </c>
       <c r="G199" s="16">
-        <f>IF(A199="","",E199*Calculator!$B$6+Calculator!$B$37+F199+Calculator!$B$30)</f>
+        <f>IF(A199="","",E199*Calculator!$B$6+Calculator!$C$37+F199+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H199" s="16">
@@ -9577,7 +9593,7 @@
         <v/>
       </c>
       <c r="G200" s="16">
-        <f>IF(A200="","",E200*Calculator!$B$6+Calculator!$B$37+F200+Calculator!$B$30)</f>
+        <f>IF(A200="","",E200*Calculator!$B$6+Calculator!$C$37+F200+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H200" s="16">
@@ -9619,7 +9635,7 @@
         <v/>
       </c>
       <c r="G201" s="16">
-        <f>IF(A201="","",E201*Calculator!$B$6+Calculator!$B$37+F201+Calculator!$B$30)</f>
+        <f>IF(A201="","",E201*Calculator!$B$6+Calculator!$C$37+F201+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H201" s="16">
@@ -9661,7 +9677,7 @@
         <v/>
       </c>
       <c r="G202" s="16">
-        <f>IF(A202="","",E202*Calculator!$B$6+Calculator!$B$37+F202+Calculator!$B$30)</f>
+        <f>IF(A202="","",E202*Calculator!$B$6+Calculator!$C$37+F202+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H202" s="16">
@@ -9703,7 +9719,7 @@
         <v/>
       </c>
       <c r="G203" s="16">
-        <f>IF(A203="","",E203*Calculator!$B$6+Calculator!$B$37+F203+Calculator!$B$30)</f>
+        <f>IF(A203="","",E203*Calculator!$B$6+Calculator!$C$37+F203+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H203" s="16">
@@ -9745,7 +9761,7 @@
         <v/>
       </c>
       <c r="G204" s="16">
-        <f>IF(A204="","",E204*Calculator!$B$6+Calculator!$B$37+F204+Calculator!$B$30)</f>
+        <f>IF(A204="","",E204*Calculator!$B$6+Calculator!$C$37+F204+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H204" s="16">
@@ -9787,7 +9803,7 @@
         <v/>
       </c>
       <c r="G205" s="16">
-        <f>IF(A205="","",E205*Calculator!$B$6+Calculator!$B$37+F205+Calculator!$B$30)</f>
+        <f>IF(A205="","",E205*Calculator!$B$6+Calculator!$C$37+F205+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H205" s="16">
@@ -9829,7 +9845,7 @@
         <v/>
       </c>
       <c r="G206" s="16">
-        <f>IF(A206="","",E206*Calculator!$B$6+Calculator!$B$37+F206+Calculator!$B$30)</f>
+        <f>IF(A206="","",E206*Calculator!$B$6+Calculator!$C$37+F206+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H206" s="16">
@@ -9871,7 +9887,7 @@
         <v/>
       </c>
       <c r="G207" s="16">
-        <f>IF(A207="","",E207*Calculator!$B$6+Calculator!$B$37+F207+Calculator!$B$30)</f>
+        <f>IF(A207="","",E207*Calculator!$B$6+Calculator!$C$37+F207+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H207" s="16">
@@ -9913,7 +9929,7 @@
         <v/>
       </c>
       <c r="G208" s="16">
-        <f>IF(A208="","",E208*Calculator!$B$6+Calculator!$B$37+F208+Calculator!$B$30)</f>
+        <f>IF(A208="","",E208*Calculator!$B$6+Calculator!$C$37+F208+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H208" s="16">
@@ -9955,7 +9971,7 @@
         <v/>
       </c>
       <c r="G209" s="16">
-        <f>IF(A209="","",E209*Calculator!$B$6+Calculator!$B$37+F209+Calculator!$B$30)</f>
+        <f>IF(A209="","",E209*Calculator!$B$6+Calculator!$C$37+F209+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H209" s="16">
@@ -9997,7 +10013,7 @@
         <v/>
       </c>
       <c r="G210" s="16">
-        <f>IF(A210="","",E210*Calculator!$B$6+Calculator!$B$37+F210+Calculator!$B$30)</f>
+        <f>IF(A210="","",E210*Calculator!$B$6+Calculator!$C$37+F210+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H210" s="16">
@@ -10039,7 +10055,7 @@
         <v/>
       </c>
       <c r="G211" s="16">
-        <f>IF(A211="","",E211*Calculator!$B$6+Calculator!$B$37+F211+Calculator!$B$30)</f>
+        <f>IF(A211="","",E211*Calculator!$B$6+Calculator!$C$37+F211+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H211" s="16">
@@ -10081,7 +10097,7 @@
         <v/>
       </c>
       <c r="G212" s="16">
-        <f>IF(A212="","",E212*Calculator!$B$6+Calculator!$B$37+F212+Calculator!$B$30)</f>
+        <f>IF(A212="","",E212*Calculator!$B$6+Calculator!$C$37+F212+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H212" s="16">
@@ -10123,7 +10139,7 @@
         <v/>
       </c>
       <c r="G213" s="16">
-        <f>IF(A213="","",E213*Calculator!$B$6+Calculator!$B$37+F213+Calculator!$B$30)</f>
+        <f>IF(A213="","",E213*Calculator!$B$6+Calculator!$C$37+F213+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H213" s="16">
@@ -10165,7 +10181,7 @@
         <v/>
       </c>
       <c r="G214" s="16">
-        <f>IF(A214="","",E214*Calculator!$B$6+Calculator!$B$37+F214+Calculator!$B$30)</f>
+        <f>IF(A214="","",E214*Calculator!$B$6+Calculator!$C$37+F214+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H214" s="16">
@@ -10207,7 +10223,7 @@
         <v/>
       </c>
       <c r="G215" s="16">
-        <f>IF(A215="","",E215*Calculator!$B$6+Calculator!$B$37+F215+Calculator!$B$30)</f>
+        <f>IF(A215="","",E215*Calculator!$B$6+Calculator!$C$37+F215+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H215" s="16">
@@ -10249,7 +10265,7 @@
         <v/>
       </c>
       <c r="G216" s="16">
-        <f>IF(A216="","",E216*Calculator!$B$6+Calculator!$B$37+F216+Calculator!$B$30)</f>
+        <f>IF(A216="","",E216*Calculator!$B$6+Calculator!$C$37+F216+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H216" s="16">
@@ -10291,7 +10307,7 @@
         <v/>
       </c>
       <c r="G217" s="16">
-        <f>IF(A217="","",E217*Calculator!$B$6+Calculator!$B$37+F217+Calculator!$B$30)</f>
+        <f>IF(A217="","",E217*Calculator!$B$6+Calculator!$C$37+F217+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H217" s="16">
@@ -10333,7 +10349,7 @@
         <v/>
       </c>
       <c r="G218" s="16">
-        <f>IF(A218="","",E218*Calculator!$B$6+Calculator!$B$37+F218+Calculator!$B$30)</f>
+        <f>IF(A218="","",E218*Calculator!$B$6+Calculator!$C$37+F218+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H218" s="16">
@@ -10375,7 +10391,7 @@
         <v/>
       </c>
       <c r="G219" s="16">
-        <f>IF(A219="","",E219*Calculator!$B$6+Calculator!$B$37+F219+Calculator!$B$30)</f>
+        <f>IF(A219="","",E219*Calculator!$B$6+Calculator!$C$37+F219+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H219" s="16">
@@ -10417,7 +10433,7 @@
         <v/>
       </c>
       <c r="G220" s="16">
-        <f>IF(A220="","",E220*Calculator!$B$6+Calculator!$B$37+F220+Calculator!$B$30)</f>
+        <f>IF(A220="","",E220*Calculator!$B$6+Calculator!$C$37+F220+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H220" s="16">
@@ -10459,7 +10475,7 @@
         <v/>
       </c>
       <c r="G221" s="16">
-        <f>IF(A221="","",E221*Calculator!$B$6+Calculator!$B$37+F221+Calculator!$B$30)</f>
+        <f>IF(A221="","",E221*Calculator!$B$6+Calculator!$C$37+F221+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H221" s="16">
@@ -10501,7 +10517,7 @@
         <v/>
       </c>
       <c r="G222" s="16">
-        <f>IF(A222="","",E222*Calculator!$B$6+Calculator!$B$37+F222+Calculator!$B$30)</f>
+        <f>IF(A222="","",E222*Calculator!$B$6+Calculator!$C$37+F222+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H222" s="16">
@@ -10543,7 +10559,7 @@
         <v/>
       </c>
       <c r="G223" s="16">
-        <f>IF(A223="","",E223*Calculator!$B$6+Calculator!$B$37+F223+Calculator!$B$30)</f>
+        <f>IF(A223="","",E223*Calculator!$B$6+Calculator!$C$37+F223+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H223" s="16">
@@ -10585,7 +10601,7 @@
         <v/>
       </c>
       <c r="G224" s="16">
-        <f>IF(A224="","",E224*Calculator!$B$6+Calculator!$B$37+F224+Calculator!$B$30)</f>
+        <f>IF(A224="","",E224*Calculator!$B$6+Calculator!$C$37+F224+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H224" s="16">
@@ -10627,7 +10643,7 @@
         <v/>
       </c>
       <c r="G225" s="16">
-        <f>IF(A225="","",E225*Calculator!$B$6+Calculator!$B$37+F225+Calculator!$B$30)</f>
+        <f>IF(A225="","",E225*Calculator!$B$6+Calculator!$C$37+F225+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H225" s="16">
@@ -10669,7 +10685,7 @@
         <v/>
       </c>
       <c r="G226" s="16">
-        <f>IF(A226="","",E226*Calculator!$B$6+Calculator!$B$37+F226+Calculator!$B$30)</f>
+        <f>IF(A226="","",E226*Calculator!$B$6+Calculator!$C$37+F226+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H226" s="16">
@@ -10711,7 +10727,7 @@
         <v/>
       </c>
       <c r="G227" s="16">
-        <f>IF(A227="","",E227*Calculator!$B$6+Calculator!$B$37+F227+Calculator!$B$30)</f>
+        <f>IF(A227="","",E227*Calculator!$B$6+Calculator!$C$37+F227+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H227" s="16">
@@ -10753,7 +10769,7 @@
         <v/>
       </c>
       <c r="G228" s="16">
-        <f>IF(A228="","",E228*Calculator!$B$6+Calculator!$B$37+F228+Calculator!$B$30)</f>
+        <f>IF(A228="","",E228*Calculator!$B$6+Calculator!$C$37+F228+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H228" s="16">
@@ -10795,7 +10811,7 @@
         <v/>
       </c>
       <c r="G229" s="16">
-        <f>IF(A229="","",E229*Calculator!$B$6+Calculator!$B$37+F229+Calculator!$B$30)</f>
+        <f>IF(A229="","",E229*Calculator!$B$6+Calculator!$C$37+F229+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H229" s="16">
@@ -10837,7 +10853,7 @@
         <v/>
       </c>
       <c r="G230" s="16">
-        <f>IF(A230="","",E230*Calculator!$B$6+Calculator!$B$37+F230+Calculator!$B$30)</f>
+        <f>IF(A230="","",E230*Calculator!$B$6+Calculator!$C$37+F230+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H230" s="16">
@@ -10879,7 +10895,7 @@
         <v/>
       </c>
       <c r="G231" s="16">
-        <f>IF(A231="","",E231*Calculator!$B$6+Calculator!$B$37+F231+Calculator!$B$30)</f>
+        <f>IF(A231="","",E231*Calculator!$B$6+Calculator!$C$37+F231+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H231" s="16">
@@ -10921,7 +10937,7 @@
         <v/>
       </c>
       <c r="G232" s="16">
-        <f>IF(A232="","",E232*Calculator!$B$6+Calculator!$B$37+F232+Calculator!$B$30)</f>
+        <f>IF(A232="","",E232*Calculator!$B$6+Calculator!$C$37+F232+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H232" s="16">
@@ -10963,7 +10979,7 @@
         <v/>
       </c>
       <c r="G233" s="16">
-        <f>IF(A233="","",E233*Calculator!$B$6+Calculator!$B$37+F233+Calculator!$B$30)</f>
+        <f>IF(A233="","",E233*Calculator!$B$6+Calculator!$C$37+F233+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H233" s="16">
@@ -11005,7 +11021,7 @@
         <v/>
       </c>
       <c r="G234" s="16">
-        <f>IF(A234="","",E234*Calculator!$B$6+Calculator!$B$37+F234+Calculator!$B$30)</f>
+        <f>IF(A234="","",E234*Calculator!$B$6+Calculator!$C$37+F234+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H234" s="16">
@@ -11047,7 +11063,7 @@
         <v/>
       </c>
       <c r="G235" s="16">
-        <f>IF(A235="","",E235*Calculator!$B$6+Calculator!$B$37+F235+Calculator!$B$30)</f>
+        <f>IF(A235="","",E235*Calculator!$B$6+Calculator!$C$37+F235+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H235" s="16">
@@ -11089,7 +11105,7 @@
         <v/>
       </c>
       <c r="G236" s="16">
-        <f>IF(A236="","",E236*Calculator!$B$6+Calculator!$B$37+F236+Calculator!$B$30)</f>
+        <f>IF(A236="","",E236*Calculator!$B$6+Calculator!$C$37+F236+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H236" s="16">
@@ -11131,7 +11147,7 @@
         <v/>
       </c>
       <c r="G237" s="16">
-        <f>IF(A237="","",E237*Calculator!$B$6+Calculator!$B$37+F237+Calculator!$B$30)</f>
+        <f>IF(A237="","",E237*Calculator!$B$6+Calculator!$C$37+F237+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H237" s="16">
@@ -11173,7 +11189,7 @@
         <v/>
       </c>
       <c r="G238" s="16">
-        <f>IF(A238="","",E238*Calculator!$B$6+Calculator!$B$37+F238+Calculator!$B$30)</f>
+        <f>IF(A238="","",E238*Calculator!$B$6+Calculator!$C$37+F238+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H238" s="16">
@@ -11215,7 +11231,7 @@
         <v/>
       </c>
       <c r="G239" s="16">
-        <f>IF(A239="","",E239*Calculator!$B$6+Calculator!$B$37+F239+Calculator!$B$30)</f>
+        <f>IF(A239="","",E239*Calculator!$B$6+Calculator!$C$37+F239+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H239" s="16">
@@ -11257,7 +11273,7 @@
         <v/>
       </c>
       <c r="G240" s="16">
-        <f>IF(A240="","",E240*Calculator!$B$6+Calculator!$B$37+F240+Calculator!$B$30)</f>
+        <f>IF(A240="","",E240*Calculator!$B$6+Calculator!$C$37+F240+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H240" s="16">
@@ -11299,7 +11315,7 @@
         <v/>
       </c>
       <c r="G241" s="16">
-        <f>IF(A241="","",E241*Calculator!$B$6+Calculator!$B$37+F241+Calculator!$B$30)</f>
+        <f>IF(A241="","",E241*Calculator!$B$6+Calculator!$C$37+F241+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H241" s="16">
@@ -11341,7 +11357,7 @@
         <v/>
       </c>
       <c r="G242" s="16">
-        <f>IF(A242="","",E242*Calculator!$B$6+Calculator!$B$37+F242+Calculator!$B$30)</f>
+        <f>IF(A242="","",E242*Calculator!$B$6+Calculator!$C$37+F242+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H242" s="16">
@@ -11383,7 +11399,7 @@
         <v/>
       </c>
       <c r="G243" s="16">
-        <f>IF(A243="","",E243*Calculator!$B$6+Calculator!$B$37+F243+Calculator!$B$30)</f>
+        <f>IF(A243="","",E243*Calculator!$B$6+Calculator!$C$37+F243+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H243" s="16">
@@ -11425,7 +11441,7 @@
         <v/>
       </c>
       <c r="G244" s="16">
-        <f>IF(A244="","",E244*Calculator!$B$6+Calculator!$B$37+F244+Calculator!$B$30)</f>
+        <f>IF(A244="","",E244*Calculator!$B$6+Calculator!$C$37+F244+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H244" s="16">
@@ -11467,7 +11483,7 @@
         <v/>
       </c>
       <c r="G245" s="16">
-        <f>IF(A245="","",E245*Calculator!$B$6+Calculator!$B$37+F245+Calculator!$B$30)</f>
+        <f>IF(A245="","",E245*Calculator!$B$6+Calculator!$C$37+F245+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H245" s="16">
@@ -11509,7 +11525,7 @@
         <v/>
       </c>
       <c r="G246" s="16">
-        <f>IF(A246="","",E246*Calculator!$B$6+Calculator!$B$37+F246+Calculator!$B$30)</f>
+        <f>IF(A246="","",E246*Calculator!$B$6+Calculator!$C$37+F246+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H246" s="16">
@@ -11551,7 +11567,7 @@
         <v/>
       </c>
       <c r="G247" s="16">
-        <f>IF(A247="","",E247*Calculator!$B$6+Calculator!$B$37+F247+Calculator!$B$30)</f>
+        <f>IF(A247="","",E247*Calculator!$B$6+Calculator!$C$37+F247+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H247" s="16">
@@ -11593,7 +11609,7 @@
         <v/>
       </c>
       <c r="G248" s="16">
-        <f>IF(A248="","",E248*Calculator!$B$6+Calculator!$B$37+F248+Calculator!$B$30)</f>
+        <f>IF(A248="","",E248*Calculator!$B$6+Calculator!$C$37+F248+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H248" s="16">
@@ -11635,7 +11651,7 @@
         <v/>
       </c>
       <c r="G249" s="16">
-        <f>IF(A249="","",E249*Calculator!$B$6+Calculator!$B$37+F249+Calculator!$B$30)</f>
+        <f>IF(A249="","",E249*Calculator!$B$6+Calculator!$C$37+F249+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H249" s="16">
@@ -11677,7 +11693,7 @@
         <v/>
       </c>
       <c r="G250" s="16">
-        <f>IF(A250="","",E250*Calculator!$B$6+Calculator!$B$37+F250+Calculator!$B$30)</f>
+        <f>IF(A250="","",E250*Calculator!$B$6+Calculator!$C$37+F250+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H250" s="16">
@@ -11719,7 +11735,7 @@
         <v/>
       </c>
       <c r="G251" s="16">
-        <f>IF(A251="","",E251*Calculator!$B$6+Calculator!$B$37+F251+Calculator!$B$30)</f>
+        <f>IF(A251="","",E251*Calculator!$B$6+Calculator!$C$37+F251+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H251" s="16">
@@ -11761,7 +11777,7 @@
         <v/>
       </c>
       <c r="G252" s="16">
-        <f>IF(A252="","",E252*Calculator!$B$6+Calculator!$B$37+F252+Calculator!$B$30)</f>
+        <f>IF(A252="","",E252*Calculator!$B$6+Calculator!$C$37+F252+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H252" s="16">
@@ -11803,7 +11819,7 @@
         <v/>
       </c>
       <c r="G253" s="16">
-        <f>IF(A253="","",E253*Calculator!$B$6+Calculator!$B$37+F253+Calculator!$B$30)</f>
+        <f>IF(A253="","",E253*Calculator!$B$6+Calculator!$C$37+F253+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H253" s="16">
@@ -11845,7 +11861,7 @@
         <v/>
       </c>
       <c r="G254" s="16">
-        <f>IF(A254="","",E254*Calculator!$B$6+Calculator!$B$37+F254+Calculator!$B$30)</f>
+        <f>IF(A254="","",E254*Calculator!$B$6+Calculator!$C$37+F254+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H254" s="16">
@@ -11887,7 +11903,7 @@
         <v/>
       </c>
       <c r="G255" s="16">
-        <f>IF(A255="","",E255*Calculator!$B$6+Calculator!$B$37+F255+Calculator!$B$30)</f>
+        <f>IF(A255="","",E255*Calculator!$B$6+Calculator!$C$37+F255+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H255" s="16">
@@ -11929,7 +11945,7 @@
         <v/>
       </c>
       <c r="G256" s="16">
-        <f>IF(A256="","",E256*Calculator!$B$6+Calculator!$B$37+F256+Calculator!$B$30)</f>
+        <f>IF(A256="","",E256*Calculator!$B$6+Calculator!$C$37+F256+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H256" s="16">
@@ -11971,7 +11987,7 @@
         <v/>
       </c>
       <c r="G257" s="16">
-        <f>IF(A257="","",E257*Calculator!$B$6+Calculator!$B$37+F257+Calculator!$B$30)</f>
+        <f>IF(A257="","",E257*Calculator!$B$6+Calculator!$C$37+F257+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H257" s="16">
@@ -12013,7 +12029,7 @@
         <v/>
       </c>
       <c r="G258" s="16">
-        <f>IF(A258="","",E258*Calculator!$B$6+Calculator!$B$37+F258+Calculator!$B$30)</f>
+        <f>IF(A258="","",E258*Calculator!$B$6+Calculator!$C$37+F258+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H258" s="16">
@@ -12055,7 +12071,7 @@
         <v/>
       </c>
       <c r="G259" s="16">
-        <f>IF(A259="","",E259*Calculator!$B$6+Calculator!$B$37+F259+Calculator!$B$30)</f>
+        <f>IF(A259="","",E259*Calculator!$B$6+Calculator!$C$37+F259+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H259" s="16">
@@ -12097,7 +12113,7 @@
         <v/>
       </c>
       <c r="G260" s="16">
-        <f>IF(A260="","",E260*Calculator!$B$6+Calculator!$B$37+F260+Calculator!$B$30)</f>
+        <f>IF(A260="","",E260*Calculator!$B$6+Calculator!$C$37+F260+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H260" s="16">
@@ -12139,7 +12155,7 @@
         <v/>
       </c>
       <c r="G261" s="16">
-        <f>IF(A261="","",E261*Calculator!$B$6+Calculator!$B$37+F261+Calculator!$B$30)</f>
+        <f>IF(A261="","",E261*Calculator!$B$6+Calculator!$C$37+F261+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H261" s="16">
@@ -12181,7 +12197,7 @@
         <v/>
       </c>
       <c r="G262" s="16">
-        <f>IF(A262="","",E262*Calculator!$B$6+Calculator!$B$37+F262+Calculator!$B$30)</f>
+        <f>IF(A262="","",E262*Calculator!$B$6+Calculator!$C$37+F262+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H262" s="16">
@@ -12223,7 +12239,7 @@
         <v/>
       </c>
       <c r="G263" s="16">
-        <f>IF(A263="","",E263*Calculator!$B$6+Calculator!$B$37+F263+Calculator!$B$30)</f>
+        <f>IF(A263="","",E263*Calculator!$B$6+Calculator!$C$37+F263+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H263" s="16">
@@ -12265,7 +12281,7 @@
         <v/>
       </c>
       <c r="G264" s="16">
-        <f>IF(A264="","",E264*Calculator!$B$6+Calculator!$B$37+F264+Calculator!$B$30)</f>
+        <f>IF(A264="","",E264*Calculator!$B$6+Calculator!$C$37+F264+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H264" s="16">
@@ -12307,7 +12323,7 @@
         <v/>
       </c>
       <c r="G265" s="16">
-        <f>IF(A265="","",E265*Calculator!$B$6+Calculator!$B$37+F265+Calculator!$B$30)</f>
+        <f>IF(A265="","",E265*Calculator!$B$6+Calculator!$C$37+F265+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H265" s="16">
@@ -12349,7 +12365,7 @@
         <v/>
       </c>
       <c r="G266" s="16">
-        <f>IF(A266="","",E266*Calculator!$B$6+Calculator!$B$37+F266+Calculator!$B$30)</f>
+        <f>IF(A266="","",E266*Calculator!$B$6+Calculator!$C$37+F266+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H266" s="16">
@@ -12391,7 +12407,7 @@
         <v/>
       </c>
       <c r="G267" s="16">
-        <f>IF(A267="","",E267*Calculator!$B$6+Calculator!$B$37+F267+Calculator!$B$30)</f>
+        <f>IF(A267="","",E267*Calculator!$B$6+Calculator!$C$37+F267+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H267" s="16">
@@ -12433,7 +12449,7 @@
         <v/>
       </c>
       <c r="G268" s="16">
-        <f>IF(A268="","",E268*Calculator!$B$6+Calculator!$B$37+F268+Calculator!$B$30)</f>
+        <f>IF(A268="","",E268*Calculator!$B$6+Calculator!$C$37+F268+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H268" s="16">
@@ -12475,7 +12491,7 @@
         <v/>
       </c>
       <c r="G269" s="16">
-        <f>IF(A269="","",E269*Calculator!$B$6+Calculator!$B$37+F269+Calculator!$B$30)</f>
+        <f>IF(A269="","",E269*Calculator!$B$6+Calculator!$C$37+F269+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H269" s="16">
@@ -12517,7 +12533,7 @@
         <v/>
       </c>
       <c r="G270" s="16">
-        <f>IF(A270="","",E270*Calculator!$B$6+Calculator!$B$37+F270+Calculator!$B$30)</f>
+        <f>IF(A270="","",E270*Calculator!$B$6+Calculator!$C$37+F270+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H270" s="16">
@@ -12559,7 +12575,7 @@
         <v/>
       </c>
       <c r="G271" s="16">
-        <f>IF(A271="","",E271*Calculator!$B$6+Calculator!$B$37+F271+Calculator!$B$30)</f>
+        <f>IF(A271="","",E271*Calculator!$B$6+Calculator!$C$37+F271+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H271" s="16">
@@ -12601,7 +12617,7 @@
         <v/>
       </c>
       <c r="G272" s="16">
-        <f>IF(A272="","",E272*Calculator!$B$6+Calculator!$B$37+F272+Calculator!$B$30)</f>
+        <f>IF(A272="","",E272*Calculator!$B$6+Calculator!$C$37+F272+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H272" s="16">
@@ -12643,7 +12659,7 @@
         <v/>
       </c>
       <c r="G273" s="16">
-        <f>IF(A273="","",E273*Calculator!$B$6+Calculator!$B$37+F273+Calculator!$B$30)</f>
+        <f>IF(A273="","",E273*Calculator!$B$6+Calculator!$C$37+F273+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H273" s="16">
@@ -12685,7 +12701,7 @@
         <v/>
       </c>
       <c r="G274" s="16">
-        <f>IF(A274="","",E274*Calculator!$B$6+Calculator!$B$37+F274+Calculator!$B$30)</f>
+        <f>IF(A274="","",E274*Calculator!$B$6+Calculator!$C$37+F274+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H274" s="16">
@@ -12727,7 +12743,7 @@
         <v/>
       </c>
       <c r="G275" s="16">
-        <f>IF(A275="","",E275*Calculator!$B$6+Calculator!$B$37+F275+Calculator!$B$30)</f>
+        <f>IF(A275="","",E275*Calculator!$B$6+Calculator!$C$37+F275+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H275" s="16">
@@ -12769,7 +12785,7 @@
         <v/>
       </c>
       <c r="G276" s="16">
-        <f>IF(A276="","",E276*Calculator!$B$6+Calculator!$B$37+F276+Calculator!$B$30)</f>
+        <f>IF(A276="","",E276*Calculator!$B$6+Calculator!$C$37+F276+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H276" s="16">
@@ -12811,7 +12827,7 @@
         <v/>
       </c>
       <c r="G277" s="16">
-        <f>IF(A277="","",E277*Calculator!$B$6+Calculator!$B$37+F277+Calculator!$B$30)</f>
+        <f>IF(A277="","",E277*Calculator!$B$6+Calculator!$C$37+F277+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H277" s="16">
@@ -12853,7 +12869,7 @@
         <v/>
       </c>
       <c r="G278" s="16">
-        <f>IF(A278="","",E278*Calculator!$B$6+Calculator!$B$37+F278+Calculator!$B$30)</f>
+        <f>IF(A278="","",E278*Calculator!$B$6+Calculator!$C$37+F278+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H278" s="16">
@@ -12895,7 +12911,7 @@
         <v/>
       </c>
       <c r="G279" s="16">
-        <f>IF(A279="","",E279*Calculator!$B$6+Calculator!$B$37+F279+Calculator!$B$30)</f>
+        <f>IF(A279="","",E279*Calculator!$B$6+Calculator!$C$37+F279+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H279" s="16">
@@ -12937,7 +12953,7 @@
         <v/>
       </c>
       <c r="G280" s="16">
-        <f>IF(A280="","",E280*Calculator!$B$6+Calculator!$B$37+F280+Calculator!$B$30)</f>
+        <f>IF(A280="","",E280*Calculator!$B$6+Calculator!$C$37+F280+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H280" s="16">
@@ -12979,7 +12995,7 @@
         <v/>
       </c>
       <c r="G281" s="16">
-        <f>IF(A281="","",E281*Calculator!$B$6+Calculator!$B$37+F281+Calculator!$B$30)</f>
+        <f>IF(A281="","",E281*Calculator!$B$6+Calculator!$C$37+F281+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H281" s="16">
@@ -13021,7 +13037,7 @@
         <v/>
       </c>
       <c r="G282" s="16">
-        <f>IF(A282="","",E282*Calculator!$B$6+Calculator!$B$37+F282+Calculator!$B$30)</f>
+        <f>IF(A282="","",E282*Calculator!$B$6+Calculator!$C$37+F282+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H282" s="16">
@@ -13063,7 +13079,7 @@
         <v/>
       </c>
       <c r="G283" s="16">
-        <f>IF(A283="","",E283*Calculator!$B$6+Calculator!$B$37+F283+Calculator!$B$30)</f>
+        <f>IF(A283="","",E283*Calculator!$B$6+Calculator!$C$37+F283+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H283" s="16">
@@ -13105,7 +13121,7 @@
         <v/>
       </c>
       <c r="G284" s="16">
-        <f>IF(A284="","",E284*Calculator!$B$6+Calculator!$B$37+F284+Calculator!$B$30)</f>
+        <f>IF(A284="","",E284*Calculator!$B$6+Calculator!$C$37+F284+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H284" s="16">
@@ -13147,7 +13163,7 @@
         <v/>
       </c>
       <c r="G285" s="16">
-        <f>IF(A285="","",E285*Calculator!$B$6+Calculator!$B$37+F285+Calculator!$B$30)</f>
+        <f>IF(A285="","",E285*Calculator!$B$6+Calculator!$C$37+F285+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H285" s="16">
@@ -13189,7 +13205,7 @@
         <v/>
       </c>
       <c r="G286" s="16">
-        <f>IF(A286="","",E286*Calculator!$B$6+Calculator!$B$37+F286+Calculator!$B$30)</f>
+        <f>IF(A286="","",E286*Calculator!$B$6+Calculator!$C$37+F286+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H286" s="16">
@@ -13231,7 +13247,7 @@
         <v/>
       </c>
       <c r="G287" s="16">
-        <f>IF(A287="","",E287*Calculator!$B$6+Calculator!$B$37+F287+Calculator!$B$30)</f>
+        <f>IF(A287="","",E287*Calculator!$B$6+Calculator!$C$37+F287+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H287" s="16">
@@ -13273,7 +13289,7 @@
         <v/>
       </c>
       <c r="G288" s="16">
-        <f>IF(A288="","",E288*Calculator!$B$6+Calculator!$B$37+F288+Calculator!$B$30)</f>
+        <f>IF(A288="","",E288*Calculator!$B$6+Calculator!$C$37+F288+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H288" s="16">
@@ -13315,7 +13331,7 @@
         <v/>
       </c>
       <c r="G289" s="16">
-        <f>IF(A289="","",E289*Calculator!$B$6+Calculator!$B$37+F289+Calculator!$B$30)</f>
+        <f>IF(A289="","",E289*Calculator!$B$6+Calculator!$C$37+F289+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H289" s="16">
@@ -13357,7 +13373,7 @@
         <v/>
       </c>
       <c r="G290" s="16">
-        <f>IF(A290="","",E290*Calculator!$B$6+Calculator!$B$37+F290+Calculator!$B$30)</f>
+        <f>IF(A290="","",E290*Calculator!$B$6+Calculator!$C$37+F290+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H290" s="16">
@@ -13399,7 +13415,7 @@
         <v/>
       </c>
       <c r="G291" s="16">
-        <f>IF(A291="","",E291*Calculator!$B$6+Calculator!$B$37+F291+Calculator!$B$30)</f>
+        <f>IF(A291="","",E291*Calculator!$B$6+Calculator!$C$37+F291+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H291" s="16">
@@ -13441,7 +13457,7 @@
         <v/>
       </c>
       <c r="G292" s="16">
-        <f>IF(A292="","",E292*Calculator!$B$6+Calculator!$B$37+F292+Calculator!$B$30)</f>
+        <f>IF(A292="","",E292*Calculator!$B$6+Calculator!$C$37+F292+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H292" s="16">
@@ -13483,7 +13499,7 @@
         <v/>
       </c>
       <c r="G293" s="16">
-        <f>IF(A293="","",E293*Calculator!$B$6+Calculator!$B$37+F293+Calculator!$B$30)</f>
+        <f>IF(A293="","",E293*Calculator!$B$6+Calculator!$C$37+F293+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H293" s="16">
@@ -13525,7 +13541,7 @@
         <v/>
       </c>
       <c r="G294" s="16">
-        <f>IF(A294="","",E294*Calculator!$B$6+Calculator!$B$37+F294+Calculator!$B$30)</f>
+        <f>IF(A294="","",E294*Calculator!$B$6+Calculator!$C$37+F294+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H294" s="16">
@@ -13567,7 +13583,7 @@
         <v/>
       </c>
       <c r="G295" s="16">
-        <f>IF(A295="","",E295*Calculator!$B$6+Calculator!$B$37+F295+Calculator!$B$30)</f>
+        <f>IF(A295="","",E295*Calculator!$B$6+Calculator!$C$37+F295+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H295" s="16">
@@ -13609,7 +13625,7 @@
         <v/>
       </c>
       <c r="G296" s="16">
-        <f>IF(A296="","",E296*Calculator!$B$6+Calculator!$B$37+F296+Calculator!$B$30)</f>
+        <f>IF(A296="","",E296*Calculator!$B$6+Calculator!$C$37+F296+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H296" s="16">
@@ -13651,7 +13667,7 @@
         <v/>
       </c>
       <c r="G297" s="16">
-        <f>IF(A297="","",E297*Calculator!$B$6+Calculator!$B$37+F297+Calculator!$B$30)</f>
+        <f>IF(A297="","",E297*Calculator!$B$6+Calculator!$C$37+F297+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H297" s="16">
@@ -13693,7 +13709,7 @@
         <v/>
       </c>
       <c r="G298" s="16">
-        <f>IF(A298="","",E298*Calculator!$B$6+Calculator!$B$37+F298+Calculator!$B$30)</f>
+        <f>IF(A298="","",E298*Calculator!$B$6+Calculator!$C$37+F298+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H298" s="16">
@@ -13735,7 +13751,7 @@
         <v/>
       </c>
       <c r="G299" s="16">
-        <f>IF(A299="","",E299*Calculator!$B$6+Calculator!$B$37+F299+Calculator!$B$30)</f>
+        <f>IF(A299="","",E299*Calculator!$B$6+Calculator!$C$37+F299+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H299" s="16">
@@ -13777,7 +13793,7 @@
         <v/>
       </c>
       <c r="G300" s="16">
-        <f>IF(A300="","",E300*Calculator!$B$6+Calculator!$B$37+F300+Calculator!$B$30)</f>
+        <f>IF(A300="","",E300*Calculator!$B$6+Calculator!$C$37+F300+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H300" s="16">
@@ -13819,7 +13835,7 @@
         <v/>
       </c>
       <c r="G301" s="16">
-        <f>IF(A301="","",E301*Calculator!$B$6+Calculator!$B$37+F301+Calculator!$B$30)</f>
+        <f>IF(A301="","",E301*Calculator!$B$6+Calculator!$C$37+F301+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H301" s="16">
@@ -13861,7 +13877,7 @@
         <v/>
       </c>
       <c r="G302" s="16">
-        <f>IF(A302="","",E302*Calculator!$B$6+Calculator!$B$37+F302+Calculator!$B$30)</f>
+        <f>IF(A302="","",E302*Calculator!$B$6+Calculator!$C$37+F302+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H302" s="16">
@@ -13903,7 +13919,7 @@
         <v/>
       </c>
       <c r="G303" s="16">
-        <f>IF(A303="","",E303*Calculator!$B$6+Calculator!$B$37+F303+Calculator!$B$30)</f>
+        <f>IF(A303="","",E303*Calculator!$B$6+Calculator!$C$37+F303+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H303" s="16">
@@ -13945,7 +13961,7 @@
         <v/>
       </c>
       <c r="G304" s="16">
-        <f>IF(A304="","",E304*Calculator!$B$6+Calculator!$B$37+F304+Calculator!$B$30)</f>
+        <f>IF(A304="","",E304*Calculator!$B$6+Calculator!$C$37+F304+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H304" s="16">
@@ -13987,7 +14003,7 @@
         <v/>
       </c>
       <c r="G305" s="16">
-        <f>IF(A305="","",E305*Calculator!$B$6+Calculator!$B$37+F305+Calculator!$B$30)</f>
+        <f>IF(A305="","",E305*Calculator!$B$6+Calculator!$C$37+F305+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H305" s="16">
@@ -14029,7 +14045,7 @@
         <v/>
       </c>
       <c r="G306" s="16">
-        <f>IF(A306="","",E306*Calculator!$B$6+Calculator!$B$37+F306+Calculator!$B$30)</f>
+        <f>IF(A306="","",E306*Calculator!$B$6+Calculator!$C$37+F306+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H306" s="16">
@@ -14071,7 +14087,7 @@
         <v/>
       </c>
       <c r="G307" s="16">
-        <f>IF(A307="","",E307*Calculator!$B$6+Calculator!$B$37+F307+Calculator!$B$30)</f>
+        <f>IF(A307="","",E307*Calculator!$B$6+Calculator!$C$37+F307+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H307" s="16">
@@ -14113,7 +14129,7 @@
         <v/>
       </c>
       <c r="G308" s="16">
-        <f>IF(A308="","",E308*Calculator!$B$6+Calculator!$B$37+F308+Calculator!$B$30)</f>
+        <f>IF(A308="","",E308*Calculator!$B$6+Calculator!$C$37+F308+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H308" s="16">
@@ -14155,7 +14171,7 @@
         <v/>
       </c>
       <c r="G309" s="16">
-        <f>IF(A309="","",E309*Calculator!$B$6+Calculator!$B$37+F309+Calculator!$B$30)</f>
+        <f>IF(A309="","",E309*Calculator!$B$6+Calculator!$C$37+F309+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H309" s="16">
@@ -14197,7 +14213,7 @@
         <v/>
       </c>
       <c r="G310" s="16">
-        <f>IF(A310="","",E310*Calculator!$B$6+Calculator!$B$37+F310+Calculator!$B$30)</f>
+        <f>IF(A310="","",E310*Calculator!$B$6+Calculator!$C$37+F310+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H310" s="16">
@@ -14239,7 +14255,7 @@
         <v/>
       </c>
       <c r="G311" s="16">
-        <f>IF(A311="","",E311*Calculator!$B$6+Calculator!$B$37+F311+Calculator!$B$30)</f>
+        <f>IF(A311="","",E311*Calculator!$B$6+Calculator!$C$37+F311+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H311" s="16">
@@ -14281,7 +14297,7 @@
         <v/>
       </c>
       <c r="G312" s="16">
-        <f>IF(A312="","",E312*Calculator!$B$6+Calculator!$B$37+F312+Calculator!$B$30)</f>
+        <f>IF(A312="","",E312*Calculator!$B$6+Calculator!$C$37+F312+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H312" s="16">
@@ -14323,7 +14339,7 @@
         <v/>
       </c>
       <c r="G313" s="16">
-        <f>IF(A313="","",E313*Calculator!$B$6+Calculator!$B$37+F313+Calculator!$B$30)</f>
+        <f>IF(A313="","",E313*Calculator!$B$6+Calculator!$C$37+F313+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H313" s="16">
@@ -14365,7 +14381,7 @@
         <v/>
       </c>
       <c r="G314" s="16">
-        <f>IF(A314="","",E314*Calculator!$B$6+Calculator!$B$37+F314+Calculator!$B$30)</f>
+        <f>IF(A314="","",E314*Calculator!$B$6+Calculator!$C$37+F314+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H314" s="16">
@@ -14407,7 +14423,7 @@
         <v/>
       </c>
       <c r="G315" s="16">
-        <f>IF(A315="","",E315*Calculator!$B$6+Calculator!$B$37+F315+Calculator!$B$30)</f>
+        <f>IF(A315="","",E315*Calculator!$B$6+Calculator!$C$37+F315+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H315" s="16">
@@ -14449,7 +14465,7 @@
         <v/>
       </c>
       <c r="G316" s="16">
-        <f>IF(A316="","",E316*Calculator!$B$6+Calculator!$B$37+F316+Calculator!$B$30)</f>
+        <f>IF(A316="","",E316*Calculator!$B$6+Calculator!$C$37+F316+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H316" s="16">
@@ -14491,7 +14507,7 @@
         <v/>
       </c>
       <c r="G317" s="16">
-        <f>IF(A317="","",E317*Calculator!$B$6+Calculator!$B$37+F317+Calculator!$B$30)</f>
+        <f>IF(A317="","",E317*Calculator!$B$6+Calculator!$C$37+F317+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H317" s="16">
@@ -14533,7 +14549,7 @@
         <v/>
       </c>
       <c r="G318" s="16">
-        <f>IF(A318="","",E318*Calculator!$B$6+Calculator!$B$37+F318+Calculator!$B$30)</f>
+        <f>IF(A318="","",E318*Calculator!$B$6+Calculator!$C$37+F318+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H318" s="16">
@@ -14575,7 +14591,7 @@
         <v/>
       </c>
       <c r="G319" s="16">
-        <f>IF(A319="","",E319*Calculator!$B$6+Calculator!$B$37+F319+Calculator!$B$30)</f>
+        <f>IF(A319="","",E319*Calculator!$B$6+Calculator!$C$37+F319+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H319" s="16">
@@ -14617,7 +14633,7 @@
         <v/>
       </c>
       <c r="G320" s="16">
-        <f>IF(A320="","",E320*Calculator!$B$6+Calculator!$B$37+F320+Calculator!$B$30)</f>
+        <f>IF(A320="","",E320*Calculator!$B$6+Calculator!$C$37+F320+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H320" s="16">
@@ -14659,7 +14675,7 @@
         <v/>
       </c>
       <c r="G321" s="16">
-        <f>IF(A321="","",E321*Calculator!$B$6+Calculator!$B$37+F321+Calculator!$B$30)</f>
+        <f>IF(A321="","",E321*Calculator!$B$6+Calculator!$C$37+F321+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H321" s="16">
@@ -14701,7 +14717,7 @@
         <v/>
       </c>
       <c r="G322" s="16">
-        <f>IF(A322="","",E322*Calculator!$B$6+Calculator!$B$37+F322+Calculator!$B$30)</f>
+        <f>IF(A322="","",E322*Calculator!$B$6+Calculator!$C$37+F322+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H322" s="16">
@@ -14743,7 +14759,7 @@
         <v/>
       </c>
       <c r="G323" s="16">
-        <f>IF(A323="","",E323*Calculator!$B$6+Calculator!$B$37+F323+Calculator!$B$30)</f>
+        <f>IF(A323="","",E323*Calculator!$B$6+Calculator!$C$37+F323+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H323" s="16">
@@ -14785,7 +14801,7 @@
         <v/>
       </c>
       <c r="G324" s="16">
-        <f>IF(A324="","",E324*Calculator!$B$6+Calculator!$B$37+F324+Calculator!$B$30)</f>
+        <f>IF(A324="","",E324*Calculator!$B$6+Calculator!$C$37+F324+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H324" s="16">
@@ -14827,7 +14843,7 @@
         <v/>
       </c>
       <c r="G325" s="16">
-        <f>IF(A325="","",E325*Calculator!$B$6+Calculator!$B$37+F325+Calculator!$B$30)</f>
+        <f>IF(A325="","",E325*Calculator!$B$6+Calculator!$C$37+F325+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H325" s="16">
@@ -14869,7 +14885,7 @@
         <v/>
       </c>
       <c r="G326" s="16">
-        <f>IF(A326="","",E326*Calculator!$B$6+Calculator!$B$37+F326+Calculator!$B$30)</f>
+        <f>IF(A326="","",E326*Calculator!$B$6+Calculator!$C$37+F326+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H326" s="16">
@@ -14911,7 +14927,7 @@
         <v/>
       </c>
       <c r="G327" s="16">
-        <f>IF(A327="","",E327*Calculator!$B$6+Calculator!$B$37+F327+Calculator!$B$30)</f>
+        <f>IF(A327="","",E327*Calculator!$B$6+Calculator!$C$37+F327+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H327" s="16">
@@ -14953,7 +14969,7 @@
         <v/>
       </c>
       <c r="G328" s="16">
-        <f>IF(A328="","",E328*Calculator!$B$6+Calculator!$B$37+F328+Calculator!$B$30)</f>
+        <f>IF(A328="","",E328*Calculator!$B$6+Calculator!$C$37+F328+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H328" s="16">
@@ -14995,7 +15011,7 @@
         <v/>
       </c>
       <c r="G329" s="16">
-        <f>IF(A329="","",E329*Calculator!$B$6+Calculator!$B$37+F329+Calculator!$B$30)</f>
+        <f>IF(A329="","",E329*Calculator!$B$6+Calculator!$C$37+F329+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H329" s="16">
@@ -15037,7 +15053,7 @@
         <v/>
       </c>
       <c r="G330" s="16">
-        <f>IF(A330="","",E330*Calculator!$B$6+Calculator!$B$37+F330+Calculator!$B$30)</f>
+        <f>IF(A330="","",E330*Calculator!$B$6+Calculator!$C$37+F330+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H330" s="16">
@@ -15079,7 +15095,7 @@
         <v/>
       </c>
       <c r="G331" s="16">
-        <f>IF(A331="","",E331*Calculator!$B$6+Calculator!$B$37+F331+Calculator!$B$30)</f>
+        <f>IF(A331="","",E331*Calculator!$B$6+Calculator!$C$37+F331+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H331" s="16">
@@ -15121,7 +15137,7 @@
         <v/>
       </c>
       <c r="G332" s="16">
-        <f>IF(A332="","",E332*Calculator!$B$6+Calculator!$B$37+F332+Calculator!$B$30)</f>
+        <f>IF(A332="","",E332*Calculator!$B$6+Calculator!$C$37+F332+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H332" s="16">
@@ -15163,7 +15179,7 @@
         <v/>
       </c>
       <c r="G333" s="16">
-        <f>IF(A333="","",E333*Calculator!$B$6+Calculator!$B$37+F333+Calculator!$B$30)</f>
+        <f>IF(A333="","",E333*Calculator!$B$6+Calculator!$C$37+F333+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H333" s="16">
@@ -15205,7 +15221,7 @@
         <v/>
       </c>
       <c r="G334" s="16">
-        <f>IF(A334="","",E334*Calculator!$B$6+Calculator!$B$37+F334+Calculator!$B$30)</f>
+        <f>IF(A334="","",E334*Calculator!$B$6+Calculator!$C$37+F334+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H334" s="16">
@@ -15247,7 +15263,7 @@
         <v/>
       </c>
       <c r="G335" s="16">
-        <f>IF(A335="","",E335*Calculator!$B$6+Calculator!$B$37+F335+Calculator!$B$30)</f>
+        <f>IF(A335="","",E335*Calculator!$B$6+Calculator!$C$37+F335+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H335" s="16">
@@ -15289,7 +15305,7 @@
         <v/>
       </c>
       <c r="G336" s="16">
-        <f>IF(A336="","",E336*Calculator!$B$6+Calculator!$B$37+F336+Calculator!$B$30)</f>
+        <f>IF(A336="","",E336*Calculator!$B$6+Calculator!$C$37+F336+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H336" s="16">
@@ -15331,7 +15347,7 @@
         <v/>
       </c>
       <c r="G337" s="16">
-        <f>IF(A337="","",E337*Calculator!$B$6+Calculator!$B$37+F337+Calculator!$B$30)</f>
+        <f>IF(A337="","",E337*Calculator!$B$6+Calculator!$C$37+F337+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H337" s="16">
@@ -15373,7 +15389,7 @@
         <v/>
       </c>
       <c r="G338" s="16">
-        <f>IF(A338="","",E338*Calculator!$B$6+Calculator!$B$37+F338+Calculator!$B$30)</f>
+        <f>IF(A338="","",E338*Calculator!$B$6+Calculator!$C$37+F338+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H338" s="16">
@@ -15415,7 +15431,7 @@
         <v/>
       </c>
       <c r="G339" s="16">
-        <f>IF(A339="","",E339*Calculator!$B$6+Calculator!$B$37+F339+Calculator!$B$30)</f>
+        <f>IF(A339="","",E339*Calculator!$B$6+Calculator!$C$37+F339+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H339" s="16">
@@ -15457,7 +15473,7 @@
         <v/>
       </c>
       <c r="G340" s="16">
-        <f>IF(A340="","",E340*Calculator!$B$6+Calculator!$B$37+F340+Calculator!$B$30)</f>
+        <f>IF(A340="","",E340*Calculator!$B$6+Calculator!$C$37+F340+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H340" s="16">
@@ -15499,7 +15515,7 @@
         <v/>
       </c>
       <c r="G341" s="16">
-        <f>IF(A341="","",E341*Calculator!$B$6+Calculator!$B$37+F341+Calculator!$B$30)</f>
+        <f>IF(A341="","",E341*Calculator!$B$6+Calculator!$C$37+F341+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H341" s="16">
@@ -15541,7 +15557,7 @@
         <v/>
       </c>
       <c r="G342" s="16">
-        <f>IF(A342="","",E342*Calculator!$B$6+Calculator!$B$37+F342+Calculator!$B$30)</f>
+        <f>IF(A342="","",E342*Calculator!$B$6+Calculator!$C$37+F342+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H342" s="16">
@@ -15583,7 +15599,7 @@
         <v/>
       </c>
       <c r="G343" s="16">
-        <f>IF(A343="","",E343*Calculator!$B$6+Calculator!$B$37+F343+Calculator!$B$30)</f>
+        <f>IF(A343="","",E343*Calculator!$B$6+Calculator!$C$37+F343+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H343" s="16">
@@ -15625,7 +15641,7 @@
         <v/>
       </c>
       <c r="G344" s="16">
-        <f>IF(A344="","",E344*Calculator!$B$6+Calculator!$B$37+F344+Calculator!$B$30)</f>
+        <f>IF(A344="","",E344*Calculator!$B$6+Calculator!$C$37+F344+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H344" s="16">
@@ -15667,7 +15683,7 @@
         <v/>
       </c>
       <c r="G345" s="16">
-        <f>IF(A345="","",E345*Calculator!$B$6+Calculator!$B$37+F345+Calculator!$B$30)</f>
+        <f>IF(A345="","",E345*Calculator!$B$6+Calculator!$C$37+F345+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H345" s="16">
@@ -15709,7 +15725,7 @@
         <v/>
       </c>
       <c r="G346" s="16">
-        <f>IF(A346="","",E346*Calculator!$B$6+Calculator!$B$37+F346+Calculator!$B$30)</f>
+        <f>IF(A346="","",E346*Calculator!$B$6+Calculator!$C$37+F346+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H346" s="16">
@@ -15751,7 +15767,7 @@
         <v/>
       </c>
       <c r="G347" s="16">
-        <f>IF(A347="","",E347*Calculator!$B$6+Calculator!$B$37+F347+Calculator!$B$30)</f>
+        <f>IF(A347="","",E347*Calculator!$B$6+Calculator!$C$37+F347+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H347" s="16">
@@ -15793,7 +15809,7 @@
         <v/>
       </c>
       <c r="G348" s="16">
-        <f>IF(A348="","",E348*Calculator!$B$6+Calculator!$B$37+F348+Calculator!$B$30)</f>
+        <f>IF(A348="","",E348*Calculator!$B$6+Calculator!$C$37+F348+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H348" s="16">
@@ -15835,7 +15851,7 @@
         <v/>
       </c>
       <c r="G349" s="16">
-        <f>IF(A349="","",E349*Calculator!$B$6+Calculator!$B$37+F349+Calculator!$B$30)</f>
+        <f>IF(A349="","",E349*Calculator!$B$6+Calculator!$C$37+F349+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H349" s="16">
@@ -15877,7 +15893,7 @@
         <v/>
       </c>
       <c r="G350" s="16">
-        <f>IF(A350="","",E350*Calculator!$B$6+Calculator!$B$37+F350+Calculator!$B$30)</f>
+        <f>IF(A350="","",E350*Calculator!$B$6+Calculator!$C$37+F350+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H350" s="16">
@@ -15919,7 +15935,7 @@
         <v/>
       </c>
       <c r="G351" s="16">
-        <f>IF(A351="","",E351*Calculator!$B$6+Calculator!$B$37+F351+Calculator!$B$30)</f>
+        <f>IF(A351="","",E351*Calculator!$B$6+Calculator!$C$37+F351+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H351" s="16">
@@ -15961,7 +15977,7 @@
         <v/>
       </c>
       <c r="G352" s="16">
-        <f>IF(A352="","",E352*Calculator!$B$6+Calculator!$B$37+F352+Calculator!$B$30)</f>
+        <f>IF(A352="","",E352*Calculator!$B$6+Calculator!$C$37+F352+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H352" s="16">
@@ -16003,7 +16019,7 @@
         <v/>
       </c>
       <c r="G353" s="16">
-        <f>IF(A353="","",E353*Calculator!$B$6+Calculator!$B$37+F353+Calculator!$B$30)</f>
+        <f>IF(A353="","",E353*Calculator!$B$6+Calculator!$C$37+F353+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H353" s="16">
@@ -16045,7 +16061,7 @@
         <v/>
       </c>
       <c r="G354" s="16">
-        <f>IF(A354="","",E354*Calculator!$B$6+Calculator!$B$37+F354+Calculator!$B$30)</f>
+        <f>IF(A354="","",E354*Calculator!$B$6+Calculator!$C$37+F354+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H354" s="16">
@@ -16087,7 +16103,7 @@
         <v/>
       </c>
       <c r="G355" s="16">
-        <f>IF(A355="","",E355*Calculator!$B$6+Calculator!$B$37+F355+Calculator!$B$30)</f>
+        <f>IF(A355="","",E355*Calculator!$B$6+Calculator!$C$37+F355+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H355" s="16">
@@ -16129,7 +16145,7 @@
         <v/>
       </c>
       <c r="G356" s="16">
-        <f>IF(A356="","",E356*Calculator!$B$6+Calculator!$B$37+F356+Calculator!$B$30)</f>
+        <f>IF(A356="","",E356*Calculator!$B$6+Calculator!$C$37+F356+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H356" s="16">
@@ -16171,7 +16187,7 @@
         <v/>
       </c>
       <c r="G357" s="16">
-        <f>IF(A357="","",E357*Calculator!$B$6+Calculator!$B$37+F357+Calculator!$B$30)</f>
+        <f>IF(A357="","",E357*Calculator!$B$6+Calculator!$C$37+F357+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H357" s="16">
@@ -16213,7 +16229,7 @@
         <v/>
       </c>
       <c r="G358" s="16">
-        <f>IF(A358="","",E358*Calculator!$B$6+Calculator!$B$37+F358+Calculator!$B$30)</f>
+        <f>IF(A358="","",E358*Calculator!$B$6+Calculator!$C$37+F358+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H358" s="16">
@@ -16255,7 +16271,7 @@
         <v/>
       </c>
       <c r="G359" s="16">
-        <f>IF(A359="","",E359*Calculator!$B$6+Calculator!$B$37+F359+Calculator!$B$30)</f>
+        <f>IF(A359="","",E359*Calculator!$B$6+Calculator!$C$37+F359+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H359" s="16">
@@ -16297,7 +16313,7 @@
         <v/>
       </c>
       <c r="G360" s="16">
-        <f>IF(A360="","",E360*Calculator!$B$6+Calculator!$B$37+F360+Calculator!$B$30)</f>
+        <f>IF(A360="","",E360*Calculator!$B$6+Calculator!$C$37+F360+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H360" s="16">
@@ -16339,7 +16355,7 @@
         <v/>
       </c>
       <c r="G361" s="16">
-        <f>IF(A361="","",E361*Calculator!$B$6+Calculator!$B$37+F361+Calculator!$B$30)</f>
+        <f>IF(A361="","",E361*Calculator!$B$6+Calculator!$C$37+F361+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H361" s="16">
@@ -16381,7 +16397,7 @@
         <v/>
       </c>
       <c r="G362" s="16">
-        <f>IF(A362="","",E362*Calculator!$B$6+Calculator!$B$37+F362+Calculator!$B$30)</f>
+        <f>IF(A362="","",E362*Calculator!$B$6+Calculator!$C$37+F362+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H362" s="16">
@@ -16423,7 +16439,7 @@
         <v/>
       </c>
       <c r="G363" s="16">
-        <f>IF(A363="","",E363*Calculator!$B$6+Calculator!$B$37+F363+Calculator!$B$30)</f>
+        <f>IF(A363="","",E363*Calculator!$B$6+Calculator!$C$37+F363+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H363" s="16">
@@ -16465,7 +16481,7 @@
         <v/>
       </c>
       <c r="G364" s="16">
-        <f>IF(A364="","",E364*Calculator!$B$6+Calculator!$B$37+F364+Calculator!$B$30)</f>
+        <f>IF(A364="","",E364*Calculator!$B$6+Calculator!$C$37+F364+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H364" s="16">
@@ -16507,7 +16523,7 @@
         <v/>
       </c>
       <c r="G365" s="16">
-        <f>IF(A365="","",E365*Calculator!$B$6+Calculator!$B$37+F365+Calculator!$B$30)</f>
+        <f>IF(A365="","",E365*Calculator!$B$6+Calculator!$C$37+F365+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H365" s="16">
@@ -16549,7 +16565,7 @@
         <v/>
       </c>
       <c r="G366" s="16">
-        <f>IF(A366="","",E366*Calculator!$B$6+Calculator!$B$37+F366+Calculator!$B$30)</f>
+        <f>IF(A366="","",E366*Calculator!$B$6+Calculator!$C$37+F366+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H366" s="16">
@@ -16591,7 +16607,7 @@
         <v/>
       </c>
       <c r="G367" s="16">
-        <f>IF(A367="","",E367*Calculator!$B$6+Calculator!$B$37+F367+Calculator!$B$30)</f>
+        <f>IF(A367="","",E367*Calculator!$B$6+Calculator!$C$37+F367+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H367" s="16">
@@ -16633,7 +16649,7 @@
         <v/>
       </c>
       <c r="G368" s="16">
-        <f>IF(A368="","",E368*Calculator!$B$6+Calculator!$B$37+F368+Calculator!$B$30)</f>
+        <f>IF(A368="","",E368*Calculator!$B$6+Calculator!$C$37+F368+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H368" s="16">
@@ -16675,7 +16691,7 @@
         <v/>
       </c>
       <c r="G369" s="16">
-        <f>IF(A369="","",E369*Calculator!$B$6+Calculator!$B$37+F369+Calculator!$B$30)</f>
+        <f>IF(A369="","",E369*Calculator!$B$6+Calculator!$C$37+F369+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H369" s="16">
@@ -16717,7 +16733,7 @@
         <v/>
       </c>
       <c r="G370" s="16">
-        <f>IF(A370="","",E370*Calculator!$B$6+Calculator!$B$37+F370+Calculator!$B$30)</f>
+        <f>IF(A370="","",E370*Calculator!$B$6+Calculator!$C$37+F370+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H370" s="16">
@@ -16759,7 +16775,7 @@
         <v/>
       </c>
       <c r="G371" s="16">
-        <f>IF(A371="","",E371*Calculator!$B$6+Calculator!$B$37+F371+Calculator!$B$30)</f>
+        <f>IF(A371="","",E371*Calculator!$B$6+Calculator!$C$37+F371+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H371" s="16">
@@ -16801,7 +16817,7 @@
         <v/>
       </c>
       <c r="G372" s="16">
-        <f>IF(A372="","",E372*Calculator!$B$6+Calculator!$B$37+F372+Calculator!$B$30)</f>
+        <f>IF(A372="","",E372*Calculator!$B$6+Calculator!$C$37+F372+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H372" s="16">
@@ -16843,7 +16859,7 @@
         <v/>
       </c>
       <c r="G373" s="16">
-        <f>IF(A373="","",E373*Calculator!$B$6+Calculator!$B$37+F373+Calculator!$B$30)</f>
+        <f>IF(A373="","",E373*Calculator!$B$6+Calculator!$C$37+F373+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H373" s="16">
@@ -16885,7 +16901,7 @@
         <v/>
       </c>
       <c r="G374" s="16">
-        <f>IF(A374="","",E374*Calculator!$B$6+Calculator!$B$37+F374+Calculator!$B$30)</f>
+        <f>IF(A374="","",E374*Calculator!$B$6+Calculator!$C$37+F374+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H374" s="16">
@@ -16927,7 +16943,7 @@
         <v/>
       </c>
       <c r="G375" s="16">
-        <f>IF(A375="","",E375*Calculator!$B$6+Calculator!$B$37+F375+Calculator!$B$30)</f>
+        <f>IF(A375="","",E375*Calculator!$B$6+Calculator!$C$37+F375+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H375" s="16">
@@ -16969,7 +16985,7 @@
         <v/>
       </c>
       <c r="G376" s="16">
-        <f>IF(A376="","",E376*Calculator!$B$6+Calculator!$B$37+F376+Calculator!$B$30)</f>
+        <f>IF(A376="","",E376*Calculator!$B$6+Calculator!$C$37+F376+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H376" s="16">
@@ -17011,7 +17027,7 @@
         <v/>
       </c>
       <c r="G377" s="16">
-        <f>IF(A377="","",E377*Calculator!$B$6+Calculator!$B$37+F377+Calculator!$B$30)</f>
+        <f>IF(A377="","",E377*Calculator!$B$6+Calculator!$C$37+F377+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H377" s="16">
@@ -17053,7 +17069,7 @@
         <v/>
       </c>
       <c r="G378" s="16">
-        <f>IF(A378="","",E378*Calculator!$B$6+Calculator!$B$37+F378+Calculator!$B$30)</f>
+        <f>IF(A378="","",E378*Calculator!$B$6+Calculator!$C$37+F378+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H378" s="16">
@@ -17095,7 +17111,7 @@
         <v/>
       </c>
       <c r="G379" s="16">
-        <f>IF(A379="","",E379*Calculator!$B$6+Calculator!$B$37+F379+Calculator!$B$30)</f>
+        <f>IF(A379="","",E379*Calculator!$B$6+Calculator!$C$37+F379+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H379" s="16">
@@ -17137,7 +17153,7 @@
         <v/>
       </c>
       <c r="G380" s="16">
-        <f>IF(A380="","",E380*Calculator!$B$6+Calculator!$B$37+F380+Calculator!$B$30)</f>
+        <f>IF(A380="","",E380*Calculator!$B$6+Calculator!$C$37+F380+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H380" s="16">
@@ -17179,7 +17195,7 @@
         <v/>
       </c>
       <c r="G381" s="16">
-        <f>IF(A381="","",E381*Calculator!$B$6+Calculator!$B$37+F381+Calculator!$B$30)</f>
+        <f>IF(A381="","",E381*Calculator!$B$6+Calculator!$C$37+F381+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H381" s="16">
@@ -17221,7 +17237,7 @@
         <v/>
       </c>
       <c r="G382" s="16">
-        <f>IF(A382="","",E382*Calculator!$B$6+Calculator!$B$37+F382+Calculator!$B$30)</f>
+        <f>IF(A382="","",E382*Calculator!$B$6+Calculator!$C$37+F382+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H382" s="16">
@@ -17263,7 +17279,7 @@
         <v/>
       </c>
       <c r="G383" s="16">
-        <f>IF(A383="","",E383*Calculator!$B$6+Calculator!$B$37+F383+Calculator!$B$30)</f>
+        <f>IF(A383="","",E383*Calculator!$B$6+Calculator!$C$37+F383+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H383" s="16">
@@ -17305,7 +17321,7 @@
         <v/>
       </c>
       <c r="G384" s="16">
-        <f>IF(A384="","",E384*Calculator!$B$6+Calculator!$B$37+F384+Calculator!$B$30)</f>
+        <f>IF(A384="","",E384*Calculator!$B$6+Calculator!$C$37+F384+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H384" s="16">
@@ -17347,7 +17363,7 @@
         <v/>
       </c>
       <c r="G385" s="16">
-        <f>IF(A385="","",E385*Calculator!$B$6+Calculator!$B$37+F385+Calculator!$B$30)</f>
+        <f>IF(A385="","",E385*Calculator!$B$6+Calculator!$C$37+F385+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H385" s="16">
@@ -17389,7 +17405,7 @@
         <v/>
       </c>
       <c r="G386" s="16">
-        <f>IF(A386="","",E386*Calculator!$B$6+Calculator!$B$37+F386+Calculator!$B$30)</f>
+        <f>IF(A386="","",E386*Calculator!$B$6+Calculator!$C$37+F386+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H386" s="16">
@@ -17431,7 +17447,7 @@
         <v/>
       </c>
       <c r="G387" s="16">
-        <f>IF(A387="","",E387*Calculator!$B$6+Calculator!$B$37+F387+Calculator!$B$30)</f>
+        <f>IF(A387="","",E387*Calculator!$B$6+Calculator!$C$37+F387+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H387" s="16">
@@ -17473,7 +17489,7 @@
         <v/>
       </c>
       <c r="G388" s="16">
-        <f>IF(A388="","",E388*Calculator!$B$6+Calculator!$B$37+F388+Calculator!$B$30)</f>
+        <f>IF(A388="","",E388*Calculator!$B$6+Calculator!$C$37+F388+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H388" s="16">
@@ -17515,7 +17531,7 @@
         <v/>
       </c>
       <c r="G389" s="16">
-        <f>IF(A389="","",E389*Calculator!$B$6+Calculator!$B$37+F389+Calculator!$B$30)</f>
+        <f>IF(A389="","",E389*Calculator!$B$6+Calculator!$C$37+F389+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H389" s="16">
@@ -17557,7 +17573,7 @@
         <v/>
       </c>
       <c r="G390" s="16">
-        <f>IF(A390="","",E390*Calculator!$B$6+Calculator!$B$37+F390+Calculator!$B$30)</f>
+        <f>IF(A390="","",E390*Calculator!$B$6+Calculator!$C$37+F390+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H390" s="16">
@@ -17599,7 +17615,7 @@
         <v/>
       </c>
       <c r="G391" s="16">
-        <f>IF(A391="","",E391*Calculator!$B$6+Calculator!$B$37+F391+Calculator!$B$30)</f>
+        <f>IF(A391="","",E391*Calculator!$B$6+Calculator!$C$37+F391+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H391" s="16">
@@ -17641,7 +17657,7 @@
         <v/>
       </c>
       <c r="G392" s="16">
-        <f>IF(A392="","",E392*Calculator!$B$6+Calculator!$B$37+F392+Calculator!$B$30)</f>
+        <f>IF(A392="","",E392*Calculator!$B$6+Calculator!$C$37+F392+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H392" s="16">
@@ -17683,7 +17699,7 @@
         <v/>
       </c>
       <c r="G393" s="16">
-        <f>IF(A393="","",E393*Calculator!$B$6+Calculator!$B$37+F393+Calculator!$B$30)</f>
+        <f>IF(A393="","",E393*Calculator!$B$6+Calculator!$C$37+F393+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H393" s="16">
@@ -17725,7 +17741,7 @@
         <v/>
       </c>
       <c r="G394" s="16">
-        <f>IF(A394="","",E394*Calculator!$B$6+Calculator!$B$37+F394+Calculator!$B$30)</f>
+        <f>IF(A394="","",E394*Calculator!$B$6+Calculator!$C$37+F394+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H394" s="16">
@@ -17767,7 +17783,7 @@
         <v/>
       </c>
       <c r="G395" s="16">
-        <f>IF(A395="","",E395*Calculator!$B$6+Calculator!$B$37+F395+Calculator!$B$30)</f>
+        <f>IF(A395="","",E395*Calculator!$B$6+Calculator!$C$37+F395+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H395" s="16">
@@ -17809,7 +17825,7 @@
         <v/>
       </c>
       <c r="G396" s="16">
-        <f>IF(A396="","",E396*Calculator!$B$6+Calculator!$B$37+F396+Calculator!$B$30)</f>
+        <f>IF(A396="","",E396*Calculator!$B$6+Calculator!$C$37+F396+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H396" s="16">
@@ -17851,7 +17867,7 @@
         <v/>
       </c>
       <c r="G397" s="16">
-        <f>IF(A397="","",E397*Calculator!$B$6+Calculator!$B$37+F397+Calculator!$B$30)</f>
+        <f>IF(A397="","",E397*Calculator!$B$6+Calculator!$C$37+F397+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H397" s="16">
@@ -17893,7 +17909,7 @@
         <v/>
       </c>
       <c r="G398" s="16">
-        <f>IF(A398="","",E398*Calculator!$B$6+Calculator!$B$37+F398+Calculator!$B$30)</f>
+        <f>IF(A398="","",E398*Calculator!$B$6+Calculator!$C$37+F398+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H398" s="16">
@@ -17935,7 +17951,7 @@
         <v/>
       </c>
       <c r="G399" s="16">
-        <f>IF(A399="","",E399*Calculator!$B$6+Calculator!$B$37+F399+Calculator!$B$30)</f>
+        <f>IF(A399="","",E399*Calculator!$B$6+Calculator!$C$37+F399+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H399" s="16">
@@ -17977,7 +17993,7 @@
         <v/>
       </c>
       <c r="G400" s="16">
-        <f>IF(A400="","",E400*Calculator!$B$6+Calculator!$B$37+F400+Calculator!$B$30)</f>
+        <f>IF(A400="","",E400*Calculator!$B$6+Calculator!$C$37+F400+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H400" s="16">
@@ -18019,7 +18035,7 @@
         <v/>
       </c>
       <c r="G401" s="16">
-        <f>IF(A401="","",E401*Calculator!$B$6+Calculator!$B$37+F401+Calculator!$B$30)</f>
+        <f>IF(A401="","",E401*Calculator!$B$6+Calculator!$C$37+F401+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H401" s="16">
@@ -18061,7 +18077,7 @@
         <v/>
       </c>
       <c r="G402" s="16">
-        <f>IF(A402="","",E402*Calculator!$B$6+Calculator!$B$37+F402+Calculator!$B$30)</f>
+        <f>IF(A402="","",E402*Calculator!$B$6+Calculator!$C$37+F402+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H402" s="16">
@@ -18103,7 +18119,7 @@
         <v/>
       </c>
       <c r="G403" s="16">
-        <f>IF(A403="","",E403*Calculator!$B$6+Calculator!$B$37+F403+Calculator!$B$30)</f>
+        <f>IF(A403="","",E403*Calculator!$B$6+Calculator!$C$37+F403+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H403" s="16">
@@ -18145,7 +18161,7 @@
         <v/>
       </c>
       <c r="G404" s="16">
-        <f>IF(A404="","",E404*Calculator!$B$6+Calculator!$B$37+F404+Calculator!$B$30)</f>
+        <f>IF(A404="","",E404*Calculator!$B$6+Calculator!$C$37+F404+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H404" s="16">
@@ -18187,7 +18203,7 @@
         <v/>
       </c>
       <c r="G405" s="16">
-        <f>IF(A405="","",E405*Calculator!$B$6+Calculator!$B$37+F405+Calculator!$B$30)</f>
+        <f>IF(A405="","",E405*Calculator!$B$6+Calculator!$C$37+F405+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H405" s="16">
@@ -18229,7 +18245,7 @@
         <v/>
       </c>
       <c r="G406" s="16">
-        <f>IF(A406="","",E406*Calculator!$B$6+Calculator!$B$37+F406+Calculator!$B$30)</f>
+        <f>IF(A406="","",E406*Calculator!$B$6+Calculator!$C$37+F406+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H406" s="16">
@@ -18271,7 +18287,7 @@
         <v/>
       </c>
       <c r="G407" s="16">
-        <f>IF(A407="","",E407*Calculator!$B$6+Calculator!$B$37+F407+Calculator!$B$30)</f>
+        <f>IF(A407="","",E407*Calculator!$B$6+Calculator!$C$37+F407+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H407" s="16">
@@ -18313,7 +18329,7 @@
         <v/>
       </c>
       <c r="G408" s="16">
-        <f>IF(A408="","",E408*Calculator!$B$6+Calculator!$B$37+F408+Calculator!$B$30)</f>
+        <f>IF(A408="","",E408*Calculator!$B$6+Calculator!$C$37+F408+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H408" s="16">
@@ -18355,7 +18371,7 @@
         <v/>
       </c>
       <c r="G409" s="16">
-        <f>IF(A409="","",E409*Calculator!$B$6+Calculator!$B$37+F409+Calculator!$B$30)</f>
+        <f>IF(A409="","",E409*Calculator!$B$6+Calculator!$C$37+F409+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H409" s="16">
@@ -18397,7 +18413,7 @@
         <v/>
       </c>
       <c r="G410" s="16">
-        <f>IF(A410="","",E410*Calculator!$B$6+Calculator!$B$37+F410+Calculator!$B$30)</f>
+        <f>IF(A410="","",E410*Calculator!$B$6+Calculator!$C$37+F410+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H410" s="16">
@@ -18439,7 +18455,7 @@
         <v/>
       </c>
       <c r="G411" s="16">
-        <f>IF(A411="","",E411*Calculator!$B$6+Calculator!$B$37+F411+Calculator!$B$30)</f>
+        <f>IF(A411="","",E411*Calculator!$B$6+Calculator!$C$37+F411+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H411" s="16">
@@ -18481,7 +18497,7 @@
         <v/>
       </c>
       <c r="G412" s="16">
-        <f>IF(A412="","",E412*Calculator!$B$6+Calculator!$B$37+F412+Calculator!$B$30)</f>
+        <f>IF(A412="","",E412*Calculator!$B$6+Calculator!$C$37+F412+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H412" s="16">
@@ -18523,7 +18539,7 @@
         <v/>
       </c>
       <c r="G413" s="16">
-        <f>IF(A413="","",E413*Calculator!$B$6+Calculator!$B$37+F413+Calculator!$B$30)</f>
+        <f>IF(A413="","",E413*Calculator!$B$6+Calculator!$C$37+F413+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H413" s="16">
@@ -18565,7 +18581,7 @@
         <v/>
       </c>
       <c r="G414" s="16">
-        <f>IF(A414="","",E414*Calculator!$B$6+Calculator!$B$37+F414+Calculator!$B$30)</f>
+        <f>IF(A414="","",E414*Calculator!$B$6+Calculator!$C$37+F414+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H414" s="16">
@@ -18607,7 +18623,7 @@
         <v/>
       </c>
       <c r="G415" s="16">
-        <f>IF(A415="","",E415*Calculator!$B$6+Calculator!$B$37+F415+Calculator!$B$30)</f>
+        <f>IF(A415="","",E415*Calculator!$B$6+Calculator!$C$37+F415+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H415" s="16">
@@ -18649,7 +18665,7 @@
         <v/>
       </c>
       <c r="G416" s="16">
-        <f>IF(A416="","",E416*Calculator!$B$6+Calculator!$B$37+F416+Calculator!$B$30)</f>
+        <f>IF(A416="","",E416*Calculator!$B$6+Calculator!$C$37+F416+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H416" s="16">
@@ -18691,7 +18707,7 @@
         <v/>
       </c>
       <c r="G417" s="16">
-        <f>IF(A417="","",E417*Calculator!$B$6+Calculator!$B$37+F417+Calculator!$B$30)</f>
+        <f>IF(A417="","",E417*Calculator!$B$6+Calculator!$C$37+F417+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H417" s="16">
@@ -18733,7 +18749,7 @@
         <v/>
       </c>
       <c r="G418" s="16">
-        <f>IF(A418="","",E418*Calculator!$B$6+Calculator!$B$37+F418+Calculator!$B$30)</f>
+        <f>IF(A418="","",E418*Calculator!$B$6+Calculator!$C$37+F418+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H418" s="16">
@@ -18775,7 +18791,7 @@
         <v/>
       </c>
       <c r="G419" s="16">
-        <f>IF(A419="","",E419*Calculator!$B$6+Calculator!$B$37+F419+Calculator!$B$30)</f>
+        <f>IF(A419="","",E419*Calculator!$B$6+Calculator!$C$37+F419+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H419" s="16">
@@ -18817,7 +18833,7 @@
         <v/>
       </c>
       <c r="G420" s="16">
-        <f>IF(A420="","",E420*Calculator!$B$6+Calculator!$B$37+F420+Calculator!$B$30)</f>
+        <f>IF(A420="","",E420*Calculator!$B$6+Calculator!$C$37+F420+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H420" s="16">
@@ -18859,7 +18875,7 @@
         <v/>
       </c>
       <c r="G421" s="16">
-        <f>IF(A421="","",E421*Calculator!$B$6+Calculator!$B$37+F421+Calculator!$B$30)</f>
+        <f>IF(A421="","",E421*Calculator!$B$6+Calculator!$C$37+F421+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H421" s="16">
@@ -18901,7 +18917,7 @@
         <v/>
       </c>
       <c r="G422" s="16">
-        <f>IF(A422="","",E422*Calculator!$B$6+Calculator!$B$37+F422+Calculator!$B$30)</f>
+        <f>IF(A422="","",E422*Calculator!$B$6+Calculator!$C$37+F422+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H422" s="16">
@@ -18943,7 +18959,7 @@
         <v/>
       </c>
       <c r="G423" s="16">
-        <f>IF(A423="","",E423*Calculator!$B$6+Calculator!$B$37+F423+Calculator!$B$30)</f>
+        <f>IF(A423="","",E423*Calculator!$B$6+Calculator!$C$37+F423+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H423" s="16">
@@ -18985,7 +19001,7 @@
         <v/>
       </c>
       <c r="G424" s="16">
-        <f>IF(A424="","",E424*Calculator!$B$6+Calculator!$B$37+F424+Calculator!$B$30)</f>
+        <f>IF(A424="","",E424*Calculator!$B$6+Calculator!$C$37+F424+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H424" s="16">
@@ -19027,7 +19043,7 @@
         <v/>
       </c>
       <c r="G425" s="16">
-        <f>IF(A425="","",E425*Calculator!$B$6+Calculator!$B$37+F425+Calculator!$B$30)</f>
+        <f>IF(A425="","",E425*Calculator!$B$6+Calculator!$C$37+F425+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H425" s="16">
@@ -19069,7 +19085,7 @@
         <v/>
       </c>
       <c r="G426" s="16">
-        <f>IF(A426="","",E426*Calculator!$B$6+Calculator!$B$37+F426+Calculator!$B$30)</f>
+        <f>IF(A426="","",E426*Calculator!$B$6+Calculator!$C$37+F426+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H426" s="16">
@@ -19111,7 +19127,7 @@
         <v/>
       </c>
       <c r="G427" s="16">
-        <f>IF(A427="","",E427*Calculator!$B$6+Calculator!$B$37+F427+Calculator!$B$30)</f>
+        <f>IF(A427="","",E427*Calculator!$B$6+Calculator!$C$37+F427+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H427" s="16">
@@ -19153,7 +19169,7 @@
         <v/>
       </c>
       <c r="G428" s="16">
-        <f>IF(A428="","",E428*Calculator!$B$6+Calculator!$B$37+F428+Calculator!$B$30)</f>
+        <f>IF(A428="","",E428*Calculator!$B$6+Calculator!$C$37+F428+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H428" s="16">
@@ -19195,7 +19211,7 @@
         <v/>
       </c>
       <c r="G429" s="16">
-        <f>IF(A429="","",E429*Calculator!$B$6+Calculator!$B$37+F429+Calculator!$B$30)</f>
+        <f>IF(A429="","",E429*Calculator!$B$6+Calculator!$C$37+F429+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H429" s="16">
@@ -19237,7 +19253,7 @@
         <v/>
       </c>
       <c r="G430" s="16">
-        <f>IF(A430="","",E430*Calculator!$B$6+Calculator!$B$37+F430+Calculator!$B$30)</f>
+        <f>IF(A430="","",E430*Calculator!$B$6+Calculator!$C$37+F430+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H430" s="16">
@@ -19279,7 +19295,7 @@
         <v/>
       </c>
       <c r="G431" s="16">
-        <f>IF(A431="","",E431*Calculator!$B$6+Calculator!$B$37+F431+Calculator!$B$30)</f>
+        <f>IF(A431="","",E431*Calculator!$B$6+Calculator!$C$37+F431+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H431" s="16">
@@ -19321,7 +19337,7 @@
         <v/>
       </c>
       <c r="G432" s="16">
-        <f>IF(A432="","",E432*Calculator!$B$6+Calculator!$B$37+F432+Calculator!$B$30)</f>
+        <f>IF(A432="","",E432*Calculator!$B$6+Calculator!$C$37+F432+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H432" s="16">
@@ -19363,7 +19379,7 @@
         <v/>
       </c>
       <c r="G433" s="16">
-        <f>IF(A433="","",E433*Calculator!$B$6+Calculator!$B$37+F433+Calculator!$B$30)</f>
+        <f>IF(A433="","",E433*Calculator!$B$6+Calculator!$C$37+F433+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H433" s="16">
@@ -19405,7 +19421,7 @@
         <v/>
       </c>
       <c r="G434" s="16">
-        <f>IF(A434="","",E434*Calculator!$B$6+Calculator!$B$37+F434+Calculator!$B$30)</f>
+        <f>IF(A434="","",E434*Calculator!$B$6+Calculator!$C$37+F434+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H434" s="16">
@@ -19447,7 +19463,7 @@
         <v/>
       </c>
       <c r="G435" s="16">
-        <f>IF(A435="","",E435*Calculator!$B$6+Calculator!$B$37+F435+Calculator!$B$30)</f>
+        <f>IF(A435="","",E435*Calculator!$B$6+Calculator!$C$37+F435+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H435" s="16">
@@ -19489,7 +19505,7 @@
         <v/>
       </c>
       <c r="G436" s="16">
-        <f>IF(A436="","",E436*Calculator!$B$6+Calculator!$B$37+F436+Calculator!$B$30)</f>
+        <f>IF(A436="","",E436*Calculator!$B$6+Calculator!$C$37+F436+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H436" s="16">
@@ -19531,7 +19547,7 @@
         <v/>
       </c>
       <c r="G437" s="16">
-        <f>IF(A437="","",E437*Calculator!$B$6+Calculator!$B$37+F437+Calculator!$B$30)</f>
+        <f>IF(A437="","",E437*Calculator!$B$6+Calculator!$C$37+F437+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H437" s="16">
@@ -19573,7 +19589,7 @@
         <v/>
       </c>
       <c r="G438" s="16">
-        <f>IF(A438="","",E438*Calculator!$B$6+Calculator!$B$37+F438+Calculator!$B$30)</f>
+        <f>IF(A438="","",E438*Calculator!$B$6+Calculator!$C$37+F438+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H438" s="16">
@@ -19615,7 +19631,7 @@
         <v/>
       </c>
       <c r="G439" s="16">
-        <f>IF(A439="","",E439*Calculator!$B$6+Calculator!$B$37+F439+Calculator!$B$30)</f>
+        <f>IF(A439="","",E439*Calculator!$B$6+Calculator!$C$37+F439+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H439" s="16">
@@ -19657,7 +19673,7 @@
         <v/>
       </c>
       <c r="G440" s="16">
-        <f>IF(A440="","",E440*Calculator!$B$6+Calculator!$B$37+F440+Calculator!$B$30)</f>
+        <f>IF(A440="","",E440*Calculator!$B$6+Calculator!$C$37+F440+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H440" s="16">
@@ -19699,7 +19715,7 @@
         <v/>
       </c>
       <c r="G441" s="16">
-        <f>IF(A441="","",E441*Calculator!$B$6+Calculator!$B$37+F441+Calculator!$B$30)</f>
+        <f>IF(A441="","",E441*Calculator!$B$6+Calculator!$C$37+F441+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H441" s="16">
@@ -19741,7 +19757,7 @@
         <v/>
       </c>
       <c r="G442" s="16">
-        <f>IF(A442="","",E442*Calculator!$B$6+Calculator!$B$37+F442+Calculator!$B$30)</f>
+        <f>IF(A442="","",E442*Calculator!$B$6+Calculator!$C$37+F442+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H442" s="16">
@@ -19783,7 +19799,7 @@
         <v/>
       </c>
       <c r="G443" s="16">
-        <f>IF(A443="","",E443*Calculator!$B$6+Calculator!$B$37+F443+Calculator!$B$30)</f>
+        <f>IF(A443="","",E443*Calculator!$B$6+Calculator!$C$37+F443+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H443" s="16">
@@ -19825,7 +19841,7 @@
         <v/>
       </c>
       <c r="G444" s="16">
-        <f>IF(A444="","",E444*Calculator!$B$6+Calculator!$B$37+F444+Calculator!$B$30)</f>
+        <f>IF(A444="","",E444*Calculator!$B$6+Calculator!$C$37+F444+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H444" s="16">
@@ -19867,7 +19883,7 @@
         <v/>
       </c>
       <c r="G445" s="16">
-        <f>IF(A445="","",E445*Calculator!$B$6+Calculator!$B$37+F445+Calculator!$B$30)</f>
+        <f>IF(A445="","",E445*Calculator!$B$6+Calculator!$C$37+F445+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H445" s="16">
@@ -19909,7 +19925,7 @@
         <v/>
       </c>
       <c r="G446" s="16">
-        <f>IF(A446="","",E446*Calculator!$B$6+Calculator!$B$37+F446+Calculator!$B$30)</f>
+        <f>IF(A446="","",E446*Calculator!$B$6+Calculator!$C$37+F446+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H446" s="16">
@@ -19951,7 +19967,7 @@
         <v/>
       </c>
       <c r="G447" s="16">
-        <f>IF(A447="","",E447*Calculator!$B$6+Calculator!$B$37+F447+Calculator!$B$30)</f>
+        <f>IF(A447="","",E447*Calculator!$B$6+Calculator!$C$37+F447+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H447" s="16">
@@ -19993,7 +20009,7 @@
         <v/>
       </c>
       <c r="G448" s="16">
-        <f>IF(A448="","",E448*Calculator!$B$6+Calculator!$B$37+F448+Calculator!$B$30)</f>
+        <f>IF(A448="","",E448*Calculator!$B$6+Calculator!$C$37+F448+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H448" s="16">
@@ -20035,7 +20051,7 @@
         <v/>
       </c>
       <c r="G449" s="16">
-        <f>IF(A449="","",E449*Calculator!$B$6+Calculator!$B$37+F449+Calculator!$B$30)</f>
+        <f>IF(A449="","",E449*Calculator!$B$6+Calculator!$C$37+F449+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H449" s="16">
@@ -20077,7 +20093,7 @@
         <v/>
       </c>
       <c r="G450" s="16">
-        <f>IF(A450="","",E450*Calculator!$B$6+Calculator!$B$37+F450+Calculator!$B$30)</f>
+        <f>IF(A450="","",E450*Calculator!$B$6+Calculator!$C$37+F450+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H450" s="16">
@@ -20119,7 +20135,7 @@
         <v/>
       </c>
       <c r="G451" s="16">
-        <f>IF(A451="","",E451*Calculator!$B$6+Calculator!$B$37+F451+Calculator!$B$30)</f>
+        <f>IF(A451="","",E451*Calculator!$B$6+Calculator!$C$37+F451+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H451" s="16">
@@ -20161,7 +20177,7 @@
         <v/>
       </c>
       <c r="G452" s="16">
-        <f>IF(A452="","",E452*Calculator!$B$6+Calculator!$B$37+F452+Calculator!$B$30)</f>
+        <f>IF(A452="","",E452*Calculator!$B$6+Calculator!$C$37+F452+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H452" s="16">
@@ -20203,7 +20219,7 @@
         <v/>
       </c>
       <c r="G453" s="16">
-        <f>IF(A453="","",E453*Calculator!$B$6+Calculator!$B$37+F453+Calculator!$B$30)</f>
+        <f>IF(A453="","",E453*Calculator!$B$6+Calculator!$C$37+F453+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H453" s="16">
@@ -20245,7 +20261,7 @@
         <v/>
       </c>
       <c r="G454" s="16">
-        <f>IF(A454="","",E454*Calculator!$B$6+Calculator!$B$37+F454+Calculator!$B$30)</f>
+        <f>IF(A454="","",E454*Calculator!$B$6+Calculator!$C$37+F454+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H454" s="16">
@@ -20287,7 +20303,7 @@
         <v/>
       </c>
       <c r="G455" s="16">
-        <f>IF(A455="","",E455*Calculator!$B$6+Calculator!$B$37+F455+Calculator!$B$30)</f>
+        <f>IF(A455="","",E455*Calculator!$B$6+Calculator!$C$37+F455+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H455" s="16">
@@ -20329,7 +20345,7 @@
         <v/>
       </c>
       <c r="G456" s="16">
-        <f>IF(A456="","",E456*Calculator!$B$6+Calculator!$B$37+F456+Calculator!$B$30)</f>
+        <f>IF(A456="","",E456*Calculator!$B$6+Calculator!$C$37+F456+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H456" s="16">
@@ -20371,7 +20387,7 @@
         <v/>
       </c>
       <c r="G457" s="16">
-        <f>IF(A457="","",E457*Calculator!$B$6+Calculator!$B$37+F457+Calculator!$B$30)</f>
+        <f>IF(A457="","",E457*Calculator!$B$6+Calculator!$C$37+F457+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H457" s="16">
@@ -20413,7 +20429,7 @@
         <v/>
       </c>
       <c r="G458" s="16">
-        <f>IF(A458="","",E458*Calculator!$B$6+Calculator!$B$37+F458+Calculator!$B$30)</f>
+        <f>IF(A458="","",E458*Calculator!$B$6+Calculator!$C$37+F458+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H458" s="16">
@@ -20455,7 +20471,7 @@
         <v/>
       </c>
       <c r="G459" s="16">
-        <f>IF(A459="","",E459*Calculator!$B$6+Calculator!$B$37+F459+Calculator!$B$30)</f>
+        <f>IF(A459="","",E459*Calculator!$B$6+Calculator!$C$37+F459+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H459" s="16">
@@ -20497,7 +20513,7 @@
         <v/>
       </c>
       <c r="G460" s="16">
-        <f>IF(A460="","",E460*Calculator!$B$6+Calculator!$B$37+F460+Calculator!$B$30)</f>
+        <f>IF(A460="","",E460*Calculator!$B$6+Calculator!$C$37+F460+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H460" s="16">
@@ -20539,7 +20555,7 @@
         <v/>
       </c>
       <c r="G461" s="16">
-        <f>IF(A461="","",E461*Calculator!$B$6+Calculator!$B$37+F461+Calculator!$B$30)</f>
+        <f>IF(A461="","",E461*Calculator!$B$6+Calculator!$C$37+F461+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H461" s="16">
@@ -20581,7 +20597,7 @@
         <v/>
       </c>
       <c r="G462" s="16">
-        <f>IF(A462="","",E462*Calculator!$B$6+Calculator!$B$37+F462+Calculator!$B$30)</f>
+        <f>IF(A462="","",E462*Calculator!$B$6+Calculator!$C$37+F462+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H462" s="16">
@@ -20623,7 +20639,7 @@
         <v/>
       </c>
       <c r="G463" s="16">
-        <f>IF(A463="","",E463*Calculator!$B$6+Calculator!$B$37+F463+Calculator!$B$30)</f>
+        <f>IF(A463="","",E463*Calculator!$B$6+Calculator!$C$37+F463+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H463" s="16">
@@ -20665,7 +20681,7 @@
         <v/>
       </c>
       <c r="G464" s="16">
-        <f>IF(A464="","",E464*Calculator!$B$6+Calculator!$B$37+F464+Calculator!$B$30)</f>
+        <f>IF(A464="","",E464*Calculator!$B$6+Calculator!$C$37+F464+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H464" s="16">
@@ -20707,7 +20723,7 @@
         <v/>
       </c>
       <c r="G465" s="16">
-        <f>IF(A465="","",E465*Calculator!$B$6+Calculator!$B$37+F465+Calculator!$B$30)</f>
+        <f>IF(A465="","",E465*Calculator!$B$6+Calculator!$C$37+F465+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H465" s="16">
@@ -20749,7 +20765,7 @@
         <v/>
       </c>
       <c r="G466" s="16">
-        <f>IF(A466="","",E466*Calculator!$B$6+Calculator!$B$37+F466+Calculator!$B$30)</f>
+        <f>IF(A466="","",E466*Calculator!$B$6+Calculator!$C$37+F466+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H466" s="16">
@@ -20791,7 +20807,7 @@
         <v/>
       </c>
       <c r="G467" s="16">
-        <f>IF(A467="","",E467*Calculator!$B$6+Calculator!$B$37+F467+Calculator!$B$30)</f>
+        <f>IF(A467="","",E467*Calculator!$B$6+Calculator!$C$37+F467+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H467" s="16">
@@ -20833,7 +20849,7 @@
         <v/>
       </c>
       <c r="G468" s="16">
-        <f>IF(A468="","",E468*Calculator!$B$6+Calculator!$B$37+F468+Calculator!$B$30)</f>
+        <f>IF(A468="","",E468*Calculator!$B$6+Calculator!$C$37+F468+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H468" s="16">
@@ -20875,7 +20891,7 @@
         <v/>
       </c>
       <c r="G469" s="16">
-        <f>IF(A469="","",E469*Calculator!$B$6+Calculator!$B$37+F469+Calculator!$B$30)</f>
+        <f>IF(A469="","",E469*Calculator!$B$6+Calculator!$C$37+F469+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H469" s="16">
@@ -20917,7 +20933,7 @@
         <v/>
       </c>
       <c r="G470" s="16">
-        <f>IF(A470="","",E470*Calculator!$B$6+Calculator!$B$37+F470+Calculator!$B$30)</f>
+        <f>IF(A470="","",E470*Calculator!$B$6+Calculator!$C$37+F470+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H470" s="16">
@@ -20959,7 +20975,7 @@
         <v/>
       </c>
       <c r="G471" s="16">
-        <f>IF(A471="","",E471*Calculator!$B$6+Calculator!$B$37+F471+Calculator!$B$30)</f>
+        <f>IF(A471="","",E471*Calculator!$B$6+Calculator!$C$37+F471+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H471" s="16">
@@ -21001,7 +21017,7 @@
         <v/>
       </c>
       <c r="G472" s="16">
-        <f>IF(A472="","",E472*Calculator!$B$6+Calculator!$B$37+F472+Calculator!$B$30)</f>
+        <f>IF(A472="","",E472*Calculator!$B$6+Calculator!$C$37+F472+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H472" s="16">
@@ -21043,7 +21059,7 @@
         <v/>
       </c>
       <c r="G473" s="16">
-        <f>IF(A473="","",E473*Calculator!$B$6+Calculator!$B$37+F473+Calculator!$B$30)</f>
+        <f>IF(A473="","",E473*Calculator!$B$6+Calculator!$C$37+F473+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H473" s="16">
@@ -21085,7 +21101,7 @@
         <v/>
       </c>
       <c r="G474" s="16">
-        <f>IF(A474="","",E474*Calculator!$B$6+Calculator!$B$37+F474+Calculator!$B$30)</f>
+        <f>IF(A474="","",E474*Calculator!$B$6+Calculator!$C$37+F474+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H474" s="16">
@@ -21127,7 +21143,7 @@
         <v/>
       </c>
       <c r="G475" s="16">
-        <f>IF(A475="","",E475*Calculator!$B$6+Calculator!$B$37+F475+Calculator!$B$30)</f>
+        <f>IF(A475="","",E475*Calculator!$B$6+Calculator!$C$37+F475+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H475" s="16">
@@ -21169,7 +21185,7 @@
         <v/>
       </c>
       <c r="G476" s="16">
-        <f>IF(A476="","",E476*Calculator!$B$6+Calculator!$B$37+F476+Calculator!$B$30)</f>
+        <f>IF(A476="","",E476*Calculator!$B$6+Calculator!$C$37+F476+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H476" s="16">
@@ -21211,7 +21227,7 @@
         <v/>
       </c>
       <c r="G477" s="16">
-        <f>IF(A477="","",E477*Calculator!$B$6+Calculator!$B$37+F477+Calculator!$B$30)</f>
+        <f>IF(A477="","",E477*Calculator!$B$6+Calculator!$C$37+F477+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H477" s="16">
@@ -21253,7 +21269,7 @@
         <v/>
       </c>
       <c r="G478" s="16">
-        <f>IF(A478="","",E478*Calculator!$B$6+Calculator!$B$37+F478+Calculator!$B$30)</f>
+        <f>IF(A478="","",E478*Calculator!$B$6+Calculator!$C$37+F478+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H478" s="16">
@@ -21295,7 +21311,7 @@
         <v/>
       </c>
       <c r="G479" s="16">
-        <f>IF(A479="","",E479*Calculator!$B$6+Calculator!$B$37+F479+Calculator!$B$30)</f>
+        <f>IF(A479="","",E479*Calculator!$B$6+Calculator!$C$37+F479+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H479" s="16">
@@ -21337,7 +21353,7 @@
         <v/>
       </c>
       <c r="G480" s="16">
-        <f>IF(A480="","",E480*Calculator!$B$6+Calculator!$B$37+F480+Calculator!$B$30)</f>
+        <f>IF(A480="","",E480*Calculator!$B$6+Calculator!$C$37+F480+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H480" s="16">
@@ -21379,7 +21395,7 @@
         <v/>
       </c>
       <c r="G481" s="16">
-        <f>IF(A481="","",E481*Calculator!$B$6+Calculator!$B$37+F481+Calculator!$B$30)</f>
+        <f>IF(A481="","",E481*Calculator!$B$6+Calculator!$C$37+F481+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H481" s="16">
@@ -21421,7 +21437,7 @@
         <v/>
       </c>
       <c r="G482" s="16">
-        <f>IF(A482="","",E482*Calculator!$B$6+Calculator!$B$37+F482+Calculator!$B$30)</f>
+        <f>IF(A482="","",E482*Calculator!$B$6+Calculator!$C$37+F482+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H482" s="16">
@@ -21463,7 +21479,7 @@
         <v/>
       </c>
       <c r="G483" s="16">
-        <f>IF(A483="","",E483*Calculator!$B$6+Calculator!$B$37+F483+Calculator!$B$30)</f>
+        <f>IF(A483="","",E483*Calculator!$B$6+Calculator!$C$37+F483+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H483" s="16">
@@ -21505,7 +21521,7 @@
         <v/>
       </c>
       <c r="G484" s="16">
-        <f>IF(A484="","",E484*Calculator!$B$6+Calculator!$B$37+F484+Calculator!$B$30)</f>
+        <f>IF(A484="","",E484*Calculator!$B$6+Calculator!$C$37+F484+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H484" s="16">
@@ -21547,7 +21563,7 @@
         <v/>
       </c>
       <c r="G485" s="16">
-        <f>IF(A485="","",E485*Calculator!$B$6+Calculator!$B$37+F485+Calculator!$B$30)</f>
+        <f>IF(A485="","",E485*Calculator!$B$6+Calculator!$C$37+F485+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H485" s="16">
@@ -21589,7 +21605,7 @@
         <v/>
       </c>
       <c r="G486" s="16">
-        <f>IF(A486="","",E486*Calculator!$B$6+Calculator!$B$37+F486+Calculator!$B$30)</f>
+        <f>IF(A486="","",E486*Calculator!$B$6+Calculator!$C$37+F486+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H486" s="16">
@@ -21631,7 +21647,7 @@
         <v/>
       </c>
       <c r="G487" s="16">
-        <f>IF(A487="","",E487*Calculator!$B$6+Calculator!$B$37+F487+Calculator!$B$30)</f>
+        <f>IF(A487="","",E487*Calculator!$B$6+Calculator!$C$37+F487+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H487" s="16">
@@ -21673,7 +21689,7 @@
         <v/>
       </c>
       <c r="G488" s="16">
-        <f>IF(A488="","",E488*Calculator!$B$6+Calculator!$B$37+F488+Calculator!$B$30)</f>
+        <f>IF(A488="","",E488*Calculator!$B$6+Calculator!$C$37+F488+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H488" s="16">
@@ -21715,7 +21731,7 @@
         <v/>
       </c>
       <c r="G489" s="16">
-        <f>IF(A489="","",E489*Calculator!$B$6+Calculator!$B$37+F489+Calculator!$B$30)</f>
+        <f>IF(A489="","",E489*Calculator!$B$6+Calculator!$C$37+F489+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H489" s="16">
@@ -21757,7 +21773,7 @@
         <v/>
       </c>
       <c r="G490" s="16">
-        <f>IF(A490="","",E490*Calculator!$B$6+Calculator!$B$37+F490+Calculator!$B$30)</f>
+        <f>IF(A490="","",E490*Calculator!$B$6+Calculator!$C$37+F490+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H490" s="16">
@@ -21799,7 +21815,7 @@
         <v/>
       </c>
       <c r="G491" s="16">
-        <f>IF(A491="","",E491*Calculator!$B$6+Calculator!$B$37+F491+Calculator!$B$30)</f>
+        <f>IF(A491="","",E491*Calculator!$B$6+Calculator!$C$37+F491+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H491" s="16">
@@ -21841,7 +21857,7 @@
         <v/>
       </c>
       <c r="G492" s="16">
-        <f>IF(A492="","",E492*Calculator!$B$6+Calculator!$B$37+F492+Calculator!$B$30)</f>
+        <f>IF(A492="","",E492*Calculator!$B$6+Calculator!$C$37+F492+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H492" s="16">
@@ -21883,7 +21899,7 @@
         <v/>
       </c>
       <c r="G493" s="16">
-        <f>IF(A493="","",E493*Calculator!$B$6+Calculator!$B$37+F493+Calculator!$B$30)</f>
+        <f>IF(A493="","",E493*Calculator!$B$6+Calculator!$C$37+F493+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H493" s="16">
@@ -21925,7 +21941,7 @@
         <v/>
       </c>
       <c r="G494" s="16">
-        <f>IF(A494="","",E494*Calculator!$B$6+Calculator!$B$37+F494+Calculator!$B$30)</f>
+        <f>IF(A494="","",E494*Calculator!$B$6+Calculator!$C$37+F494+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H494" s="16">
@@ -21967,7 +21983,7 @@
         <v/>
       </c>
       <c r="G495" s="16">
-        <f>IF(A495="","",E495*Calculator!$B$6+Calculator!$B$37+F495+Calculator!$B$30)</f>
+        <f>IF(A495="","",E495*Calculator!$B$6+Calculator!$C$37+F495+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H495" s="16">
@@ -22009,7 +22025,7 @@
         <v/>
       </c>
       <c r="G496" s="16">
-        <f>IF(A496="","",E496*Calculator!$B$6+Calculator!$B$37+F496+Calculator!$B$30)</f>
+        <f>IF(A496="","",E496*Calculator!$B$6+Calculator!$C$37+F496+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H496" s="16">
@@ -22051,7 +22067,7 @@
         <v/>
       </c>
       <c r="G497" s="16">
-        <f>IF(A497="","",E497*Calculator!$B$6+Calculator!$B$37+F497+Calculator!$B$30)</f>
+        <f>IF(A497="","",E497*Calculator!$B$6+Calculator!$C$37+F497+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H497" s="16">
@@ -22093,7 +22109,7 @@
         <v/>
       </c>
       <c r="G498" s="16">
-        <f>IF(A498="","",E498*Calculator!$B$6+Calculator!$B$37+F498+Calculator!$B$30)</f>
+        <f>IF(A498="","",E498*Calculator!$B$6+Calculator!$C$37+F498+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H498" s="16">
@@ -22135,7 +22151,7 @@
         <v/>
       </c>
       <c r="G499" s="16">
-        <f>IF(A499="","",E499*Calculator!$B$6+Calculator!$B$37+F499+Calculator!$B$30)</f>
+        <f>IF(A499="","",E499*Calculator!$B$6+Calculator!$C$37+F499+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H499" s="16">
@@ -22177,7 +22193,7 @@
         <v/>
       </c>
       <c r="G500" s="16">
-        <f>IF(A500="","",E500*Calculator!$B$6+Calculator!$B$37+F500+Calculator!$B$30)</f>
+        <f>IF(A500="","",E500*Calculator!$B$6+Calculator!$C$37+F500+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H500" s="16">
@@ -22219,7 +22235,7 @@
         <v/>
       </c>
       <c r="G501" s="16">
-        <f>IF(A501="","",E501*Calculator!$B$6+Calculator!$B$37+F501+Calculator!$B$30)</f>
+        <f>IF(A501="","",E501*Calculator!$B$6+Calculator!$C$37+F501+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H501" s="16">
@@ -22261,7 +22277,7 @@
         <v/>
       </c>
       <c r="G502" s="16">
-        <f>IF(A502="","",E502*Calculator!$B$6+Calculator!$B$37+F502+Calculator!$B$30)</f>
+        <f>IF(A502="","",E502*Calculator!$B$6+Calculator!$C$37+F502+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H502" s="16">
@@ -22303,7 +22319,7 @@
         <v/>
       </c>
       <c r="G503" s="16">
-        <f>IF(A503="","",E503*Calculator!$B$6+Calculator!$B$37+F503+Calculator!$B$30)</f>
+        <f>IF(A503="","",E503*Calculator!$B$6+Calculator!$C$37+F503+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H503" s="16">
@@ -22345,7 +22361,7 @@
         <v/>
       </c>
       <c r="G504" s="16">
-        <f>IF(A504="","",E504*Calculator!$B$6+Calculator!$B$37+F504+Calculator!$B$30)</f>
+        <f>IF(A504="","",E504*Calculator!$B$6+Calculator!$C$37+F504+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H504" s="16">
@@ -22387,7 +22403,7 @@
         <v/>
       </c>
       <c r="G505" s="16">
-        <f>IF(A505="","",E505*Calculator!$B$6+Calculator!$B$37+F505+Calculator!$B$30)</f>
+        <f>IF(A505="","",E505*Calculator!$B$6+Calculator!$C$37+F505+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H505" s="16">
@@ -22429,7 +22445,7 @@
         <v/>
       </c>
       <c r="G506" s="16">
-        <f>IF(A506="","",E506*Calculator!$B$6+Calculator!$B$37+F506+Calculator!$B$30)</f>
+        <f>IF(A506="","",E506*Calculator!$B$6+Calculator!$C$37+F506+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H506" s="16">
@@ -22471,7 +22487,7 @@
         <v/>
       </c>
       <c r="G507" s="16">
-        <f>IF(A507="","",E507*Calculator!$B$6+Calculator!$B$37+F507+Calculator!$B$30)</f>
+        <f>IF(A507="","",E507*Calculator!$B$6+Calculator!$C$37+F507+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H507" s="16">
@@ -22513,7 +22529,7 @@
         <v/>
       </c>
       <c r="G508" s="16">
-        <f>IF(A508="","",E508*Calculator!$B$6+Calculator!$B$37+F508+Calculator!$B$30)</f>
+        <f>IF(A508="","",E508*Calculator!$B$6+Calculator!$C$37+F508+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H508" s="16">
@@ -22555,7 +22571,7 @@
         <v/>
       </c>
       <c r="G509" s="16">
-        <f>IF(A509="","",E509*Calculator!$B$6+Calculator!$B$37+F509+Calculator!$B$30)</f>
+        <f>IF(A509="","",E509*Calculator!$B$6+Calculator!$C$37+F509+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H509" s="16">
@@ -22597,7 +22613,7 @@
         <v/>
       </c>
       <c r="G510" s="16">
-        <f>IF(A510="","",E510*Calculator!$B$6+Calculator!$B$37+F510+Calculator!$B$30)</f>
+        <f>IF(A510="","",E510*Calculator!$B$6+Calculator!$C$37+F510+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H510" s="16">
@@ -22639,7 +22655,7 @@
         <v/>
       </c>
       <c r="G511" s="16">
-        <f>IF(A511="","",E511*Calculator!$B$6+Calculator!$B$37+F511+Calculator!$B$30)</f>
+        <f>IF(A511="","",E511*Calculator!$B$6+Calculator!$C$37+F511+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H511" s="16">
@@ -22681,7 +22697,7 @@
         <v/>
       </c>
       <c r="G512" s="16">
-        <f>IF(A512="","",E512*Calculator!$B$6+Calculator!$B$37+F512+Calculator!$B$30)</f>
+        <f>IF(A512="","",E512*Calculator!$B$6+Calculator!$C$37+F512+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H512" s="16">
@@ -22723,7 +22739,7 @@
         <v/>
       </c>
       <c r="G513" s="16">
-        <f>IF(A513="","",E513*Calculator!$B$6+Calculator!$B$37+F513+Calculator!$B$30)</f>
+        <f>IF(A513="","",E513*Calculator!$B$6+Calculator!$C$37+F513+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H513" s="16">
@@ -22765,7 +22781,7 @@
         <v/>
       </c>
       <c r="G514" s="16">
-        <f>IF(A514="","",E514*Calculator!$B$6+Calculator!$B$37+F514+Calculator!$B$30)</f>
+        <f>IF(A514="","",E514*Calculator!$B$6+Calculator!$C$37+F514+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H514" s="16">
@@ -22807,7 +22823,7 @@
         <v/>
       </c>
       <c r="G515" s="16">
-        <f>IF(A515="","",E515*Calculator!$B$6+Calculator!$B$37+F515+Calculator!$B$30)</f>
+        <f>IF(A515="","",E515*Calculator!$B$6+Calculator!$C$37+F515+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H515" s="16">
@@ -22849,7 +22865,7 @@
         <v/>
       </c>
       <c r="G516" s="16">
-        <f>IF(A516="","",E516*Calculator!$B$6+Calculator!$B$37+F516+Calculator!$B$30)</f>
+        <f>IF(A516="","",E516*Calculator!$B$6+Calculator!$C$37+F516+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H516" s="16">
@@ -22891,7 +22907,7 @@
         <v/>
       </c>
       <c r="G517" s="16">
-        <f>IF(A517="","",E517*Calculator!$B$6+Calculator!$B$37+F517+Calculator!$B$30)</f>
+        <f>IF(A517="","",E517*Calculator!$B$6+Calculator!$C$37+F517+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H517" s="16">
@@ -22933,7 +22949,7 @@
         <v/>
       </c>
       <c r="G518" s="16">
-        <f>IF(A518="","",E518*Calculator!$B$6+Calculator!$B$37+F518+Calculator!$B$30)</f>
+        <f>IF(A518="","",E518*Calculator!$B$6+Calculator!$C$37+F518+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H518" s="16">
@@ -22975,7 +22991,7 @@
         <v/>
       </c>
       <c r="G519" s="16">
-        <f>IF(A519="","",E519*Calculator!$B$6+Calculator!$B$37+F519+Calculator!$B$30)</f>
+        <f>IF(A519="","",E519*Calculator!$B$6+Calculator!$C$37+F519+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H519" s="16">
@@ -23017,7 +23033,7 @@
         <v/>
       </c>
       <c r="G520" s="16">
-        <f>IF(A520="","",E520*Calculator!$B$6+Calculator!$B$37+F520+Calculator!$B$30)</f>
+        <f>IF(A520="","",E520*Calculator!$B$6+Calculator!$C$37+F520+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H520" s="16">
@@ -23059,7 +23075,7 @@
         <v/>
       </c>
       <c r="G521" s="16">
-        <f>IF(A521="","",E521*Calculator!$B$6+Calculator!$B$37+F521+Calculator!$B$30)</f>
+        <f>IF(A521="","",E521*Calculator!$B$6+Calculator!$C$37+F521+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H521" s="16">
@@ -23101,7 +23117,7 @@
         <v/>
       </c>
       <c r="G522" s="16">
-        <f>IF(A522="","",E522*Calculator!$B$6+Calculator!$B$37+F522+Calculator!$B$30)</f>
+        <f>IF(A522="","",E522*Calculator!$B$6+Calculator!$C$37+F522+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H522" s="16">
@@ -23143,7 +23159,7 @@
         <v/>
       </c>
       <c r="G523" s="16">
-        <f>IF(A523="","",E523*Calculator!$B$6+Calculator!$B$37+F523+Calculator!$B$30)</f>
+        <f>IF(A523="","",E523*Calculator!$B$6+Calculator!$C$37+F523+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H523" s="16">
@@ -23185,7 +23201,7 @@
         <v/>
       </c>
       <c r="G524" s="16">
-        <f>IF(A524="","",E524*Calculator!$B$6+Calculator!$B$37+F524+Calculator!$B$30)</f>
+        <f>IF(A524="","",E524*Calculator!$B$6+Calculator!$C$37+F524+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H524" s="16">
@@ -23227,7 +23243,7 @@
         <v/>
       </c>
       <c r="G525" s="16">
-        <f>IF(A525="","",E525*Calculator!$B$6+Calculator!$B$37+F525+Calculator!$B$30)</f>
+        <f>IF(A525="","",E525*Calculator!$B$6+Calculator!$C$37+F525+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H525" s="16">
@@ -23269,7 +23285,7 @@
         <v/>
       </c>
       <c r="G526" s="16">
-        <f>IF(A526="","",E526*Calculator!$B$6+Calculator!$B$37+F526+Calculator!$B$30)</f>
+        <f>IF(A526="","",E526*Calculator!$B$6+Calculator!$C$37+F526+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H526" s="16">
@@ -23311,7 +23327,7 @@
         <v/>
       </c>
       <c r="G527" s="16">
-        <f>IF(A527="","",E527*Calculator!$B$6+Calculator!$B$37+F527+Calculator!$B$30)</f>
+        <f>IF(A527="","",E527*Calculator!$B$6+Calculator!$C$37+F527+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H527" s="16">
@@ -23353,7 +23369,7 @@
         <v/>
       </c>
       <c r="G528" s="16">
-        <f>IF(A528="","",E528*Calculator!$B$6+Calculator!$B$37+F528+Calculator!$B$30)</f>
+        <f>IF(A528="","",E528*Calculator!$B$6+Calculator!$C$37+F528+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H528" s="16">
@@ -23395,7 +23411,7 @@
         <v/>
       </c>
       <c r="G529" s="16">
-        <f>IF(A529="","",E529*Calculator!$B$6+Calculator!$B$37+F529+Calculator!$B$30)</f>
+        <f>IF(A529="","",E529*Calculator!$B$6+Calculator!$C$37+F529+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H529" s="16">
@@ -23437,7 +23453,7 @@
         <v/>
       </c>
       <c r="G530" s="16">
-        <f>IF(A530="","",E530*Calculator!$B$6+Calculator!$B$37+F530+Calculator!$B$30)</f>
+        <f>IF(A530="","",E530*Calculator!$B$6+Calculator!$C$37+F530+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H530" s="16">
@@ -23479,7 +23495,7 @@
         <v/>
       </c>
       <c r="G531" s="16">
-        <f>IF(A531="","",E531*Calculator!$B$6+Calculator!$B$37+F531+Calculator!$B$30)</f>
+        <f>IF(A531="","",E531*Calculator!$B$6+Calculator!$C$37+F531+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H531" s="16">
@@ -23521,7 +23537,7 @@
         <v/>
       </c>
       <c r="G532" s="16">
-        <f>IF(A532="","",E532*Calculator!$B$6+Calculator!$B$37+F532+Calculator!$B$30)</f>
+        <f>IF(A532="","",E532*Calculator!$B$6+Calculator!$C$37+F532+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H532" s="16">
@@ -23563,7 +23579,7 @@
         <v/>
       </c>
       <c r="G533" s="16">
-        <f>IF(A533="","",E533*Calculator!$B$6+Calculator!$B$37+F533+Calculator!$B$30)</f>
+        <f>IF(A533="","",E533*Calculator!$B$6+Calculator!$C$37+F533+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H533" s="16">
@@ -23605,7 +23621,7 @@
         <v/>
       </c>
       <c r="G534" s="16">
-        <f>IF(A534="","",E534*Calculator!$B$6+Calculator!$B$37+F534+Calculator!$B$30)</f>
+        <f>IF(A534="","",E534*Calculator!$B$6+Calculator!$C$37+F534+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H534" s="16">
@@ -23647,7 +23663,7 @@
         <v/>
       </c>
       <c r="G535" s="16">
-        <f>IF(A535="","",E535*Calculator!$B$6+Calculator!$B$37+F535+Calculator!$B$30)</f>
+        <f>IF(A535="","",E535*Calculator!$B$6+Calculator!$C$37+F535+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H535" s="16">
@@ -23689,7 +23705,7 @@
         <v/>
       </c>
       <c r="G536" s="16">
-        <f>IF(A536="","",E536*Calculator!$B$6+Calculator!$B$37+F536+Calculator!$B$30)</f>
+        <f>IF(A536="","",E536*Calculator!$B$6+Calculator!$C$37+F536+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H536" s="16">
@@ -23731,7 +23747,7 @@
         <v/>
       </c>
       <c r="G537" s="16">
-        <f>IF(A537="","",E537*Calculator!$B$6+Calculator!$B$37+F537+Calculator!$B$30)</f>
+        <f>IF(A537="","",E537*Calculator!$B$6+Calculator!$C$37+F537+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H537" s="16">
@@ -23773,7 +23789,7 @@
         <v/>
       </c>
       <c r="G538" s="16">
-        <f>IF(A538="","",E538*Calculator!$B$6+Calculator!$B$37+F538+Calculator!$B$30)</f>
+        <f>IF(A538="","",E538*Calculator!$B$6+Calculator!$C$37+F538+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H538" s="16">
@@ -23815,7 +23831,7 @@
         <v/>
       </c>
       <c r="G539" s="16">
-        <f>IF(A539="","",E539*Calculator!$B$6+Calculator!$B$37+F539+Calculator!$B$30)</f>
+        <f>IF(A539="","",E539*Calculator!$B$6+Calculator!$C$37+F539+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H539" s="16">
@@ -23857,7 +23873,7 @@
         <v/>
       </c>
       <c r="G540" s="16">
-        <f>IF(A540="","",E540*Calculator!$B$6+Calculator!$B$37+F540+Calculator!$B$30)</f>
+        <f>IF(A540="","",E540*Calculator!$B$6+Calculator!$C$37+F540+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H540" s="16">
@@ -23899,7 +23915,7 @@
         <v/>
       </c>
       <c r="G541" s="16">
-        <f>IF(A541="","",E541*Calculator!$B$6+Calculator!$B$37+F541+Calculator!$B$30)</f>
+        <f>IF(A541="","",E541*Calculator!$B$6+Calculator!$C$37+F541+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H541" s="16">
@@ -23941,7 +23957,7 @@
         <v/>
       </c>
       <c r="G542" s="16">
-        <f>IF(A542="","",E542*Calculator!$B$6+Calculator!$B$37+F542+Calculator!$B$30)</f>
+        <f>IF(A542="","",E542*Calculator!$B$6+Calculator!$C$37+F542+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H542" s="16">
@@ -23983,7 +23999,7 @@
         <v/>
       </c>
       <c r="G543" s="16">
-        <f>IF(A543="","",E543*Calculator!$B$6+Calculator!$B$37+F543+Calculator!$B$30)</f>
+        <f>IF(A543="","",E543*Calculator!$B$6+Calculator!$C$37+F543+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H543" s="16">
@@ -24025,7 +24041,7 @@
         <v/>
       </c>
       <c r="G544" s="16">
-        <f>IF(A544="","",E544*Calculator!$B$6+Calculator!$B$37+F544+Calculator!$B$30)</f>
+        <f>IF(A544="","",E544*Calculator!$B$6+Calculator!$C$37+F544+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H544" s="16">
@@ -24067,7 +24083,7 @@
         <v/>
       </c>
       <c r="G545" s="16">
-        <f>IF(A545="","",E545*Calculator!$B$6+Calculator!$B$37+F545+Calculator!$B$30)</f>
+        <f>IF(A545="","",E545*Calculator!$B$6+Calculator!$C$37+F545+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H545" s="16">
@@ -24109,7 +24125,7 @@
         <v/>
       </c>
       <c r="G546" s="16">
-        <f>IF(A546="","",E546*Calculator!$B$6+Calculator!$B$37+F546+Calculator!$B$30)</f>
+        <f>IF(A546="","",E546*Calculator!$B$6+Calculator!$C$37+F546+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H546" s="16">
@@ -24151,7 +24167,7 @@
         <v/>
       </c>
       <c r="G547" s="16">
-        <f>IF(A547="","",E547*Calculator!$B$6+Calculator!$B$37+F547+Calculator!$B$30)</f>
+        <f>IF(A547="","",E547*Calculator!$B$6+Calculator!$C$37+F547+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H547" s="16">
@@ -24193,7 +24209,7 @@
         <v/>
       </c>
       <c r="G548" s="16">
-        <f>IF(A548="","",E548*Calculator!$B$6+Calculator!$B$37+F548+Calculator!$B$30)</f>
+        <f>IF(A548="","",E548*Calculator!$B$6+Calculator!$C$37+F548+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H548" s="16">
@@ -24235,7 +24251,7 @@
         <v/>
       </c>
       <c r="G549" s="16">
-        <f>IF(A549="","",E549*Calculator!$B$6+Calculator!$B$37+F549+Calculator!$B$30)</f>
+        <f>IF(A549="","",E549*Calculator!$B$6+Calculator!$C$37+F549+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H549" s="16">
@@ -24277,7 +24293,7 @@
         <v/>
       </c>
       <c r="G550" s="16">
-        <f>IF(A550="","",E550*Calculator!$B$6+Calculator!$B$37+F550+Calculator!$B$30)</f>
+        <f>IF(A550="","",E550*Calculator!$B$6+Calculator!$C$37+F550+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H550" s="16">
@@ -24319,7 +24335,7 @@
         <v/>
       </c>
       <c r="G551" s="16">
-        <f>IF(A551="","",E551*Calculator!$B$6+Calculator!$B$37+F551+Calculator!$B$30)</f>
+        <f>IF(A551="","",E551*Calculator!$B$6+Calculator!$C$37+F551+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H551" s="16">
@@ -24361,7 +24377,7 @@
         <v/>
       </c>
       <c r="G552" s="16">
-        <f>IF(A552="","",E552*Calculator!$B$6+Calculator!$B$37+F552+Calculator!$B$30)</f>
+        <f>IF(A552="","",E552*Calculator!$B$6+Calculator!$C$37+F552+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H552" s="16">
@@ -24403,7 +24419,7 @@
         <v/>
       </c>
       <c r="G553" s="16">
-        <f>IF(A553="","",E553*Calculator!$B$6+Calculator!$B$37+F553+Calculator!$B$30)</f>
+        <f>IF(A553="","",E553*Calculator!$B$6+Calculator!$C$37+F553+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H553" s="16">
@@ -24445,7 +24461,7 @@
         <v/>
       </c>
       <c r="G554" s="16">
-        <f>IF(A554="","",E554*Calculator!$B$6+Calculator!$B$37+F554+Calculator!$B$30)</f>
+        <f>IF(A554="","",E554*Calculator!$B$6+Calculator!$C$37+F554+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H554" s="16">
@@ -24487,7 +24503,7 @@
         <v/>
       </c>
       <c r="G555" s="16">
-        <f>IF(A555="","",E555*Calculator!$B$6+Calculator!$B$37+F555+Calculator!$B$30)</f>
+        <f>IF(A555="","",E555*Calculator!$B$6+Calculator!$C$37+F555+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H555" s="16">
@@ -24529,7 +24545,7 @@
         <v/>
       </c>
       <c r="G556" s="16">
-        <f>IF(A556="","",E556*Calculator!$B$6+Calculator!$B$37+F556+Calculator!$B$30)</f>
+        <f>IF(A556="","",E556*Calculator!$B$6+Calculator!$C$37+F556+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H556" s="16">
@@ -24571,7 +24587,7 @@
         <v/>
       </c>
       <c r="G557" s="16">
-        <f>IF(A557="","",E557*Calculator!$B$6+Calculator!$B$37+F557+Calculator!$B$30)</f>
+        <f>IF(A557="","",E557*Calculator!$B$6+Calculator!$C$37+F557+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H557" s="16">
@@ -24613,7 +24629,7 @@
         <v/>
       </c>
       <c r="G558" s="16">
-        <f>IF(A558="","",E558*Calculator!$B$6+Calculator!$B$37+F558+Calculator!$B$30)</f>
+        <f>IF(A558="","",E558*Calculator!$B$6+Calculator!$C$37+F558+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H558" s="16">
@@ -24655,7 +24671,7 @@
         <v/>
       </c>
       <c r="G559" s="16">
-        <f>IF(A559="","",E559*Calculator!$B$6+Calculator!$B$37+F559+Calculator!$B$30)</f>
+        <f>IF(A559="","",E559*Calculator!$B$6+Calculator!$C$37+F559+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H559" s="16">
@@ -24697,7 +24713,7 @@
         <v/>
       </c>
       <c r="G560" s="16">
-        <f>IF(A560="","",E560*Calculator!$B$6+Calculator!$B$37+F560+Calculator!$B$30)</f>
+        <f>IF(A560="","",E560*Calculator!$B$6+Calculator!$C$37+F560+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H560" s="16">
@@ -24739,7 +24755,7 @@
         <v/>
       </c>
       <c r="G561" s="16">
-        <f>IF(A561="","",E561*Calculator!$B$6+Calculator!$B$37+F561+Calculator!$B$30)</f>
+        <f>IF(A561="","",E561*Calculator!$B$6+Calculator!$C$37+F561+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H561" s="16">
@@ -24781,7 +24797,7 @@
         <v/>
       </c>
       <c r="G562" s="16">
-        <f>IF(A562="","",E562*Calculator!$B$6+Calculator!$B$37+F562+Calculator!$B$30)</f>
+        <f>IF(A562="","",E562*Calculator!$B$6+Calculator!$C$37+F562+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H562" s="16">
@@ -24823,7 +24839,7 @@
         <v/>
       </c>
       <c r="G563" s="16">
-        <f>IF(A563="","",E563*Calculator!$B$6+Calculator!$B$37+F563+Calculator!$B$30)</f>
+        <f>IF(A563="","",E563*Calculator!$B$6+Calculator!$C$37+F563+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H563" s="16">
@@ -24865,7 +24881,7 @@
         <v/>
       </c>
       <c r="G564" s="16">
-        <f>IF(A564="","",E564*Calculator!$B$6+Calculator!$B$37+F564+Calculator!$B$30)</f>
+        <f>IF(A564="","",E564*Calculator!$B$6+Calculator!$C$37+F564+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H564" s="16">
@@ -24907,7 +24923,7 @@
         <v/>
       </c>
       <c r="G565" s="16">
-        <f>IF(A565="","",E565*Calculator!$B$6+Calculator!$B$37+F565+Calculator!$B$30)</f>
+        <f>IF(A565="","",E565*Calculator!$B$6+Calculator!$C$37+F565+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H565" s="16">
@@ -24949,7 +24965,7 @@
         <v/>
       </c>
       <c r="G566" s="16">
-        <f>IF(A566="","",E566*Calculator!$B$6+Calculator!$B$37+F566+Calculator!$B$30)</f>
+        <f>IF(A566="","",E566*Calculator!$B$6+Calculator!$C$37+F566+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H566" s="16">
@@ -24991,7 +25007,7 @@
         <v/>
       </c>
       <c r="G567" s="16">
-        <f>IF(A567="","",E567*Calculator!$B$6+Calculator!$B$37+F567+Calculator!$B$30)</f>
+        <f>IF(A567="","",E567*Calculator!$B$6+Calculator!$C$37+F567+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H567" s="16">
@@ -25033,7 +25049,7 @@
         <v/>
       </c>
       <c r="G568" s="16">
-        <f>IF(A568="","",E568*Calculator!$B$6+Calculator!$B$37+F568+Calculator!$B$30)</f>
+        <f>IF(A568="","",E568*Calculator!$B$6+Calculator!$C$37+F568+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H568" s="16">
@@ -25075,7 +25091,7 @@
         <v/>
       </c>
       <c r="G569" s="16">
-        <f>IF(A569="","",E569*Calculator!$B$6+Calculator!$B$37+F569+Calculator!$B$30)</f>
+        <f>IF(A569="","",E569*Calculator!$B$6+Calculator!$C$37+F569+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H569" s="16">
@@ -25117,7 +25133,7 @@
         <v/>
       </c>
       <c r="G570" s="16">
-        <f>IF(A570="","",E570*Calculator!$B$6+Calculator!$B$37+F570+Calculator!$B$30)</f>
+        <f>IF(A570="","",E570*Calculator!$B$6+Calculator!$C$37+F570+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H570" s="16">
@@ -25159,7 +25175,7 @@
         <v/>
       </c>
       <c r="G571" s="16">
-        <f>IF(A571="","",E571*Calculator!$B$6+Calculator!$B$37+F571+Calculator!$B$30)</f>
+        <f>IF(A571="","",E571*Calculator!$B$6+Calculator!$C$37+F571+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H571" s="16">
@@ -25201,7 +25217,7 @@
         <v/>
       </c>
       <c r="G572" s="16">
-        <f>IF(A572="","",E572*Calculator!$B$6+Calculator!$B$37+F572+Calculator!$B$30)</f>
+        <f>IF(A572="","",E572*Calculator!$B$6+Calculator!$C$37+F572+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H572" s="16">
@@ -25243,7 +25259,7 @@
         <v/>
       </c>
       <c r="G573" s="16">
-        <f>IF(A573="","",E573*Calculator!$B$6+Calculator!$B$37+F573+Calculator!$B$30)</f>
+        <f>IF(A573="","",E573*Calculator!$B$6+Calculator!$C$37+F573+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H573" s="16">
@@ -25285,7 +25301,7 @@
         <v/>
       </c>
       <c r="G574" s="16">
-        <f>IF(A574="","",E574*Calculator!$B$6+Calculator!$B$37+F574+Calculator!$B$30)</f>
+        <f>IF(A574="","",E574*Calculator!$B$6+Calculator!$C$37+F574+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H574" s="16">
@@ -25327,7 +25343,7 @@
         <v/>
       </c>
       <c r="G575" s="16">
-        <f>IF(A575="","",E575*Calculator!$B$6+Calculator!$B$37+F575+Calculator!$B$30)</f>
+        <f>IF(A575="","",E575*Calculator!$B$6+Calculator!$C$37+F575+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H575" s="16">
@@ -25369,7 +25385,7 @@
         <v/>
       </c>
       <c r="G576" s="16">
-        <f>IF(A576="","",E576*Calculator!$B$6+Calculator!$B$37+F576+Calculator!$B$30)</f>
+        <f>IF(A576="","",E576*Calculator!$B$6+Calculator!$C$37+F576+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H576" s="16">
@@ -25411,7 +25427,7 @@
         <v/>
       </c>
       <c r="G577" s="16">
-        <f>IF(A577="","",E577*Calculator!$B$6+Calculator!$B$37+F577+Calculator!$B$30)</f>
+        <f>IF(A577="","",E577*Calculator!$B$6+Calculator!$C$37+F577+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H577" s="16">
@@ -25453,7 +25469,7 @@
         <v/>
       </c>
       <c r="G578" s="16">
-        <f>IF(A578="","",E578*Calculator!$B$6+Calculator!$B$37+F578+Calculator!$B$30)</f>
+        <f>IF(A578="","",E578*Calculator!$B$6+Calculator!$C$37+F578+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H578" s="16">
@@ -25495,7 +25511,7 @@
         <v/>
       </c>
       <c r="G579" s="16">
-        <f>IF(A579="","",E579*Calculator!$B$6+Calculator!$B$37+F579+Calculator!$B$30)</f>
+        <f>IF(A579="","",E579*Calculator!$B$6+Calculator!$C$37+F579+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H579" s="16">
@@ -25537,7 +25553,7 @@
         <v/>
       </c>
       <c r="G580" s="16">
-        <f>IF(A580="","",E580*Calculator!$B$6+Calculator!$B$37+F580+Calculator!$B$30)</f>
+        <f>IF(A580="","",E580*Calculator!$B$6+Calculator!$C$37+F580+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H580" s="16">
@@ -25579,7 +25595,7 @@
         <v/>
       </c>
       <c r="G581" s="16">
-        <f>IF(A581="","",E581*Calculator!$B$6+Calculator!$B$37+F581+Calculator!$B$30)</f>
+        <f>IF(A581="","",E581*Calculator!$B$6+Calculator!$C$37+F581+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H581" s="16">
@@ -25621,7 +25637,7 @@
         <v/>
       </c>
       <c r="G582" s="16">
-        <f>IF(A582="","",E582*Calculator!$B$6+Calculator!$B$37+F582+Calculator!$B$30)</f>
+        <f>IF(A582="","",E582*Calculator!$B$6+Calculator!$C$37+F582+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H582" s="16">
@@ -25663,7 +25679,7 @@
         <v/>
       </c>
       <c r="G583" s="16">
-        <f>IF(A583="","",E583*Calculator!$B$6+Calculator!$B$37+F583+Calculator!$B$30)</f>
+        <f>IF(A583="","",E583*Calculator!$B$6+Calculator!$C$37+F583+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H583" s="16">
@@ -25705,7 +25721,7 @@
         <v/>
       </c>
       <c r="G584" s="16">
-        <f>IF(A584="","",E584*Calculator!$B$6+Calculator!$B$37+F584+Calculator!$B$30)</f>
+        <f>IF(A584="","",E584*Calculator!$B$6+Calculator!$C$37+F584+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H584" s="16">
@@ -25747,7 +25763,7 @@
         <v/>
       </c>
       <c r="G585" s="16">
-        <f>IF(A585="","",E585*Calculator!$B$6+Calculator!$B$37+F585+Calculator!$B$30)</f>
+        <f>IF(A585="","",E585*Calculator!$B$6+Calculator!$C$37+F585+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H585" s="16">
@@ -25789,7 +25805,7 @@
         <v/>
       </c>
       <c r="G586" s="16">
-        <f>IF(A586="","",E586*Calculator!$B$6+Calculator!$B$37+F586+Calculator!$B$30)</f>
+        <f>IF(A586="","",E586*Calculator!$B$6+Calculator!$C$37+F586+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H586" s="16">
@@ -25831,7 +25847,7 @@
         <v/>
       </c>
       <c r="G587" s="16">
-        <f>IF(A587="","",E587*Calculator!$B$6+Calculator!$B$37+F587+Calculator!$B$30)</f>
+        <f>IF(A587="","",E587*Calculator!$B$6+Calculator!$C$37+F587+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H587" s="16">
@@ -25873,7 +25889,7 @@
         <v/>
       </c>
       <c r="G588" s="16">
-        <f>IF(A588="","",E588*Calculator!$B$6+Calculator!$B$37+F588+Calculator!$B$30)</f>
+        <f>IF(A588="","",E588*Calculator!$B$6+Calculator!$C$37+F588+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H588" s="16">
@@ -25915,7 +25931,7 @@
         <v/>
       </c>
       <c r="G589" s="16">
-        <f>IF(A589="","",E589*Calculator!$B$6+Calculator!$B$37+F589+Calculator!$B$30)</f>
+        <f>IF(A589="","",E589*Calculator!$B$6+Calculator!$C$37+F589+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H589" s="16">
@@ -25957,7 +25973,7 @@
         <v/>
       </c>
       <c r="G590" s="16">
-        <f>IF(A590="","",E590*Calculator!$B$6+Calculator!$B$37+F590+Calculator!$B$30)</f>
+        <f>IF(A590="","",E590*Calculator!$B$6+Calculator!$C$37+F590+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H590" s="16">
@@ -25999,7 +26015,7 @@
         <v/>
       </c>
       <c r="G591" s="16">
-        <f>IF(A591="","",E591*Calculator!$B$6+Calculator!$B$37+F591+Calculator!$B$30)</f>
+        <f>IF(A591="","",E591*Calculator!$B$6+Calculator!$C$37+F591+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H591" s="16">
@@ -26041,7 +26057,7 @@
         <v/>
       </c>
       <c r="G592" s="16">
-        <f>IF(A592="","",E592*Calculator!$B$6+Calculator!$B$37+F592+Calculator!$B$30)</f>
+        <f>IF(A592="","",E592*Calculator!$B$6+Calculator!$C$37+F592+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H592" s="16">
@@ -26083,7 +26099,7 @@
         <v/>
       </c>
       <c r="G593" s="16">
-        <f>IF(A593="","",E593*Calculator!$B$6+Calculator!$B$37+F593+Calculator!$B$30)</f>
+        <f>IF(A593="","",E593*Calculator!$B$6+Calculator!$C$37+F593+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H593" s="16">
@@ -26125,7 +26141,7 @@
         <v/>
       </c>
       <c r="G594" s="16">
-        <f>IF(A594="","",E594*Calculator!$B$6+Calculator!$B$37+F594+Calculator!$B$30)</f>
+        <f>IF(A594="","",E594*Calculator!$B$6+Calculator!$C$37+F594+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H594" s="16">
@@ -26167,7 +26183,7 @@
         <v/>
       </c>
       <c r="G595" s="16">
-        <f>IF(A595="","",E595*Calculator!$B$6+Calculator!$B$37+F595+Calculator!$B$30)</f>
+        <f>IF(A595="","",E595*Calculator!$B$6+Calculator!$C$37+F595+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H595" s="16">
@@ -26209,7 +26225,7 @@
         <v/>
       </c>
       <c r="G596" s="16">
-        <f>IF(A596="","",E596*Calculator!$B$6+Calculator!$B$37+F596+Calculator!$B$30)</f>
+        <f>IF(A596="","",E596*Calculator!$B$6+Calculator!$C$37+F596+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H596" s="16">
@@ -26251,7 +26267,7 @@
         <v/>
       </c>
       <c r="G597" s="16">
-        <f>IF(A597="","",E597*Calculator!$B$6+Calculator!$B$37+F597+Calculator!$B$30)</f>
+        <f>IF(A597="","",E597*Calculator!$B$6+Calculator!$C$37+F597+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H597" s="16">
@@ -26293,7 +26309,7 @@
         <v/>
       </c>
       <c r="G598" s="16">
-        <f>IF(A598="","",E598*Calculator!$B$6+Calculator!$B$37+F598+Calculator!$B$30)</f>
+        <f>IF(A598="","",E598*Calculator!$B$6+Calculator!$C$37+F598+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H598" s="16">
@@ -26335,7 +26351,7 @@
         <v/>
       </c>
       <c r="G599" s="16">
-        <f>IF(A599="","",E599*Calculator!$B$6+Calculator!$B$37+F599+Calculator!$B$30)</f>
+        <f>IF(A599="","",E599*Calculator!$B$6+Calculator!$C$37+F599+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H599" s="16">
@@ -26377,7 +26393,7 @@
         <v/>
       </c>
       <c r="G600" s="16">
-        <f>IF(A600="","",E600*Calculator!$B$6+Calculator!$B$37+F600+Calculator!$B$30)</f>
+        <f>IF(A600="","",E600*Calculator!$B$6+Calculator!$C$37+F600+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H600" s="16">
@@ -26419,7 +26435,7 @@
         <v/>
       </c>
       <c r="G601" s="16">
-        <f>IF(A601="","",E601*Calculator!$B$6+Calculator!$B$37+F601+Calculator!$B$30)</f>
+        <f>IF(A601="","",E601*Calculator!$B$6+Calculator!$C$37+F601+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H601" s="16">
@@ -26461,7 +26477,7 @@
         <v/>
       </c>
       <c r="G602" s="16">
-        <f>IF(A602="","",E602*Calculator!$B$6+Calculator!$B$37+F602+Calculator!$B$30)</f>
+        <f>IF(A602="","",E602*Calculator!$B$6+Calculator!$C$37+F602+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H602" s="16">
@@ -26503,7 +26519,7 @@
         <v/>
       </c>
       <c r="G603" s="16">
-        <f>IF(A603="","",E603*Calculator!$B$6+Calculator!$B$37+F603+Calculator!$B$30)</f>
+        <f>IF(A603="","",E603*Calculator!$B$6+Calculator!$C$37+F603+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H603" s="16">
@@ -26545,7 +26561,7 @@
         <v/>
       </c>
       <c r="G604" s="16">
-        <f>IF(A604="","",E604*Calculator!$B$6+Calculator!$B$37+F604+Calculator!$B$30)</f>
+        <f>IF(A604="","",E604*Calculator!$B$6+Calculator!$C$37+F604+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H604" s="16">
@@ -26587,7 +26603,7 @@
         <v/>
       </c>
       <c r="G605" s="16">
-        <f>IF(A605="","",E605*Calculator!$B$6+Calculator!$B$37+F605+Calculator!$B$30)</f>
+        <f>IF(A605="","",E605*Calculator!$B$6+Calculator!$C$37+F605+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H605" s="16">
@@ -26629,7 +26645,7 @@
         <v/>
       </c>
       <c r="G606" s="16">
-        <f>IF(A606="","",E606*Calculator!$B$6+Calculator!$B$37+F606+Calculator!$B$30)</f>
+        <f>IF(A606="","",E606*Calculator!$B$6+Calculator!$C$37+F606+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H606" s="16">
@@ -26671,7 +26687,7 @@
         <v/>
       </c>
       <c r="G607" s="16">
-        <f>IF(A607="","",E607*Calculator!$B$6+Calculator!$B$37+F607+Calculator!$B$30)</f>
+        <f>IF(A607="","",E607*Calculator!$B$6+Calculator!$C$37+F607+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H607" s="16">
@@ -26713,7 +26729,7 @@
         <v/>
       </c>
       <c r="G608" s="16">
-        <f>IF(A608="","",E608*Calculator!$B$6+Calculator!$B$37+F608+Calculator!$B$30)</f>
+        <f>IF(A608="","",E608*Calculator!$B$6+Calculator!$C$37+F608+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H608" s="16">
@@ -26755,7 +26771,7 @@
         <v/>
       </c>
       <c r="G609" s="16">
-        <f>IF(A609="","",E609*Calculator!$B$6+Calculator!$B$37+F609+Calculator!$B$30)</f>
+        <f>IF(A609="","",E609*Calculator!$B$6+Calculator!$C$37+F609+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H609" s="16">
@@ -26797,7 +26813,7 @@
         <v/>
       </c>
       <c r="G610" s="16">
-        <f>IF(A610="","",E610*Calculator!$B$6+Calculator!$B$37+F610+Calculator!$B$30)</f>
+        <f>IF(A610="","",E610*Calculator!$B$6+Calculator!$C$37+F610+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H610" s="16">
@@ -26839,7 +26855,7 @@
         <v/>
       </c>
       <c r="G611" s="16">
-        <f>IF(A611="","",E611*Calculator!$B$6+Calculator!$B$37+F611+Calculator!$B$30)</f>
+        <f>IF(A611="","",E611*Calculator!$B$6+Calculator!$C$37+F611+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H611" s="16">
@@ -26881,7 +26897,7 @@
         <v/>
       </c>
       <c r="G612" s="16">
-        <f>IF(A612="","",E612*Calculator!$B$6+Calculator!$B$37+F612+Calculator!$B$30)</f>
+        <f>IF(A612="","",E612*Calculator!$B$6+Calculator!$C$37+F612+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H612" s="16">
@@ -26923,7 +26939,7 @@
         <v/>
       </c>
       <c r="G613" s="16">
-        <f>IF(A613="","",E613*Calculator!$B$6+Calculator!$B$37+F613+Calculator!$B$30)</f>
+        <f>IF(A613="","",E613*Calculator!$B$6+Calculator!$C$37+F613+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H613" s="16">
@@ -26965,7 +26981,7 @@
         <v/>
       </c>
       <c r="G614" s="16">
-        <f>IF(A614="","",E614*Calculator!$B$6+Calculator!$B$37+F614+Calculator!$B$30)</f>
+        <f>IF(A614="","",E614*Calculator!$B$6+Calculator!$C$37+F614+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H614" s="16">
@@ -27007,7 +27023,7 @@
         <v/>
       </c>
       <c r="G615" s="16">
-        <f>IF(A615="","",E615*Calculator!$B$6+Calculator!$B$37+F615+Calculator!$B$30)</f>
+        <f>IF(A615="","",E615*Calculator!$B$6+Calculator!$C$37+F615+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H615" s="16">
@@ -27049,7 +27065,7 @@
         <v/>
       </c>
       <c r="G616" s="16">
-        <f>IF(A616="","",E616*Calculator!$B$6+Calculator!$B$37+F616+Calculator!$B$30)</f>
+        <f>IF(A616="","",E616*Calculator!$B$6+Calculator!$C$37+F616+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H616" s="16">
@@ -27091,7 +27107,7 @@
         <v/>
       </c>
       <c r="G617" s="16">
-        <f>IF(A617="","",E617*Calculator!$B$6+Calculator!$B$37+F617+Calculator!$B$30)</f>
+        <f>IF(A617="","",E617*Calculator!$B$6+Calculator!$C$37+F617+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H617" s="16">
@@ -27133,7 +27149,7 @@
         <v/>
       </c>
       <c r="G618" s="16">
-        <f>IF(A618="","",E618*Calculator!$B$6+Calculator!$B$37+F618+Calculator!$B$30)</f>
+        <f>IF(A618="","",E618*Calculator!$B$6+Calculator!$C$37+F618+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H618" s="16">
@@ -27175,7 +27191,7 @@
         <v/>
       </c>
       <c r="G619" s="16">
-        <f>IF(A619="","",E619*Calculator!$B$6+Calculator!$B$37+F619+Calculator!$B$30)</f>
+        <f>IF(A619="","",E619*Calculator!$B$6+Calculator!$C$37+F619+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H619" s="16">
@@ -27217,7 +27233,7 @@
         <v/>
       </c>
       <c r="G620" s="16">
-        <f>IF(A620="","",E620*Calculator!$B$6+Calculator!$B$37+F620+Calculator!$B$30)</f>
+        <f>IF(A620="","",E620*Calculator!$B$6+Calculator!$C$37+F620+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H620" s="16">
@@ -27259,7 +27275,7 @@
         <v/>
       </c>
       <c r="G621" s="16">
-        <f>IF(A621="","",E621*Calculator!$B$6+Calculator!$B$37+F621+Calculator!$B$30)</f>
+        <f>IF(A621="","",E621*Calculator!$B$6+Calculator!$C$37+F621+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H621" s="16">
@@ -27301,7 +27317,7 @@
         <v/>
       </c>
       <c r="G622" s="16">
-        <f>IF(A622="","",E622*Calculator!$B$6+Calculator!$B$37+F622+Calculator!$B$30)</f>
+        <f>IF(A622="","",E622*Calculator!$B$6+Calculator!$C$37+F622+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H622" s="16">
@@ -27343,7 +27359,7 @@
         <v/>
       </c>
       <c r="G623" s="16">
-        <f>IF(A623="","",E623*Calculator!$B$6+Calculator!$B$37+F623+Calculator!$B$30)</f>
+        <f>IF(A623="","",E623*Calculator!$B$6+Calculator!$C$37+F623+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H623" s="16">
@@ -27385,7 +27401,7 @@
         <v/>
       </c>
       <c r="G624" s="16">
-        <f>IF(A624="","",E624*Calculator!$B$6+Calculator!$B$37+F624+Calculator!$B$30)</f>
+        <f>IF(A624="","",E624*Calculator!$B$6+Calculator!$C$37+F624+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H624" s="16">
@@ -27427,7 +27443,7 @@
         <v/>
       </c>
       <c r="G625" s="16">
-        <f>IF(A625="","",E625*Calculator!$B$6+Calculator!$B$37+F625+Calculator!$B$30)</f>
+        <f>IF(A625="","",E625*Calculator!$B$6+Calculator!$C$37+F625+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H625" s="16">
@@ -27469,7 +27485,7 @@
         <v/>
       </c>
       <c r="G626" s="16">
-        <f>IF(A626="","",E626*Calculator!$B$6+Calculator!$B$37+F626+Calculator!$B$30)</f>
+        <f>IF(A626="","",E626*Calculator!$B$6+Calculator!$C$37+F626+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H626" s="16">
@@ -27511,7 +27527,7 @@
         <v/>
       </c>
       <c r="G627" s="16">
-        <f>IF(A627="","",E627*Calculator!$B$6+Calculator!$B$37+F627+Calculator!$B$30)</f>
+        <f>IF(A627="","",E627*Calculator!$B$6+Calculator!$C$37+F627+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H627" s="16">
@@ -27553,7 +27569,7 @@
         <v/>
       </c>
       <c r="G628" s="16">
-        <f>IF(A628="","",E628*Calculator!$B$6+Calculator!$B$37+F628+Calculator!$B$30)</f>
+        <f>IF(A628="","",E628*Calculator!$B$6+Calculator!$C$37+F628+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H628" s="16">
@@ -27595,7 +27611,7 @@
         <v/>
       </c>
       <c r="G629" s="16">
-        <f>IF(A629="","",E629*Calculator!$B$6+Calculator!$B$37+F629+Calculator!$B$30)</f>
+        <f>IF(A629="","",E629*Calculator!$B$6+Calculator!$C$37+F629+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H629" s="16">
@@ -27637,7 +27653,7 @@
         <v/>
       </c>
       <c r="G630" s="16">
-        <f>IF(A630="","",E630*Calculator!$B$6+Calculator!$B$37+F630+Calculator!$B$30)</f>
+        <f>IF(A630="","",E630*Calculator!$B$6+Calculator!$C$37+F630+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H630" s="16">
@@ -27679,7 +27695,7 @@
         <v/>
       </c>
       <c r="G631" s="16">
-        <f>IF(A631="","",E631*Calculator!$B$6+Calculator!$B$37+F631+Calculator!$B$30)</f>
+        <f>IF(A631="","",E631*Calculator!$B$6+Calculator!$C$37+F631+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H631" s="16">
@@ -27721,7 +27737,7 @@
         <v/>
       </c>
       <c r="G632" s="16">
-        <f>IF(A632="","",E632*Calculator!$B$6+Calculator!$B$37+F632+Calculator!$B$30)</f>
+        <f>IF(A632="","",E632*Calculator!$B$6+Calculator!$C$37+F632+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H632" s="16">
@@ -27763,7 +27779,7 @@
         <v/>
       </c>
       <c r="G633" s="16">
-        <f>IF(A633="","",E633*Calculator!$B$6+Calculator!$B$37+F633+Calculator!$B$30)</f>
+        <f>IF(A633="","",E633*Calculator!$B$6+Calculator!$C$37+F633+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H633" s="16">
@@ -27805,7 +27821,7 @@
         <v/>
       </c>
       <c r="G634" s="16">
-        <f>IF(A634="","",E634*Calculator!$B$6+Calculator!$B$37+F634+Calculator!$B$30)</f>
+        <f>IF(A634="","",E634*Calculator!$B$6+Calculator!$C$37+F634+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H634" s="16">
@@ -27847,7 +27863,7 @@
         <v/>
       </c>
       <c r="G635" s="16">
-        <f>IF(A635="","",E635*Calculator!$B$6+Calculator!$B$37+F635+Calculator!$B$30)</f>
+        <f>IF(A635="","",E635*Calculator!$B$6+Calculator!$C$37+F635+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H635" s="16">
@@ -27889,7 +27905,7 @@
         <v/>
       </c>
       <c r="G636" s="16">
-        <f>IF(A636="","",E636*Calculator!$B$6+Calculator!$B$37+F636+Calculator!$B$30)</f>
+        <f>IF(A636="","",E636*Calculator!$B$6+Calculator!$C$37+F636+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H636" s="16">
@@ -27931,7 +27947,7 @@
         <v/>
       </c>
       <c r="G637" s="16">
-        <f>IF(A637="","",E637*Calculator!$B$6+Calculator!$B$37+F637+Calculator!$B$30)</f>
+        <f>IF(A637="","",E637*Calculator!$B$6+Calculator!$C$37+F637+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H637" s="16">
@@ -27973,7 +27989,7 @@
         <v/>
       </c>
       <c r="G638" s="16">
-        <f>IF(A638="","",E638*Calculator!$B$6+Calculator!$B$37+F638+Calculator!$B$30)</f>
+        <f>IF(A638="","",E638*Calculator!$B$6+Calculator!$C$37+F638+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H638" s="16">
@@ -28015,7 +28031,7 @@
         <v/>
       </c>
       <c r="G639" s="16">
-        <f>IF(A639="","",E639*Calculator!$B$6+Calculator!$B$37+F639+Calculator!$B$30)</f>
+        <f>IF(A639="","",E639*Calculator!$B$6+Calculator!$C$37+F639+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H639" s="16">
@@ -28057,7 +28073,7 @@
         <v/>
       </c>
       <c r="G640" s="16">
-        <f>IF(A640="","",E640*Calculator!$B$6+Calculator!$B$37+F640+Calculator!$B$30)</f>
+        <f>IF(A640="","",E640*Calculator!$B$6+Calculator!$C$37+F640+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H640" s="16">
@@ -28099,7 +28115,7 @@
         <v/>
       </c>
       <c r="G641" s="16">
-        <f>IF(A641="","",E641*Calculator!$B$6+Calculator!$B$37+F641+Calculator!$B$30)</f>
+        <f>IF(A641="","",E641*Calculator!$B$6+Calculator!$C$37+F641+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H641" s="16">
@@ -28141,7 +28157,7 @@
         <v/>
       </c>
       <c r="G642" s="16">
-        <f>IF(A642="","",E642*Calculator!$B$6+Calculator!$B$37+F642+Calculator!$B$30)</f>
+        <f>IF(A642="","",E642*Calculator!$B$6+Calculator!$C$37+F642+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H642" s="16">
@@ -28183,7 +28199,7 @@
         <v/>
       </c>
       <c r="G643" s="16">
-        <f>IF(A643="","",E643*Calculator!$B$6+Calculator!$B$37+F643+Calculator!$B$30)</f>
+        <f>IF(A643="","",E643*Calculator!$B$6+Calculator!$C$37+F643+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H643" s="16">
@@ -28225,7 +28241,7 @@
         <v/>
       </c>
       <c r="G644" s="16">
-        <f>IF(A644="","",E644*Calculator!$B$6+Calculator!$B$37+F644+Calculator!$B$30)</f>
+        <f>IF(A644="","",E644*Calculator!$B$6+Calculator!$C$37+F644+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H644" s="16">
@@ -28267,7 +28283,7 @@
         <v/>
       </c>
       <c r="G645" s="16">
-        <f>IF(A645="","",E645*Calculator!$B$6+Calculator!$B$37+F645+Calculator!$B$30)</f>
+        <f>IF(A645="","",E645*Calculator!$B$6+Calculator!$C$37+F645+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H645" s="16">
@@ -28309,7 +28325,7 @@
         <v/>
       </c>
       <c r="G646" s="16">
-        <f>IF(A646="","",E646*Calculator!$B$6+Calculator!$B$37+F646+Calculator!$B$30)</f>
+        <f>IF(A646="","",E646*Calculator!$B$6+Calculator!$C$37+F646+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H646" s="16">
@@ -28351,7 +28367,7 @@
         <v/>
       </c>
       <c r="G647" s="16">
-        <f>IF(A647="","",E647*Calculator!$B$6+Calculator!$B$37+F647+Calculator!$B$30)</f>
+        <f>IF(A647="","",E647*Calculator!$B$6+Calculator!$C$37+F647+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H647" s="16">
@@ -28393,7 +28409,7 @@
         <v/>
       </c>
       <c r="G648" s="16">
-        <f>IF(A648="","",E648*Calculator!$B$6+Calculator!$B$37+F648+Calculator!$B$30)</f>
+        <f>IF(A648="","",E648*Calculator!$B$6+Calculator!$C$37+F648+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H648" s="16">
@@ -28435,7 +28451,7 @@
         <v/>
       </c>
       <c r="G649" s="16">
-        <f>IF(A649="","",E649*Calculator!$B$6+Calculator!$B$37+F649+Calculator!$B$30)</f>
+        <f>IF(A649="","",E649*Calculator!$B$6+Calculator!$C$37+F649+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H649" s="16">
@@ -28477,7 +28493,7 @@
         <v/>
       </c>
       <c r="G650" s="16">
-        <f>IF(A650="","",E650*Calculator!$B$6+Calculator!$B$37+F650+Calculator!$B$30)</f>
+        <f>IF(A650="","",E650*Calculator!$B$6+Calculator!$C$37+F650+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H650" s="16">
@@ -28519,7 +28535,7 @@
         <v/>
       </c>
       <c r="G651" s="16">
-        <f>IF(A651="","",E651*Calculator!$B$6+Calculator!$B$37+F651+Calculator!$B$30)</f>
+        <f>IF(A651="","",E651*Calculator!$B$6+Calculator!$C$37+F651+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H651" s="16">
@@ -28561,7 +28577,7 @@
         <v/>
       </c>
       <c r="G652" s="16">
-        <f>IF(A652="","",E652*Calculator!$B$6+Calculator!$B$37+F652+Calculator!$B$30)</f>
+        <f>IF(A652="","",E652*Calculator!$B$6+Calculator!$C$37+F652+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H652" s="16">
@@ -28603,7 +28619,7 @@
         <v/>
       </c>
       <c r="G653" s="16">
-        <f>IF(A653="","",E653*Calculator!$B$6+Calculator!$B$37+F653+Calculator!$B$30)</f>
+        <f>IF(A653="","",E653*Calculator!$B$6+Calculator!$C$37+F653+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H653" s="16">
@@ -28645,7 +28661,7 @@
         <v/>
       </c>
       <c r="G654" s="16">
-        <f>IF(A654="","",E654*Calculator!$B$6+Calculator!$B$37+F654+Calculator!$B$30)</f>
+        <f>IF(A654="","",E654*Calculator!$B$6+Calculator!$C$37+F654+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H654" s="16">
@@ -28687,7 +28703,7 @@
         <v/>
       </c>
       <c r="G655" s="16">
-        <f>IF(A655="","",E655*Calculator!$B$6+Calculator!$B$37+F655+Calculator!$B$30)</f>
+        <f>IF(A655="","",E655*Calculator!$B$6+Calculator!$C$37+F655+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H655" s="16">
@@ -28729,7 +28745,7 @@
         <v/>
       </c>
       <c r="G656" s="16">
-        <f>IF(A656="","",E656*Calculator!$B$6+Calculator!$B$37+F656+Calculator!$B$30)</f>
+        <f>IF(A656="","",E656*Calculator!$B$6+Calculator!$C$37+F656+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H656" s="16">
@@ -28771,7 +28787,7 @@
         <v/>
       </c>
       <c r="G657" s="16">
-        <f>IF(A657="","",E657*Calculator!$B$6+Calculator!$B$37+F657+Calculator!$B$30)</f>
+        <f>IF(A657="","",E657*Calculator!$B$6+Calculator!$C$37+F657+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H657" s="16">
@@ -28813,7 +28829,7 @@
         <v/>
       </c>
       <c r="G658" s="16">
-        <f>IF(A658="","",E658*Calculator!$B$6+Calculator!$B$37+F658+Calculator!$B$30)</f>
+        <f>IF(A658="","",E658*Calculator!$B$6+Calculator!$C$37+F658+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H658" s="16">
@@ -28855,7 +28871,7 @@
         <v/>
       </c>
       <c r="G659" s="16">
-        <f>IF(A659="","",E659*Calculator!$B$6+Calculator!$B$37+F659+Calculator!$B$30)</f>
+        <f>IF(A659="","",E659*Calculator!$B$6+Calculator!$C$37+F659+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H659" s="16">
@@ -28897,7 +28913,7 @@
         <v/>
       </c>
       <c r="G660" s="16">
-        <f>IF(A660="","",E660*Calculator!$B$6+Calculator!$B$37+F660+Calculator!$B$30)</f>
+        <f>IF(A660="","",E660*Calculator!$B$6+Calculator!$C$37+F660+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H660" s="16">
@@ -28939,7 +28955,7 @@
         <v/>
       </c>
       <c r="G661" s="16">
-        <f>IF(A661="","",E661*Calculator!$B$6+Calculator!$B$37+F661+Calculator!$B$30)</f>
+        <f>IF(A661="","",E661*Calculator!$B$6+Calculator!$C$37+F661+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H661" s="16">
@@ -28981,7 +28997,7 @@
         <v/>
       </c>
       <c r="G662" s="16">
-        <f>IF(A662="","",E662*Calculator!$B$6+Calculator!$B$37+F662+Calculator!$B$30)</f>
+        <f>IF(A662="","",E662*Calculator!$B$6+Calculator!$C$37+F662+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H662" s="16">
@@ -29023,7 +29039,7 @@
         <v/>
       </c>
       <c r="G663" s="16">
-        <f>IF(A663="","",E663*Calculator!$B$6+Calculator!$B$37+F663+Calculator!$B$30)</f>
+        <f>IF(A663="","",E663*Calculator!$B$6+Calculator!$C$37+F663+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H663" s="16">
@@ -29065,7 +29081,7 @@
         <v/>
       </c>
       <c r="G664" s="16">
-        <f>IF(A664="","",E664*Calculator!$B$6+Calculator!$B$37+F664+Calculator!$B$30)</f>
+        <f>IF(A664="","",E664*Calculator!$B$6+Calculator!$C$37+F664+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H664" s="16">
@@ -29107,7 +29123,7 @@
         <v/>
       </c>
       <c r="G665" s="16">
-        <f>IF(A665="","",E665*Calculator!$B$6+Calculator!$B$37+F665+Calculator!$B$30)</f>
+        <f>IF(A665="","",E665*Calculator!$B$6+Calculator!$C$37+F665+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H665" s="16">
@@ -29149,7 +29165,7 @@
         <v/>
       </c>
       <c r="G666" s="16">
-        <f>IF(A666="","",E666*Calculator!$B$6+Calculator!$B$37+F666+Calculator!$B$30)</f>
+        <f>IF(A666="","",E666*Calculator!$B$6+Calculator!$C$37+F666+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H666" s="16">
@@ -29191,7 +29207,7 @@
         <v/>
       </c>
       <c r="G667" s="16">
-        <f>IF(A667="","",E667*Calculator!$B$6+Calculator!$B$37+F667+Calculator!$B$30)</f>
+        <f>IF(A667="","",E667*Calculator!$B$6+Calculator!$C$37+F667+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H667" s="16">
@@ -29233,7 +29249,7 @@
         <v/>
       </c>
       <c r="G668" s="16">
-        <f>IF(A668="","",E668*Calculator!$B$6+Calculator!$B$37+F668+Calculator!$B$30)</f>
+        <f>IF(A668="","",E668*Calculator!$B$6+Calculator!$C$37+F668+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H668" s="16">
@@ -29275,7 +29291,7 @@
         <v/>
       </c>
       <c r="G669" s="16">
-        <f>IF(A669="","",E669*Calculator!$B$6+Calculator!$B$37+F669+Calculator!$B$30)</f>
+        <f>IF(A669="","",E669*Calculator!$B$6+Calculator!$C$37+F669+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H669" s="16">
@@ -29317,7 +29333,7 @@
         <v/>
       </c>
       <c r="G670" s="16">
-        <f>IF(A670="","",E670*Calculator!$B$6+Calculator!$B$37+F670+Calculator!$B$30)</f>
+        <f>IF(A670="","",E670*Calculator!$B$6+Calculator!$C$37+F670+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H670" s="16">
@@ -29359,7 +29375,7 @@
         <v/>
       </c>
       <c r="G671" s="16">
-        <f>IF(A671="","",E671*Calculator!$B$6+Calculator!$B$37+F671+Calculator!$B$30)</f>
+        <f>IF(A671="","",E671*Calculator!$B$6+Calculator!$C$37+F671+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H671" s="16">
@@ -29401,7 +29417,7 @@
         <v/>
       </c>
       <c r="G672" s="16">
-        <f>IF(A672="","",E672*Calculator!$B$6+Calculator!$B$37+F672+Calculator!$B$30)</f>
+        <f>IF(A672="","",E672*Calculator!$B$6+Calculator!$C$37+F672+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H672" s="16">
@@ -29443,7 +29459,7 @@
         <v/>
       </c>
       <c r="G673" s="16">
-        <f>IF(A673="","",E673*Calculator!$B$6+Calculator!$B$37+F673+Calculator!$B$30)</f>
+        <f>IF(A673="","",E673*Calculator!$B$6+Calculator!$C$37+F673+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H673" s="16">
@@ -29485,7 +29501,7 @@
         <v/>
       </c>
       <c r="G674" s="16">
-        <f>IF(A674="","",E674*Calculator!$B$6+Calculator!$B$37+F674+Calculator!$B$30)</f>
+        <f>IF(A674="","",E674*Calculator!$B$6+Calculator!$C$37+F674+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H674" s="16">
@@ -29527,7 +29543,7 @@
         <v/>
       </c>
       <c r="G675" s="16">
-        <f>IF(A675="","",E675*Calculator!$B$6+Calculator!$B$37+F675+Calculator!$B$30)</f>
+        <f>IF(A675="","",E675*Calculator!$B$6+Calculator!$C$37+F675+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H675" s="16">
@@ -29569,7 +29585,7 @@
         <v/>
       </c>
       <c r="G676" s="16">
-        <f>IF(A676="","",E676*Calculator!$B$6+Calculator!$B$37+F676+Calculator!$B$30)</f>
+        <f>IF(A676="","",E676*Calculator!$B$6+Calculator!$C$37+F676+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H676" s="16">
@@ -29611,7 +29627,7 @@
         <v/>
       </c>
       <c r="G677" s="16">
-        <f>IF(A677="","",E677*Calculator!$B$6+Calculator!$B$37+F677+Calculator!$B$30)</f>
+        <f>IF(A677="","",E677*Calculator!$B$6+Calculator!$C$37+F677+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H677" s="16">
@@ -29653,7 +29669,7 @@
         <v/>
       </c>
       <c r="G678" s="16">
-        <f>IF(A678="","",E678*Calculator!$B$6+Calculator!$B$37+F678+Calculator!$B$30)</f>
+        <f>IF(A678="","",E678*Calculator!$B$6+Calculator!$C$37+F678+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H678" s="16">
@@ -29695,7 +29711,7 @@
         <v/>
       </c>
       <c r="G679" s="16">
-        <f>IF(A679="","",E679*Calculator!$B$6+Calculator!$B$37+F679+Calculator!$B$30)</f>
+        <f>IF(A679="","",E679*Calculator!$B$6+Calculator!$C$37+F679+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H679" s="16">
@@ -29737,7 +29753,7 @@
         <v/>
       </c>
       <c r="G680" s="16">
-        <f>IF(A680="","",E680*Calculator!$B$6+Calculator!$B$37+F680+Calculator!$B$30)</f>
+        <f>IF(A680="","",E680*Calculator!$B$6+Calculator!$C$37+F680+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H680" s="16">
@@ -29779,7 +29795,7 @@
         <v/>
       </c>
       <c r="G681" s="16">
-        <f>IF(A681="","",E681*Calculator!$B$6+Calculator!$B$37+F681+Calculator!$B$30)</f>
+        <f>IF(A681="","",E681*Calculator!$B$6+Calculator!$C$37+F681+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H681" s="16">
@@ -29821,7 +29837,7 @@
         <v/>
       </c>
       <c r="G682" s="16">
-        <f>IF(A682="","",E682*Calculator!$B$6+Calculator!$B$37+F682+Calculator!$B$30)</f>
+        <f>IF(A682="","",E682*Calculator!$B$6+Calculator!$C$37+F682+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H682" s="16">
@@ -29863,7 +29879,7 @@
         <v/>
       </c>
       <c r="G683" s="16">
-        <f>IF(A683="","",E683*Calculator!$B$6+Calculator!$B$37+F683+Calculator!$B$30)</f>
+        <f>IF(A683="","",E683*Calculator!$B$6+Calculator!$C$37+F683+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H683" s="16">
@@ -29905,7 +29921,7 @@
         <v/>
       </c>
       <c r="G684" s="16">
-        <f>IF(A684="","",E684*Calculator!$B$6+Calculator!$B$37+F684+Calculator!$B$30)</f>
+        <f>IF(A684="","",E684*Calculator!$B$6+Calculator!$C$37+F684+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H684" s="16">
@@ -29947,7 +29963,7 @@
         <v/>
       </c>
       <c r="G685" s="16">
-        <f>IF(A685="","",E685*Calculator!$B$6+Calculator!$B$37+F685+Calculator!$B$30)</f>
+        <f>IF(A685="","",E685*Calculator!$B$6+Calculator!$C$37+F685+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H685" s="16">
@@ -29989,7 +30005,7 @@
         <v/>
       </c>
       <c r="G686" s="16">
-        <f>IF(A686="","",E686*Calculator!$B$6+Calculator!$B$37+F686+Calculator!$B$30)</f>
+        <f>IF(A686="","",E686*Calculator!$B$6+Calculator!$C$37+F686+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H686" s="16">
@@ -30031,7 +30047,7 @@
         <v/>
       </c>
       <c r="G687" s="16">
-        <f>IF(A687="","",E687*Calculator!$B$6+Calculator!$B$37+F687+Calculator!$B$30)</f>
+        <f>IF(A687="","",E687*Calculator!$B$6+Calculator!$C$37+F687+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H687" s="16">
@@ -30073,7 +30089,7 @@
         <v/>
       </c>
       <c r="G688" s="16">
-        <f>IF(A688="","",E688*Calculator!$B$6+Calculator!$B$37+F688+Calculator!$B$30)</f>
+        <f>IF(A688="","",E688*Calculator!$B$6+Calculator!$C$37+F688+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H688" s="16">
@@ -30115,7 +30131,7 @@
         <v/>
       </c>
       <c r="G689" s="16">
-        <f>IF(A689="","",E689*Calculator!$B$6+Calculator!$B$37+F689+Calculator!$B$30)</f>
+        <f>IF(A689="","",E689*Calculator!$B$6+Calculator!$C$37+F689+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H689" s="16">
@@ -30157,7 +30173,7 @@
         <v/>
       </c>
       <c r="G690" s="16">
-        <f>IF(A690="","",E690*Calculator!$B$6+Calculator!$B$37+F690+Calculator!$B$30)</f>
+        <f>IF(A690="","",E690*Calculator!$B$6+Calculator!$C$37+F690+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H690" s="16">
@@ -30199,7 +30215,7 @@
         <v/>
       </c>
       <c r="G691" s="16">
-        <f>IF(A691="","",E691*Calculator!$B$6+Calculator!$B$37+F691+Calculator!$B$30)</f>
+        <f>IF(A691="","",E691*Calculator!$B$6+Calculator!$C$37+F691+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H691" s="16">
@@ -30241,7 +30257,7 @@
         <v/>
       </c>
       <c r="G692" s="16">
-        <f>IF(A692="","",E692*Calculator!$B$6+Calculator!$B$37+F692+Calculator!$B$30)</f>
+        <f>IF(A692="","",E692*Calculator!$B$6+Calculator!$C$37+F692+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H692" s="16">
@@ -30283,7 +30299,7 @@
         <v/>
       </c>
       <c r="G693" s="16">
-        <f>IF(A693="","",E693*Calculator!$B$6+Calculator!$B$37+F693+Calculator!$B$30)</f>
+        <f>IF(A693="","",E693*Calculator!$B$6+Calculator!$C$37+F693+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H693" s="16">
@@ -30325,7 +30341,7 @@
         <v/>
       </c>
       <c r="G694" s="16">
-        <f>IF(A694="","",E694*Calculator!$B$6+Calculator!$B$37+F694+Calculator!$B$30)</f>
+        <f>IF(A694="","",E694*Calculator!$B$6+Calculator!$C$37+F694+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H694" s="16">
@@ -30367,7 +30383,7 @@
         <v/>
       </c>
       <c r="G695" s="16">
-        <f>IF(A695="","",E695*Calculator!$B$6+Calculator!$B$37+F695+Calculator!$B$30)</f>
+        <f>IF(A695="","",E695*Calculator!$B$6+Calculator!$C$37+F695+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H695" s="16">
@@ -30409,7 +30425,7 @@
         <v/>
       </c>
       <c r="G696" s="16">
-        <f>IF(A696="","",E696*Calculator!$B$6+Calculator!$B$37+F696+Calculator!$B$30)</f>
+        <f>IF(A696="","",E696*Calculator!$B$6+Calculator!$C$37+F696+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H696" s="16">
@@ -30451,7 +30467,7 @@
         <v/>
       </c>
       <c r="G697" s="16">
-        <f>IF(A697="","",E697*Calculator!$B$6+Calculator!$B$37+F697+Calculator!$B$30)</f>
+        <f>IF(A697="","",E697*Calculator!$B$6+Calculator!$C$37+F697+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H697" s="16">
@@ -30493,7 +30509,7 @@
         <v/>
       </c>
       <c r="G698" s="16">
-        <f>IF(A698="","",E698*Calculator!$B$6+Calculator!$B$37+F698+Calculator!$B$30)</f>
+        <f>IF(A698="","",E698*Calculator!$B$6+Calculator!$C$37+F698+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H698" s="16">
@@ -30535,7 +30551,7 @@
         <v/>
       </c>
       <c r="G699" s="16">
-        <f>IF(A699="","",E699*Calculator!$B$6+Calculator!$B$37+F699+Calculator!$B$30)</f>
+        <f>IF(A699="","",E699*Calculator!$B$6+Calculator!$C$37+F699+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H699" s="16">
@@ -30577,7 +30593,7 @@
         <v/>
       </c>
       <c r="G700" s="16">
-        <f>IF(A700="","",E700*Calculator!$B$6+Calculator!$B$37+F700+Calculator!$B$30)</f>
+        <f>IF(A700="","",E700*Calculator!$B$6+Calculator!$C$37+F700+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H700" s="16">
@@ -30619,7 +30635,7 @@
         <v/>
       </c>
       <c r="G701" s="16">
-        <f>IF(A701="","",E701*Calculator!$B$6+Calculator!$B$37+F701+Calculator!$B$30)</f>
+        <f>IF(A701="","",E701*Calculator!$B$6+Calculator!$C$37+F701+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H701" s="16">
@@ -30661,7 +30677,7 @@
         <v/>
       </c>
       <c r="G702" s="16">
-        <f>IF(A702="","",E702*Calculator!$B$6+Calculator!$B$37+F702+Calculator!$B$30)</f>
+        <f>IF(A702="","",E702*Calculator!$B$6+Calculator!$C$37+F702+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H702" s="16">
@@ -30703,7 +30719,7 @@
         <v/>
       </c>
       <c r="G703" s="16">
-        <f>IF(A703="","",E703*Calculator!$B$6+Calculator!$B$37+F703+Calculator!$B$30)</f>
+        <f>IF(A703="","",E703*Calculator!$B$6+Calculator!$C$37+F703+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H703" s="16">
@@ -30745,7 +30761,7 @@
         <v/>
       </c>
       <c r="G704" s="16">
-        <f>IF(A704="","",E704*Calculator!$B$6+Calculator!$B$37+F704+Calculator!$B$30)</f>
+        <f>IF(A704="","",E704*Calculator!$B$6+Calculator!$C$37+F704+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H704" s="16">
@@ -30787,7 +30803,7 @@
         <v/>
       </c>
       <c r="G705" s="16">
-        <f>IF(A705="","",E705*Calculator!$B$6+Calculator!$B$37+F705+Calculator!$B$30)</f>
+        <f>IF(A705="","",E705*Calculator!$B$6+Calculator!$C$37+F705+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H705" s="16">
@@ -30829,7 +30845,7 @@
         <v/>
       </c>
       <c r="G706" s="16">
-        <f>IF(A706="","",E706*Calculator!$B$6+Calculator!$B$37+F706+Calculator!$B$30)</f>
+        <f>IF(A706="","",E706*Calculator!$B$6+Calculator!$C$37+F706+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H706" s="16">
@@ -30871,7 +30887,7 @@
         <v/>
       </c>
       <c r="G707" s="16">
-        <f>IF(A707="","",E707*Calculator!$B$6+Calculator!$B$37+F707+Calculator!$B$30)</f>
+        <f>IF(A707="","",E707*Calculator!$B$6+Calculator!$C$37+F707+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H707" s="16">
@@ -30913,7 +30929,7 @@
         <v/>
       </c>
       <c r="G708" s="16">
-        <f>IF(A708="","",E708*Calculator!$B$6+Calculator!$B$37+F708+Calculator!$B$30)</f>
+        <f>IF(A708="","",E708*Calculator!$B$6+Calculator!$C$37+F708+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H708" s="16">
@@ -30955,7 +30971,7 @@
         <v/>
       </c>
       <c r="G709" s="16">
-        <f>IF(A709="","",E709*Calculator!$B$6+Calculator!$B$37+F709+Calculator!$B$30)</f>
+        <f>IF(A709="","",E709*Calculator!$B$6+Calculator!$C$37+F709+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H709" s="16">
@@ -30997,7 +31013,7 @@
         <v/>
       </c>
       <c r="G710" s="16">
-        <f>IF(A710="","",E710*Calculator!$B$6+Calculator!$B$37+F710+Calculator!$B$30)</f>
+        <f>IF(A710="","",E710*Calculator!$B$6+Calculator!$C$37+F710+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H710" s="16">
@@ -31039,7 +31055,7 @@
         <v/>
       </c>
       <c r="G711" s="16">
-        <f>IF(A711="","",E711*Calculator!$B$6+Calculator!$B$37+F711+Calculator!$B$30)</f>
+        <f>IF(A711="","",E711*Calculator!$B$6+Calculator!$C$37+F711+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H711" s="16">
@@ -31081,7 +31097,7 @@
         <v/>
       </c>
       <c r="G712" s="16">
-        <f>IF(A712="","",E712*Calculator!$B$6+Calculator!$B$37+F712+Calculator!$B$30)</f>
+        <f>IF(A712="","",E712*Calculator!$B$6+Calculator!$C$37+F712+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H712" s="16">
@@ -31123,7 +31139,7 @@
         <v/>
       </c>
       <c r="G713" s="16">
-        <f>IF(A713="","",E713*Calculator!$B$6+Calculator!$B$37+F713+Calculator!$B$30)</f>
+        <f>IF(A713="","",E713*Calculator!$B$6+Calculator!$C$37+F713+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H713" s="16">
@@ -31165,7 +31181,7 @@
         <v/>
       </c>
       <c r="G714" s="16">
-        <f>IF(A714="","",E714*Calculator!$B$6+Calculator!$B$37+F714+Calculator!$B$30)</f>
+        <f>IF(A714="","",E714*Calculator!$B$6+Calculator!$C$37+F714+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H714" s="16">
@@ -31207,7 +31223,7 @@
         <v/>
       </c>
       <c r="G715" s="16">
-        <f>IF(A715="","",E715*Calculator!$B$6+Calculator!$B$37+F715+Calculator!$B$30)</f>
+        <f>IF(A715="","",E715*Calculator!$B$6+Calculator!$C$37+F715+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H715" s="16">
@@ -31249,7 +31265,7 @@
         <v/>
       </c>
       <c r="G716" s="16">
-        <f>IF(A716="","",E716*Calculator!$B$6+Calculator!$B$37+F716+Calculator!$B$30)</f>
+        <f>IF(A716="","",E716*Calculator!$B$6+Calculator!$C$37+F716+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H716" s="16">
@@ -31291,7 +31307,7 @@
         <v/>
       </c>
       <c r="G717" s="16">
-        <f>IF(A717="","",E717*Calculator!$B$6+Calculator!$B$37+F717+Calculator!$B$30)</f>
+        <f>IF(A717="","",E717*Calculator!$B$6+Calculator!$C$37+F717+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H717" s="16">
@@ -31333,7 +31349,7 @@
         <v/>
       </c>
       <c r="G718" s="16">
-        <f>IF(A718="","",E718*Calculator!$B$6+Calculator!$B$37+F718+Calculator!$B$30)</f>
+        <f>IF(A718="","",E718*Calculator!$B$6+Calculator!$C$37+F718+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H718" s="16">
@@ -31375,7 +31391,7 @@
         <v/>
       </c>
       <c r="G719" s="16">
-        <f>IF(A719="","",E719*Calculator!$B$6+Calculator!$B$37+F719+Calculator!$B$30)</f>
+        <f>IF(A719="","",E719*Calculator!$B$6+Calculator!$C$37+F719+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H719" s="16">
@@ -31417,7 +31433,7 @@
         <v/>
       </c>
       <c r="G720" s="16">
-        <f>IF(A720="","",E720*Calculator!$B$6+Calculator!$B$37+F720+Calculator!$B$30)</f>
+        <f>IF(A720="","",E720*Calculator!$B$6+Calculator!$C$37+F720+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H720" s="16">
@@ -31459,7 +31475,7 @@
         <v/>
       </c>
       <c r="G721" s="16">
-        <f>IF(A721="","",E721*Calculator!$B$6+Calculator!$B$37+F721+Calculator!$B$30)</f>
+        <f>IF(A721="","",E721*Calculator!$B$6+Calculator!$C$37+F721+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H721" s="16">
@@ -31501,7 +31517,7 @@
         <v/>
       </c>
       <c r="G722" s="16">
-        <f>IF(A722="","",E722*Calculator!$B$6+Calculator!$B$37+F722+Calculator!$B$30)</f>
+        <f>IF(A722="","",E722*Calculator!$B$6+Calculator!$C$37+F722+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H722" s="16">
@@ -31543,7 +31559,7 @@
         <v/>
       </c>
       <c r="G723" s="16">
-        <f>IF(A723="","",E723*Calculator!$B$6+Calculator!$B$37+F723+Calculator!$B$30)</f>
+        <f>IF(A723="","",E723*Calculator!$B$6+Calculator!$C$37+F723+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H723" s="16">
@@ -31585,7 +31601,7 @@
         <v/>
       </c>
       <c r="G724" s="16">
-        <f>IF(A724="","",E724*Calculator!$B$6+Calculator!$B$37+F724+Calculator!$B$30)</f>
+        <f>IF(A724="","",E724*Calculator!$B$6+Calculator!$C$37+F724+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H724" s="16">
@@ -31627,7 +31643,7 @@
         <v/>
       </c>
       <c r="G725" s="16">
-        <f>IF(A725="","",E725*Calculator!$B$6+Calculator!$B$37+F725+Calculator!$B$30)</f>
+        <f>IF(A725="","",E725*Calculator!$B$6+Calculator!$C$37+F725+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H725" s="16">
@@ -31669,7 +31685,7 @@
         <v/>
       </c>
       <c r="G726" s="16">
-        <f>IF(A726="","",E726*Calculator!$B$6+Calculator!$B$37+F726+Calculator!$B$30)</f>
+        <f>IF(A726="","",E726*Calculator!$B$6+Calculator!$C$37+F726+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H726" s="16">
@@ -31711,7 +31727,7 @@
         <v/>
       </c>
       <c r="G727" s="16">
-        <f>IF(A727="","",E727*Calculator!$B$6+Calculator!$B$37+F727+Calculator!$B$30)</f>
+        <f>IF(A727="","",E727*Calculator!$B$6+Calculator!$C$37+F727+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H727" s="16">
@@ -31753,7 +31769,7 @@
         <v/>
       </c>
       <c r="G728" s="16">
-        <f>IF(A728="","",E728*Calculator!$B$6+Calculator!$B$37+F728+Calculator!$B$30)</f>
+        <f>IF(A728="","",E728*Calculator!$B$6+Calculator!$C$37+F728+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H728" s="16">
@@ -31795,7 +31811,7 @@
         <v/>
       </c>
       <c r="G729" s="16">
-        <f>IF(A729="","",E729*Calculator!$B$6+Calculator!$B$37+F729+Calculator!$B$30)</f>
+        <f>IF(A729="","",E729*Calculator!$B$6+Calculator!$C$37+F729+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H729" s="16">
@@ -31837,7 +31853,7 @@
         <v/>
       </c>
       <c r="G730" s="16">
-        <f>IF(A730="","",E730*Calculator!$B$6+Calculator!$B$37+F730+Calculator!$B$30)</f>
+        <f>IF(A730="","",E730*Calculator!$B$6+Calculator!$C$37+F730+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H730" s="16">
@@ -31879,7 +31895,7 @@
         <v/>
       </c>
       <c r="G731" s="16">
-        <f>IF(A731="","",E731*Calculator!$B$6+Calculator!$B$37+F731+Calculator!$B$30)</f>
+        <f>IF(A731="","",E731*Calculator!$B$6+Calculator!$C$37+F731+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H731" s="16">
@@ -31921,7 +31937,7 @@
         <v/>
       </c>
       <c r="G732" s="16">
-        <f>IF(A732="","",E732*Calculator!$B$6+Calculator!$B$37+F732+Calculator!$B$30)</f>
+        <f>IF(A732="","",E732*Calculator!$B$6+Calculator!$C$37+F732+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H732" s="16">
@@ -31963,7 +31979,7 @@
         <v/>
       </c>
       <c r="G733" s="16">
-        <f>IF(A733="","",E733*Calculator!$B$6+Calculator!$B$37+F733+Calculator!$B$30)</f>
+        <f>IF(A733="","",E733*Calculator!$B$6+Calculator!$C$37+F733+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H733" s="16">
@@ -32005,7 +32021,7 @@
         <v/>
       </c>
       <c r="G734" s="16">
-        <f>IF(A734="","",E734*Calculator!$B$6+Calculator!$B$37+F734+Calculator!$B$30)</f>
+        <f>IF(A734="","",E734*Calculator!$B$6+Calculator!$C$37+F734+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H734" s="16">
@@ -32047,7 +32063,7 @@
         <v/>
       </c>
       <c r="G735" s="16">
-        <f>IF(A735="","",E735*Calculator!$B$6+Calculator!$B$37+F735+Calculator!$B$30)</f>
+        <f>IF(A735="","",E735*Calculator!$B$6+Calculator!$C$37+F735+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H735" s="16">
@@ -32089,7 +32105,7 @@
         <v/>
       </c>
       <c r="G736" s="16">
-        <f>IF(A736="","",E736*Calculator!$B$6+Calculator!$B$37+F736+Calculator!$B$30)</f>
+        <f>IF(A736="","",E736*Calculator!$B$6+Calculator!$C$37+F736+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H736" s="16">
@@ -32131,7 +32147,7 @@
         <v/>
       </c>
       <c r="G737" s="16">
-        <f>IF(A737="","",E737*Calculator!$B$6+Calculator!$B$37+F737+Calculator!$B$30)</f>
+        <f>IF(A737="","",E737*Calculator!$B$6+Calculator!$C$37+F737+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H737" s="16">
@@ -32173,7 +32189,7 @@
         <v/>
       </c>
       <c r="G738" s="16">
-        <f>IF(A738="","",E738*Calculator!$B$6+Calculator!$B$37+F738+Calculator!$B$30)</f>
+        <f>IF(A738="","",E738*Calculator!$B$6+Calculator!$C$37+F738+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H738" s="16">
@@ -32215,7 +32231,7 @@
         <v/>
       </c>
       <c r="G739" s="16">
-        <f>IF(A739="","",E739*Calculator!$B$6+Calculator!$B$37+F739+Calculator!$B$30)</f>
+        <f>IF(A739="","",E739*Calculator!$B$6+Calculator!$C$37+F739+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H739" s="16">
@@ -32257,7 +32273,7 @@
         <v/>
       </c>
       <c r="G740" s="16">
-        <f>IF(A740="","",E740*Calculator!$B$6+Calculator!$B$37+F740+Calculator!$B$30)</f>
+        <f>IF(A740="","",E740*Calculator!$B$6+Calculator!$C$37+F740+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H740" s="16">
@@ -32299,7 +32315,7 @@
         <v/>
       </c>
       <c r="G741" s="16">
-        <f>IF(A741="","",E741*Calculator!$B$6+Calculator!$B$37+F741+Calculator!$B$30)</f>
+        <f>IF(A741="","",E741*Calculator!$B$6+Calculator!$C$37+F741+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H741" s="16">
@@ -32341,7 +32357,7 @@
         <v/>
       </c>
       <c r="G742" s="16">
-        <f>IF(A742="","",E742*Calculator!$B$6+Calculator!$B$37+F742+Calculator!$B$30)</f>
+        <f>IF(A742="","",E742*Calculator!$B$6+Calculator!$C$37+F742+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H742" s="16">
@@ -32383,7 +32399,7 @@
         <v/>
       </c>
       <c r="G743" s="16">
-        <f>IF(A743="","",E743*Calculator!$B$6+Calculator!$B$37+F743+Calculator!$B$30)</f>
+        <f>IF(A743="","",E743*Calculator!$B$6+Calculator!$C$37+F743+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H743" s="16">
@@ -32425,7 +32441,7 @@
         <v/>
       </c>
       <c r="G744" s="16">
-        <f>IF(A744="","",E744*Calculator!$B$6+Calculator!$B$37+F744+Calculator!$B$30)</f>
+        <f>IF(A744="","",E744*Calculator!$B$6+Calculator!$C$37+F744+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H744" s="16">
@@ -32467,7 +32483,7 @@
         <v/>
       </c>
       <c r="G745" s="16">
-        <f>IF(A745="","",E745*Calculator!$B$6+Calculator!$B$37+F745+Calculator!$B$30)</f>
+        <f>IF(A745="","",E745*Calculator!$B$6+Calculator!$C$37+F745+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H745" s="16">
@@ -32509,7 +32525,7 @@
         <v/>
       </c>
       <c r="G746" s="16">
-        <f>IF(A746="","",E746*Calculator!$B$6+Calculator!$B$37+F746+Calculator!$B$30)</f>
+        <f>IF(A746="","",E746*Calculator!$B$6+Calculator!$C$37+F746+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H746" s="16">
@@ -32551,7 +32567,7 @@
         <v/>
       </c>
       <c r="G747" s="16">
-        <f>IF(A747="","",E747*Calculator!$B$6+Calculator!$B$37+F747+Calculator!$B$30)</f>
+        <f>IF(A747="","",E747*Calculator!$B$6+Calculator!$C$37+F747+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H747" s="16">
@@ -32593,7 +32609,7 @@
         <v/>
       </c>
       <c r="G748" s="16">
-        <f>IF(A748="","",E748*Calculator!$B$6+Calculator!$B$37+F748+Calculator!$B$30)</f>
+        <f>IF(A748="","",E748*Calculator!$B$6+Calculator!$C$37+F748+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H748" s="16">
@@ -32635,7 +32651,7 @@
         <v/>
       </c>
       <c r="G749" s="16">
-        <f>IF(A749="","",E749*Calculator!$B$6+Calculator!$B$37+F749+Calculator!$B$30)</f>
+        <f>IF(A749="","",E749*Calculator!$B$6+Calculator!$C$37+F749+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H749" s="16">
@@ -32677,7 +32693,7 @@
         <v/>
       </c>
       <c r="G750" s="16">
-        <f>IF(A750="","",E750*Calculator!$B$6+Calculator!$B$37+F750+Calculator!$B$30)</f>
+        <f>IF(A750="","",E750*Calculator!$B$6+Calculator!$C$37+F750+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H750" s="16">
@@ -32719,7 +32735,7 @@
         <v/>
       </c>
       <c r="G751" s="16">
-        <f>IF(A751="","",E751*Calculator!$B$6+Calculator!$B$37+F751+Calculator!$B$30)</f>
+        <f>IF(A751="","",E751*Calculator!$B$6+Calculator!$C$37+F751+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H751" s="16">
@@ -32761,7 +32777,7 @@
         <v/>
       </c>
       <c r="G752" s="16">
-        <f>IF(A752="","",E752*Calculator!$B$6+Calculator!$B$37+F752+Calculator!$B$30)</f>
+        <f>IF(A752="","",E752*Calculator!$B$6+Calculator!$C$37+F752+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H752" s="16">
@@ -32803,7 +32819,7 @@
         <v/>
       </c>
       <c r="G753" s="16">
-        <f>IF(A753="","",E753*Calculator!$B$6+Calculator!$B$37+F753+Calculator!$B$30)</f>
+        <f>IF(A753="","",E753*Calculator!$B$6+Calculator!$C$37+F753+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H753" s="16">
@@ -32845,7 +32861,7 @@
         <v/>
       </c>
       <c r="G754" s="16">
-        <f>IF(A754="","",E754*Calculator!$B$6+Calculator!$B$37+F754+Calculator!$B$30)</f>
+        <f>IF(A754="","",E754*Calculator!$B$6+Calculator!$C$37+F754+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H754" s="16">
@@ -32887,7 +32903,7 @@
         <v/>
       </c>
       <c r="G755" s="16">
-        <f>IF(A755="","",E755*Calculator!$B$6+Calculator!$B$37+F755+Calculator!$B$30)</f>
+        <f>IF(A755="","",E755*Calculator!$B$6+Calculator!$C$37+F755+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H755" s="16">
@@ -32929,7 +32945,7 @@
         <v/>
       </c>
       <c r="G756" s="16">
-        <f>IF(A756="","",E756*Calculator!$B$6+Calculator!$B$37+F756+Calculator!$B$30)</f>
+        <f>IF(A756="","",E756*Calculator!$B$6+Calculator!$C$37+F756+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H756" s="16">
@@ -32971,7 +32987,7 @@
         <v/>
       </c>
       <c r="G757" s="16">
-        <f>IF(A757="","",E757*Calculator!$B$6+Calculator!$B$37+F757+Calculator!$B$30)</f>
+        <f>IF(A757="","",E757*Calculator!$B$6+Calculator!$C$37+F757+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H757" s="16">
@@ -33013,7 +33029,7 @@
         <v/>
       </c>
       <c r="G758" s="16">
-        <f>IF(A758="","",E758*Calculator!$B$6+Calculator!$B$37+F758+Calculator!$B$30)</f>
+        <f>IF(A758="","",E758*Calculator!$B$6+Calculator!$C$37+F758+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H758" s="16">
@@ -33055,7 +33071,7 @@
         <v/>
       </c>
       <c r="G759" s="16">
-        <f>IF(A759="","",E759*Calculator!$B$6+Calculator!$B$37+F759+Calculator!$B$30)</f>
+        <f>IF(A759="","",E759*Calculator!$B$6+Calculator!$C$37+F759+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H759" s="16">
@@ -33097,7 +33113,7 @@
         <v/>
       </c>
       <c r="G760" s="16">
-        <f>IF(A760="","",E760*Calculator!$B$6+Calculator!$B$37+F760+Calculator!$B$30)</f>
+        <f>IF(A760="","",E760*Calculator!$B$6+Calculator!$C$37+F760+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H760" s="16">
@@ -33139,7 +33155,7 @@
         <v/>
       </c>
       <c r="G761" s="16">
-        <f>IF(A761="","",E761*Calculator!$B$6+Calculator!$B$37+F761+Calculator!$B$30)</f>
+        <f>IF(A761="","",E761*Calculator!$B$6+Calculator!$C$37+F761+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H761" s="16">
@@ -33181,7 +33197,7 @@
         <v/>
       </c>
       <c r="G762" s="16">
-        <f>IF(A762="","",E762*Calculator!$B$6+Calculator!$B$37+F762+Calculator!$B$30)</f>
+        <f>IF(A762="","",E762*Calculator!$B$6+Calculator!$C$37+F762+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H762" s="16">
@@ -33223,7 +33239,7 @@
         <v/>
       </c>
       <c r="G763" s="16">
-        <f>IF(A763="","",E763*Calculator!$B$6+Calculator!$B$37+F763+Calculator!$B$30)</f>
+        <f>IF(A763="","",E763*Calculator!$B$6+Calculator!$C$37+F763+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H763" s="16">
@@ -33265,7 +33281,7 @@
         <v/>
       </c>
       <c r="G764" s="16">
-        <f>IF(A764="","",E764*Calculator!$B$6+Calculator!$B$37+F764+Calculator!$B$30)</f>
+        <f>IF(A764="","",E764*Calculator!$B$6+Calculator!$C$37+F764+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H764" s="16">
@@ -33307,7 +33323,7 @@
         <v/>
       </c>
       <c r="G765" s="16">
-        <f>IF(A765="","",E765*Calculator!$B$6+Calculator!$B$37+F765+Calculator!$B$30)</f>
+        <f>IF(A765="","",E765*Calculator!$B$6+Calculator!$C$37+F765+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H765" s="16">
@@ -33349,7 +33365,7 @@
         <v/>
       </c>
       <c r="G766" s="16">
-        <f>IF(A766="","",E766*Calculator!$B$6+Calculator!$B$37+F766+Calculator!$B$30)</f>
+        <f>IF(A766="","",E766*Calculator!$B$6+Calculator!$C$37+F766+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H766" s="16">
@@ -33391,7 +33407,7 @@
         <v/>
       </c>
       <c r="G767" s="16">
-        <f>IF(A767="","",E767*Calculator!$B$6+Calculator!$B$37+F767+Calculator!$B$30)</f>
+        <f>IF(A767="","",E767*Calculator!$B$6+Calculator!$C$37+F767+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H767" s="16">
@@ -33433,7 +33449,7 @@
         <v/>
       </c>
       <c r="G768" s="16">
-        <f>IF(A768="","",E768*Calculator!$B$6+Calculator!$B$37+F768+Calculator!$B$30)</f>
+        <f>IF(A768="","",E768*Calculator!$B$6+Calculator!$C$37+F768+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H768" s="16">
@@ -33475,7 +33491,7 @@
         <v/>
       </c>
       <c r="G769" s="16">
-        <f>IF(A769="","",E769*Calculator!$B$6+Calculator!$B$37+F769+Calculator!$B$30)</f>
+        <f>IF(A769="","",E769*Calculator!$B$6+Calculator!$C$37+F769+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H769" s="16">
@@ -33517,7 +33533,7 @@
         <v/>
       </c>
       <c r="G770" s="16">
-        <f>IF(A770="","",E770*Calculator!$B$6+Calculator!$B$37+F770+Calculator!$B$30)</f>
+        <f>IF(A770="","",E770*Calculator!$B$6+Calculator!$C$37+F770+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H770" s="16">
@@ -33559,7 +33575,7 @@
         <v/>
       </c>
       <c r="G771" s="16">
-        <f>IF(A771="","",E771*Calculator!$B$6+Calculator!$B$37+F771+Calculator!$B$30)</f>
+        <f>IF(A771="","",E771*Calculator!$B$6+Calculator!$C$37+F771+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H771" s="16">
@@ -33601,7 +33617,7 @@
         <v/>
       </c>
       <c r="G772" s="16">
-        <f>IF(A772="","",E772*Calculator!$B$6+Calculator!$B$37+F772+Calculator!$B$30)</f>
+        <f>IF(A772="","",E772*Calculator!$B$6+Calculator!$C$37+F772+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H772" s="16">
@@ -33643,7 +33659,7 @@
         <v/>
       </c>
       <c r="G773" s="16">
-        <f>IF(A773="","",E773*Calculator!$B$6+Calculator!$B$37+F773+Calculator!$B$30)</f>
+        <f>IF(A773="","",E773*Calculator!$B$6+Calculator!$C$37+F773+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H773" s="16">
@@ -33685,7 +33701,7 @@
         <v/>
       </c>
       <c r="G774" s="16">
-        <f>IF(A774="","",E774*Calculator!$B$6+Calculator!$B$37+F774+Calculator!$B$30)</f>
+        <f>IF(A774="","",E774*Calculator!$B$6+Calculator!$C$37+F774+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H774" s="16">
@@ -33727,7 +33743,7 @@
         <v/>
       </c>
       <c r="G775" s="16">
-        <f>IF(A775="","",E775*Calculator!$B$6+Calculator!$B$37+F775+Calculator!$B$30)</f>
+        <f>IF(A775="","",E775*Calculator!$B$6+Calculator!$C$37+F775+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H775" s="16">
@@ -33769,7 +33785,7 @@
         <v/>
       </c>
       <c r="G776" s="16">
-        <f>IF(A776="","",E776*Calculator!$B$6+Calculator!$B$37+F776+Calculator!$B$30)</f>
+        <f>IF(A776="","",E776*Calculator!$B$6+Calculator!$C$37+F776+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H776" s="16">
@@ -33811,7 +33827,7 @@
         <v/>
       </c>
       <c r="G777" s="16">
-        <f>IF(A777="","",E777*Calculator!$B$6+Calculator!$B$37+F777+Calculator!$B$30)</f>
+        <f>IF(A777="","",E777*Calculator!$B$6+Calculator!$C$37+F777+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H777" s="16">
@@ -33853,7 +33869,7 @@
         <v/>
       </c>
       <c r="G778" s="16">
-        <f>IF(A778="","",E778*Calculator!$B$6+Calculator!$B$37+F778+Calculator!$B$30)</f>
+        <f>IF(A778="","",E778*Calculator!$B$6+Calculator!$C$37+F778+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H778" s="16">
@@ -33895,7 +33911,7 @@
         <v/>
       </c>
       <c r="G779" s="16">
-        <f>IF(A779="","",E779*Calculator!$B$6+Calculator!$B$37+F779+Calculator!$B$30)</f>
+        <f>IF(A779="","",E779*Calculator!$B$6+Calculator!$C$37+F779+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H779" s="16">
@@ -33937,7 +33953,7 @@
         <v/>
       </c>
       <c r="G780" s="16">
-        <f>IF(A780="","",E780*Calculator!$B$6+Calculator!$B$37+F780+Calculator!$B$30)</f>
+        <f>IF(A780="","",E780*Calculator!$B$6+Calculator!$C$37+F780+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H780" s="16">
@@ -33979,7 +33995,7 @@
         <v/>
       </c>
       <c r="G781" s="16">
-        <f>IF(A781="","",E781*Calculator!$B$6+Calculator!$B$37+F781+Calculator!$B$30)</f>
+        <f>IF(A781="","",E781*Calculator!$B$6+Calculator!$C$37+F781+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H781" s="16">
@@ -34021,7 +34037,7 @@
         <v/>
       </c>
       <c r="G782" s="16">
-        <f>IF(A782="","",E782*Calculator!$B$6+Calculator!$B$37+F782+Calculator!$B$30)</f>
+        <f>IF(A782="","",E782*Calculator!$B$6+Calculator!$C$37+F782+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H782" s="16">
@@ -34063,7 +34079,7 @@
         <v/>
       </c>
       <c r="G783" s="16">
-        <f>IF(A783="","",E783*Calculator!$B$6+Calculator!$B$37+F783+Calculator!$B$30)</f>
+        <f>IF(A783="","",E783*Calculator!$B$6+Calculator!$C$37+F783+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H783" s="16">
@@ -34105,7 +34121,7 @@
         <v/>
       </c>
       <c r="G784" s="16">
-        <f>IF(A784="","",E784*Calculator!$B$6+Calculator!$B$37+F784+Calculator!$B$30)</f>
+        <f>IF(A784="","",E784*Calculator!$B$6+Calculator!$C$37+F784+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H784" s="16">
@@ -34147,7 +34163,7 @@
         <v/>
       </c>
       <c r="G785" s="16">
-        <f>IF(A785="","",E785*Calculator!$B$6+Calculator!$B$37+F785+Calculator!$B$30)</f>
+        <f>IF(A785="","",E785*Calculator!$B$6+Calculator!$C$37+F785+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H785" s="16">
@@ -34189,7 +34205,7 @@
         <v/>
       </c>
       <c r="G786" s="16">
-        <f>IF(A786="","",E786*Calculator!$B$6+Calculator!$B$37+F786+Calculator!$B$30)</f>
+        <f>IF(A786="","",E786*Calculator!$B$6+Calculator!$C$37+F786+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H786" s="16">
@@ -34231,7 +34247,7 @@
         <v/>
       </c>
       <c r="G787" s="16">
-        <f>IF(A787="","",E787*Calculator!$B$6+Calculator!$B$37+F787+Calculator!$B$30)</f>
+        <f>IF(A787="","",E787*Calculator!$B$6+Calculator!$C$37+F787+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H787" s="16">
@@ -34273,7 +34289,7 @@
         <v/>
       </c>
       <c r="G788" s="16">
-        <f>IF(A788="","",E788*Calculator!$B$6+Calculator!$B$37+F788+Calculator!$B$30)</f>
+        <f>IF(A788="","",E788*Calculator!$B$6+Calculator!$C$37+F788+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H788" s="16">
@@ -34315,7 +34331,7 @@
         <v/>
       </c>
       <c r="G789" s="16">
-        <f>IF(A789="","",E789*Calculator!$B$6+Calculator!$B$37+F789+Calculator!$B$30)</f>
+        <f>IF(A789="","",E789*Calculator!$B$6+Calculator!$C$37+F789+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H789" s="16">
@@ -34357,7 +34373,7 @@
         <v/>
       </c>
       <c r="G790" s="16">
-        <f>IF(A790="","",E790*Calculator!$B$6+Calculator!$B$37+F790+Calculator!$B$30)</f>
+        <f>IF(A790="","",E790*Calculator!$B$6+Calculator!$C$37+F790+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H790" s="16">
@@ -34399,7 +34415,7 @@
         <v/>
       </c>
       <c r="G791" s="16">
-        <f>IF(A791="","",E791*Calculator!$B$6+Calculator!$B$37+F791+Calculator!$B$30)</f>
+        <f>IF(A791="","",E791*Calculator!$B$6+Calculator!$C$37+F791+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H791" s="16">
@@ -34441,7 +34457,7 @@
         <v/>
       </c>
       <c r="G792" s="16">
-        <f>IF(A792="","",E792*Calculator!$B$6+Calculator!$B$37+F792+Calculator!$B$30)</f>
+        <f>IF(A792="","",E792*Calculator!$B$6+Calculator!$C$37+F792+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H792" s="16">
@@ -34483,7 +34499,7 @@
         <v/>
       </c>
       <c r="G793" s="16">
-        <f>IF(A793="","",E793*Calculator!$B$6+Calculator!$B$37+F793+Calculator!$B$30)</f>
+        <f>IF(A793="","",E793*Calculator!$B$6+Calculator!$C$37+F793+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H793" s="16">
@@ -34525,7 +34541,7 @@
         <v/>
       </c>
       <c r="G794" s="16">
-        <f>IF(A794="","",E794*Calculator!$B$6+Calculator!$B$37+F794+Calculator!$B$30)</f>
+        <f>IF(A794="","",E794*Calculator!$B$6+Calculator!$C$37+F794+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H794" s="16">
@@ -34567,7 +34583,7 @@
         <v/>
       </c>
       <c r="G795" s="16">
-        <f>IF(A795="","",E795*Calculator!$B$6+Calculator!$B$37+F795+Calculator!$B$30)</f>
+        <f>IF(A795="","",E795*Calculator!$B$6+Calculator!$C$37+F795+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H795" s="16">
@@ -34609,7 +34625,7 @@
         <v/>
       </c>
       <c r="G796" s="16">
-        <f>IF(A796="","",E796*Calculator!$B$6+Calculator!$B$37+F796+Calculator!$B$30)</f>
+        <f>IF(A796="","",E796*Calculator!$B$6+Calculator!$C$37+F796+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H796" s="16">
@@ -34651,7 +34667,7 @@
         <v/>
       </c>
       <c r="G797" s="16">
-        <f>IF(A797="","",E797*Calculator!$B$6+Calculator!$B$37+F797+Calculator!$B$30)</f>
+        <f>IF(A797="","",E797*Calculator!$B$6+Calculator!$C$37+F797+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H797" s="16">
@@ -34693,7 +34709,7 @@
         <v/>
       </c>
       <c r="G798" s="16">
-        <f>IF(A798="","",E798*Calculator!$B$6+Calculator!$B$37+F798+Calculator!$B$30)</f>
+        <f>IF(A798="","",E798*Calculator!$B$6+Calculator!$C$37+F798+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H798" s="16">
@@ -34735,7 +34751,7 @@
         <v/>
       </c>
       <c r="G799" s="16">
-        <f>IF(A799="","",E799*Calculator!$B$6+Calculator!$B$37+F799+Calculator!$B$30)</f>
+        <f>IF(A799="","",E799*Calculator!$B$6+Calculator!$C$37+F799+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H799" s="16">
@@ -34777,7 +34793,7 @@
         <v/>
       </c>
       <c r="G800" s="16">
-        <f>IF(A800="","",E800*Calculator!$B$6+Calculator!$B$37+F800+Calculator!$B$30)</f>
+        <f>IF(A800="","",E800*Calculator!$B$6+Calculator!$C$37+F800+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H800" s="16">
@@ -34819,7 +34835,7 @@
         <v/>
       </c>
       <c r="G801" s="16">
-        <f>IF(A801="","",E801*Calculator!$B$6+Calculator!$B$37+F801+Calculator!$B$30)</f>
+        <f>IF(A801="","",E801*Calculator!$B$6+Calculator!$C$37+F801+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H801" s="16">
@@ -34861,7 +34877,7 @@
         <v/>
       </c>
       <c r="G802" s="16">
-        <f>IF(A802="","",E802*Calculator!$B$6+Calculator!$B$37+F802+Calculator!$B$30)</f>
+        <f>IF(A802="","",E802*Calculator!$B$6+Calculator!$C$37+F802+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H802" s="16">
@@ -34903,7 +34919,7 @@
         <v/>
       </c>
       <c r="G803" s="16">
-        <f>IF(A803="","",E803*Calculator!$B$6+Calculator!$B$37+F803+Calculator!$B$30)</f>
+        <f>IF(A803="","",E803*Calculator!$B$6+Calculator!$C$37+F803+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H803" s="16">
@@ -34945,7 +34961,7 @@
         <v/>
       </c>
       <c r="G804" s="16">
-        <f>IF(A804="","",E804*Calculator!$B$6+Calculator!$B$37+F804+Calculator!$B$30)</f>
+        <f>IF(A804="","",E804*Calculator!$B$6+Calculator!$C$37+F804+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H804" s="16">
@@ -34987,7 +35003,7 @@
         <v/>
       </c>
       <c r="G805" s="16">
-        <f>IF(A805="","",E805*Calculator!$B$6+Calculator!$B$37+F805+Calculator!$B$30)</f>
+        <f>IF(A805="","",E805*Calculator!$B$6+Calculator!$C$37+F805+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H805" s="16">
@@ -35029,7 +35045,7 @@
         <v/>
       </c>
       <c r="G806" s="16">
-        <f>IF(A806="","",E806*Calculator!$B$6+Calculator!$B$37+F806+Calculator!$B$30)</f>
+        <f>IF(A806="","",E806*Calculator!$B$6+Calculator!$C$37+F806+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H806" s="16">
@@ -35071,7 +35087,7 @@
         <v/>
       </c>
       <c r="G807" s="16">
-        <f>IF(A807="","",E807*Calculator!$B$6+Calculator!$B$37+F807+Calculator!$B$30)</f>
+        <f>IF(A807="","",E807*Calculator!$B$6+Calculator!$C$37+F807+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H807" s="16">
@@ -35113,7 +35129,7 @@
         <v/>
       </c>
       <c r="G808" s="16">
-        <f>IF(A808="","",E808*Calculator!$B$6+Calculator!$B$37+F808+Calculator!$B$30)</f>
+        <f>IF(A808="","",E808*Calculator!$B$6+Calculator!$C$37+F808+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H808" s="16">
@@ -35155,7 +35171,7 @@
         <v/>
       </c>
       <c r="G809" s="16">
-        <f>IF(A809="","",E809*Calculator!$B$6+Calculator!$B$37+F809+Calculator!$B$30)</f>
+        <f>IF(A809="","",E809*Calculator!$B$6+Calculator!$C$37+F809+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H809" s="16">
@@ -35197,7 +35213,7 @@
         <v/>
       </c>
       <c r="G810" s="16">
-        <f>IF(A810="","",E810*Calculator!$B$6+Calculator!$B$37+F810+Calculator!$B$30)</f>
+        <f>IF(A810="","",E810*Calculator!$B$6+Calculator!$C$37+F810+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H810" s="16">
@@ -35239,7 +35255,7 @@
         <v/>
       </c>
       <c r="G811" s="16">
-        <f>IF(A811="","",E811*Calculator!$B$6+Calculator!$B$37+F811+Calculator!$B$30)</f>
+        <f>IF(A811="","",E811*Calculator!$B$6+Calculator!$C$37+F811+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H811" s="16">
@@ -35281,7 +35297,7 @@
         <v/>
       </c>
       <c r="G812" s="16">
-        <f>IF(A812="","",E812*Calculator!$B$6+Calculator!$B$37+F812+Calculator!$B$30)</f>
+        <f>IF(A812="","",E812*Calculator!$B$6+Calculator!$C$37+F812+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H812" s="16">
@@ -35323,7 +35339,7 @@
         <v/>
       </c>
       <c r="G813" s="16">
-        <f>IF(A813="","",E813*Calculator!$B$6+Calculator!$B$37+F813+Calculator!$B$30)</f>
+        <f>IF(A813="","",E813*Calculator!$B$6+Calculator!$C$37+F813+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H813" s="16">
@@ -35365,7 +35381,7 @@
         <v/>
       </c>
       <c r="G814" s="16">
-        <f>IF(A814="","",E814*Calculator!$B$6+Calculator!$B$37+F814+Calculator!$B$30)</f>
+        <f>IF(A814="","",E814*Calculator!$B$6+Calculator!$C$37+F814+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H814" s="16">
@@ -35407,7 +35423,7 @@
         <v/>
       </c>
       <c r="G815" s="16">
-        <f>IF(A815="","",E815*Calculator!$B$6+Calculator!$B$37+F815+Calculator!$B$30)</f>
+        <f>IF(A815="","",E815*Calculator!$B$6+Calculator!$C$37+F815+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H815" s="16">
@@ -35449,7 +35465,7 @@
         <v/>
       </c>
       <c r="G816" s="16">
-        <f>IF(A816="","",E816*Calculator!$B$6+Calculator!$B$37+F816+Calculator!$B$30)</f>
+        <f>IF(A816="","",E816*Calculator!$B$6+Calculator!$C$37+F816+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H816" s="16">
@@ -35491,7 +35507,7 @@
         <v/>
       </c>
       <c r="G817" s="16">
-        <f>IF(A817="","",E817*Calculator!$B$6+Calculator!$B$37+F817+Calculator!$B$30)</f>
+        <f>IF(A817="","",E817*Calculator!$B$6+Calculator!$C$37+F817+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H817" s="16">
@@ -35533,7 +35549,7 @@
         <v/>
       </c>
       <c r="G818" s="16">
-        <f>IF(A818="","",E818*Calculator!$B$6+Calculator!$B$37+F818+Calculator!$B$30)</f>
+        <f>IF(A818="","",E818*Calculator!$B$6+Calculator!$C$37+F818+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H818" s="16">
@@ -35575,7 +35591,7 @@
         <v/>
       </c>
       <c r="G819" s="16">
-        <f>IF(A819="","",E819*Calculator!$B$6+Calculator!$B$37+F819+Calculator!$B$30)</f>
+        <f>IF(A819="","",E819*Calculator!$B$6+Calculator!$C$37+F819+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H819" s="16">
@@ -35617,7 +35633,7 @@
         <v/>
       </c>
       <c r="G820" s="16">
-        <f>IF(A820="","",E820*Calculator!$B$6+Calculator!$B$37+F820+Calculator!$B$30)</f>
+        <f>IF(A820="","",E820*Calculator!$B$6+Calculator!$C$37+F820+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H820" s="16">
@@ -35659,7 +35675,7 @@
         <v/>
       </c>
       <c r="G821" s="16">
-        <f>IF(A821="","",E821*Calculator!$B$6+Calculator!$B$37+F821+Calculator!$B$30)</f>
+        <f>IF(A821="","",E821*Calculator!$B$6+Calculator!$C$37+F821+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H821" s="16">
@@ -35701,7 +35717,7 @@
         <v/>
       </c>
       <c r="G822" s="16">
-        <f>IF(A822="","",E822*Calculator!$B$6+Calculator!$B$37+F822+Calculator!$B$30)</f>
+        <f>IF(A822="","",E822*Calculator!$B$6+Calculator!$C$37+F822+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H822" s="16">
@@ -35743,7 +35759,7 @@
         <v/>
       </c>
       <c r="G823" s="16">
-        <f>IF(A823="","",E823*Calculator!$B$6+Calculator!$B$37+F823+Calculator!$B$30)</f>
+        <f>IF(A823="","",E823*Calculator!$B$6+Calculator!$C$37+F823+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H823" s="16">
@@ -35785,7 +35801,7 @@
         <v/>
       </c>
       <c r="G824" s="16">
-        <f>IF(A824="","",E824*Calculator!$B$6+Calculator!$B$37+F824+Calculator!$B$30)</f>
+        <f>IF(A824="","",E824*Calculator!$B$6+Calculator!$C$37+F824+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H824" s="16">
@@ -35827,7 +35843,7 @@
         <v/>
       </c>
       <c r="G825" s="16">
-        <f>IF(A825="","",E825*Calculator!$B$6+Calculator!$B$37+F825+Calculator!$B$30)</f>
+        <f>IF(A825="","",E825*Calculator!$B$6+Calculator!$C$37+F825+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H825" s="16">
@@ -35869,7 +35885,7 @@
         <v/>
       </c>
       <c r="G826" s="16">
-        <f>IF(A826="","",E826*Calculator!$B$6+Calculator!$B$37+F826+Calculator!$B$30)</f>
+        <f>IF(A826="","",E826*Calculator!$B$6+Calculator!$C$37+F826+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H826" s="16">
@@ -35911,7 +35927,7 @@
         <v/>
       </c>
       <c r="G827" s="16">
-        <f>IF(A827="","",E827*Calculator!$B$6+Calculator!$B$37+F827+Calculator!$B$30)</f>
+        <f>IF(A827="","",E827*Calculator!$B$6+Calculator!$C$37+F827+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H827" s="16">
@@ -35953,7 +35969,7 @@
         <v/>
       </c>
       <c r="G828" s="16">
-        <f>IF(A828="","",E828*Calculator!$B$6+Calculator!$B$37+F828+Calculator!$B$30)</f>
+        <f>IF(A828="","",E828*Calculator!$B$6+Calculator!$C$37+F828+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H828" s="16">
@@ -35995,7 +36011,7 @@
         <v/>
       </c>
       <c r="G829" s="16">
-        <f>IF(A829="","",E829*Calculator!$B$6+Calculator!$B$37+F829+Calculator!$B$30)</f>
+        <f>IF(A829="","",E829*Calculator!$B$6+Calculator!$C$37+F829+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H829" s="16">
@@ -36037,7 +36053,7 @@
         <v/>
       </c>
       <c r="G830" s="16">
-        <f>IF(A830="","",E830*Calculator!$B$6+Calculator!$B$37+F830+Calculator!$B$30)</f>
+        <f>IF(A830="","",E830*Calculator!$B$6+Calculator!$C$37+F830+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H830" s="16">
@@ -36079,7 +36095,7 @@
         <v/>
       </c>
       <c r="G831" s="16">
-        <f>IF(A831="","",E831*Calculator!$B$6+Calculator!$B$37+F831+Calculator!$B$30)</f>
+        <f>IF(A831="","",E831*Calculator!$B$6+Calculator!$C$37+F831+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H831" s="16">
@@ -36121,7 +36137,7 @@
         <v/>
       </c>
       <c r="G832" s="16">
-        <f>IF(A832="","",E832*Calculator!$B$6+Calculator!$B$37+F832+Calculator!$B$30)</f>
+        <f>IF(A832="","",E832*Calculator!$B$6+Calculator!$C$37+F832+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H832" s="16">
@@ -36163,7 +36179,7 @@
         <v/>
       </c>
       <c r="G833" s="16">
-        <f>IF(A833="","",E833*Calculator!$B$6+Calculator!$B$37+F833+Calculator!$B$30)</f>
+        <f>IF(A833="","",E833*Calculator!$B$6+Calculator!$C$37+F833+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H833" s="16">
@@ -36205,7 +36221,7 @@
         <v/>
       </c>
       <c r="G834" s="16">
-        <f>IF(A834="","",E834*Calculator!$B$6+Calculator!$B$37+F834+Calculator!$B$30)</f>
+        <f>IF(A834="","",E834*Calculator!$B$6+Calculator!$C$37+F834+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H834" s="16">
@@ -36247,7 +36263,7 @@
         <v/>
       </c>
       <c r="G835" s="16">
-        <f>IF(A835="","",E835*Calculator!$B$6+Calculator!$B$37+F835+Calculator!$B$30)</f>
+        <f>IF(A835="","",E835*Calculator!$B$6+Calculator!$C$37+F835+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H835" s="16">
@@ -36289,7 +36305,7 @@
         <v/>
       </c>
       <c r="G836" s="16">
-        <f>IF(A836="","",E836*Calculator!$B$6+Calculator!$B$37+F836+Calculator!$B$30)</f>
+        <f>IF(A836="","",E836*Calculator!$B$6+Calculator!$C$37+F836+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H836" s="16">
@@ -36331,7 +36347,7 @@
         <v/>
       </c>
       <c r="G837" s="16">
-        <f>IF(A837="","",E837*Calculator!$B$6+Calculator!$B$37+F837+Calculator!$B$30)</f>
+        <f>IF(A837="","",E837*Calculator!$B$6+Calculator!$C$37+F837+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H837" s="16">
@@ -36373,7 +36389,7 @@
         <v/>
       </c>
       <c r="G838" s="16">
-        <f>IF(A838="","",E838*Calculator!$B$6+Calculator!$B$37+F838+Calculator!$B$30)</f>
+        <f>IF(A838="","",E838*Calculator!$B$6+Calculator!$C$37+F838+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H838" s="16">
@@ -36415,7 +36431,7 @@
         <v/>
       </c>
       <c r="G839" s="16">
-        <f>IF(A839="","",E839*Calculator!$B$6+Calculator!$B$37+F839+Calculator!$B$30)</f>
+        <f>IF(A839="","",E839*Calculator!$B$6+Calculator!$C$37+F839+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H839" s="16">
@@ -36457,7 +36473,7 @@
         <v/>
       </c>
       <c r="G840" s="16">
-        <f>IF(A840="","",E840*Calculator!$B$6+Calculator!$B$37+F840+Calculator!$B$30)</f>
+        <f>IF(A840="","",E840*Calculator!$B$6+Calculator!$C$37+F840+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H840" s="16">
@@ -36499,7 +36515,7 @@
         <v/>
       </c>
       <c r="G841" s="16">
-        <f>IF(A841="","",E841*Calculator!$B$6+Calculator!$B$37+F841+Calculator!$B$30)</f>
+        <f>IF(A841="","",E841*Calculator!$B$6+Calculator!$C$37+F841+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H841" s="16">
@@ -36541,7 +36557,7 @@
         <v/>
       </c>
       <c r="G842" s="16">
-        <f>IF(A842="","",E842*Calculator!$B$6+Calculator!$B$37+F842+Calculator!$B$30)</f>
+        <f>IF(A842="","",E842*Calculator!$B$6+Calculator!$C$37+F842+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H842" s="16">
@@ -36583,7 +36599,7 @@
         <v/>
       </c>
       <c r="G843" s="16">
-        <f>IF(A843="","",E843*Calculator!$B$6+Calculator!$B$37+F843+Calculator!$B$30)</f>
+        <f>IF(A843="","",E843*Calculator!$B$6+Calculator!$C$37+F843+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H843" s="16">
@@ -36625,7 +36641,7 @@
         <v/>
       </c>
       <c r="G844" s="16">
-        <f>IF(A844="","",E844*Calculator!$B$6+Calculator!$B$37+F844+Calculator!$B$30)</f>
+        <f>IF(A844="","",E844*Calculator!$B$6+Calculator!$C$37+F844+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H844" s="16">
@@ -36667,7 +36683,7 @@
         <v/>
       </c>
       <c r="G845" s="16">
-        <f>IF(A845="","",E845*Calculator!$B$6+Calculator!$B$37+F845+Calculator!$B$30)</f>
+        <f>IF(A845="","",E845*Calculator!$B$6+Calculator!$C$37+F845+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H845" s="16">
@@ -36709,7 +36725,7 @@
         <v/>
       </c>
       <c r="G846" s="16">
-        <f>IF(A846="","",E846*Calculator!$B$6+Calculator!$B$37+F846+Calculator!$B$30)</f>
+        <f>IF(A846="","",E846*Calculator!$B$6+Calculator!$C$37+F846+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H846" s="16">
@@ -36751,7 +36767,7 @@
         <v/>
       </c>
       <c r="G847" s="16">
-        <f>IF(A847="","",E847*Calculator!$B$6+Calculator!$B$37+F847+Calculator!$B$30)</f>
+        <f>IF(A847="","",E847*Calculator!$B$6+Calculator!$C$37+F847+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H847" s="16">
@@ -36793,7 +36809,7 @@
         <v/>
       </c>
       <c r="G848" s="16">
-        <f>IF(A848="","",E848*Calculator!$B$6+Calculator!$B$37+F848+Calculator!$B$30)</f>
+        <f>IF(A848="","",E848*Calculator!$B$6+Calculator!$C$37+F848+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H848" s="16">
@@ -36835,7 +36851,7 @@
         <v/>
       </c>
       <c r="G849" s="16">
-        <f>IF(A849="","",E849*Calculator!$B$6+Calculator!$B$37+F849+Calculator!$B$30)</f>
+        <f>IF(A849="","",E849*Calculator!$B$6+Calculator!$C$37+F849+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H849" s="16">
@@ -36877,7 +36893,7 @@
         <v/>
       </c>
       <c r="G850" s="16">
-        <f>IF(A850="","",E850*Calculator!$B$6+Calculator!$B$37+F850+Calculator!$B$30)</f>
+        <f>IF(A850="","",E850*Calculator!$B$6+Calculator!$C$37+F850+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H850" s="16">
@@ -36919,7 +36935,7 @@
         <v/>
       </c>
       <c r="G851" s="16">
-        <f>IF(A851="","",E851*Calculator!$B$6+Calculator!$B$37+F851+Calculator!$B$30)</f>
+        <f>IF(A851="","",E851*Calculator!$B$6+Calculator!$C$37+F851+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H851" s="16">
@@ -36961,7 +36977,7 @@
         <v/>
       </c>
       <c r="G852" s="16">
-        <f>IF(A852="","",E852*Calculator!$B$6+Calculator!$B$37+F852+Calculator!$B$30)</f>
+        <f>IF(A852="","",E852*Calculator!$B$6+Calculator!$C$37+F852+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H852" s="16">
@@ -37003,7 +37019,7 @@
         <v/>
       </c>
       <c r="G853" s="16">
-        <f>IF(A853="","",E853*Calculator!$B$6+Calculator!$B$37+F853+Calculator!$B$30)</f>
+        <f>IF(A853="","",E853*Calculator!$B$6+Calculator!$C$37+F853+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H853" s="16">
@@ -37045,7 +37061,7 @@
         <v/>
       </c>
       <c r="G854" s="16">
-        <f>IF(A854="","",E854*Calculator!$B$6+Calculator!$B$37+F854+Calculator!$B$30)</f>
+        <f>IF(A854="","",E854*Calculator!$B$6+Calculator!$C$37+F854+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H854" s="16">
@@ -37087,7 +37103,7 @@
         <v/>
       </c>
       <c r="G855" s="16">
-        <f>IF(A855="","",E855*Calculator!$B$6+Calculator!$B$37+F855+Calculator!$B$30)</f>
+        <f>IF(A855="","",E855*Calculator!$B$6+Calculator!$C$37+F855+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H855" s="16">
@@ -37129,7 +37145,7 @@
         <v/>
       </c>
       <c r="G856" s="16">
-        <f>IF(A856="","",E856*Calculator!$B$6+Calculator!$B$37+F856+Calculator!$B$30)</f>
+        <f>IF(A856="","",E856*Calculator!$B$6+Calculator!$C$37+F856+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H856" s="16">
@@ -37171,7 +37187,7 @@
         <v/>
       </c>
       <c r="G857" s="16">
-        <f>IF(A857="","",E857*Calculator!$B$6+Calculator!$B$37+F857+Calculator!$B$30)</f>
+        <f>IF(A857="","",E857*Calculator!$B$6+Calculator!$C$37+F857+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H857" s="16">
@@ -37213,7 +37229,7 @@
         <v/>
       </c>
       <c r="G858" s="16">
-        <f>IF(A858="","",E858*Calculator!$B$6+Calculator!$B$37+F858+Calculator!$B$30)</f>
+        <f>IF(A858="","",E858*Calculator!$B$6+Calculator!$C$37+F858+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H858" s="16">
@@ -37255,7 +37271,7 @@
         <v/>
       </c>
       <c r="G859" s="16">
-        <f>IF(A859="","",E859*Calculator!$B$6+Calculator!$B$37+F859+Calculator!$B$30)</f>
+        <f>IF(A859="","",E859*Calculator!$B$6+Calculator!$C$37+F859+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H859" s="16">
@@ -37297,7 +37313,7 @@
         <v/>
       </c>
       <c r="G860" s="16">
-        <f>IF(A860="","",E860*Calculator!$B$6+Calculator!$B$37+F860+Calculator!$B$30)</f>
+        <f>IF(A860="","",E860*Calculator!$B$6+Calculator!$C$37+F860+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H860" s="16">
@@ -37339,7 +37355,7 @@
         <v/>
       </c>
       <c r="G861" s="16">
-        <f>IF(A861="","",E861*Calculator!$B$6+Calculator!$B$37+F861+Calculator!$B$30)</f>
+        <f>IF(A861="","",E861*Calculator!$B$6+Calculator!$C$37+F861+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H861" s="16">
@@ -37381,7 +37397,7 @@
         <v/>
       </c>
       <c r="G862" s="16">
-        <f>IF(A862="","",E862*Calculator!$B$6+Calculator!$B$37+F862+Calculator!$B$30)</f>
+        <f>IF(A862="","",E862*Calculator!$B$6+Calculator!$C$37+F862+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H862" s="16">
@@ -37423,7 +37439,7 @@
         <v/>
       </c>
       <c r="G863" s="16">
-        <f>IF(A863="","",E863*Calculator!$B$6+Calculator!$B$37+F863+Calculator!$B$30)</f>
+        <f>IF(A863="","",E863*Calculator!$B$6+Calculator!$C$37+F863+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H863" s="16">
@@ -37465,7 +37481,7 @@
         <v/>
       </c>
       <c r="G864" s="16">
-        <f>IF(A864="","",E864*Calculator!$B$6+Calculator!$B$37+F864+Calculator!$B$30)</f>
+        <f>IF(A864="","",E864*Calculator!$B$6+Calculator!$C$37+F864+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H864" s="16">
@@ -37507,7 +37523,7 @@
         <v/>
       </c>
       <c r="G865" s="16">
-        <f>IF(A865="","",E865*Calculator!$B$6+Calculator!$B$37+F865+Calculator!$B$30)</f>
+        <f>IF(A865="","",E865*Calculator!$B$6+Calculator!$C$37+F865+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H865" s="16">
@@ -37549,7 +37565,7 @@
         <v/>
       </c>
       <c r="G866" s="16">
-        <f>IF(A866="","",E866*Calculator!$B$6+Calculator!$B$37+F866+Calculator!$B$30)</f>
+        <f>IF(A866="","",E866*Calculator!$B$6+Calculator!$C$37+F866+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H866" s="16">
@@ -37591,7 +37607,7 @@
         <v/>
       </c>
       <c r="G867" s="16">
-        <f>IF(A867="","",E867*Calculator!$B$6+Calculator!$B$37+F867+Calculator!$B$30)</f>
+        <f>IF(A867="","",E867*Calculator!$B$6+Calculator!$C$37+F867+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H867" s="16">
@@ -37633,7 +37649,7 @@
         <v/>
       </c>
       <c r="G868" s="16">
-        <f>IF(A868="","",E868*Calculator!$B$6+Calculator!$B$37+F868+Calculator!$B$30)</f>
+        <f>IF(A868="","",E868*Calculator!$B$6+Calculator!$C$37+F868+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H868" s="16">
@@ -37675,7 +37691,7 @@
         <v/>
       </c>
       <c r="G869" s="16">
-        <f>IF(A869="","",E869*Calculator!$B$6+Calculator!$B$37+F869+Calculator!$B$30)</f>
+        <f>IF(A869="","",E869*Calculator!$B$6+Calculator!$C$37+F869+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H869" s="16">
@@ -37717,7 +37733,7 @@
         <v/>
       </c>
       <c r="G870" s="16">
-        <f>IF(A870="","",E870*Calculator!$B$6+Calculator!$B$37+F870+Calculator!$B$30)</f>
+        <f>IF(A870="","",E870*Calculator!$B$6+Calculator!$C$37+F870+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H870" s="16">
@@ -37759,7 +37775,7 @@
         <v/>
       </c>
       <c r="G871" s="16">
-        <f>IF(A871="","",E871*Calculator!$B$6+Calculator!$B$37+F871+Calculator!$B$30)</f>
+        <f>IF(A871="","",E871*Calculator!$B$6+Calculator!$C$37+F871+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H871" s="16">
@@ -37801,7 +37817,7 @@
         <v/>
       </c>
       <c r="G872" s="16">
-        <f>IF(A872="","",E872*Calculator!$B$6+Calculator!$B$37+F872+Calculator!$B$30)</f>
+        <f>IF(A872="","",E872*Calculator!$B$6+Calculator!$C$37+F872+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H872" s="16">
@@ -37843,7 +37859,7 @@
         <v/>
       </c>
       <c r="G873" s="16">
-        <f>IF(A873="","",E873*Calculator!$B$6+Calculator!$B$37+F873+Calculator!$B$30)</f>
+        <f>IF(A873="","",E873*Calculator!$B$6+Calculator!$C$37+F873+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H873" s="16">
@@ -37885,7 +37901,7 @@
         <v/>
       </c>
       <c r="G874" s="16">
-        <f>IF(A874="","",E874*Calculator!$B$6+Calculator!$B$37+F874+Calculator!$B$30)</f>
+        <f>IF(A874="","",E874*Calculator!$B$6+Calculator!$C$37+F874+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H874" s="16">
@@ -37927,7 +37943,7 @@
         <v/>
       </c>
       <c r="G875" s="16">
-        <f>IF(A875="","",E875*Calculator!$B$6+Calculator!$B$37+F875+Calculator!$B$30)</f>
+        <f>IF(A875="","",E875*Calculator!$B$6+Calculator!$C$37+F875+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H875" s="16">
@@ -37969,7 +37985,7 @@
         <v/>
       </c>
       <c r="G876" s="16">
-        <f>IF(A876="","",E876*Calculator!$B$6+Calculator!$B$37+F876+Calculator!$B$30)</f>
+        <f>IF(A876="","",E876*Calculator!$B$6+Calculator!$C$37+F876+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H876" s="16">
@@ -38011,7 +38027,7 @@
         <v/>
       </c>
       <c r="G877" s="16">
-        <f>IF(A877="","",E877*Calculator!$B$6+Calculator!$B$37+F877+Calculator!$B$30)</f>
+        <f>IF(A877="","",E877*Calculator!$B$6+Calculator!$C$37+F877+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H877" s="16">
@@ -38053,7 +38069,7 @@
         <v/>
       </c>
       <c r="G878" s="16">
-        <f>IF(A878="","",E878*Calculator!$B$6+Calculator!$B$37+F878+Calculator!$B$30)</f>
+        <f>IF(A878="","",E878*Calculator!$B$6+Calculator!$C$37+F878+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H878" s="16">
@@ -38095,7 +38111,7 @@
         <v/>
       </c>
       <c r="G879" s="16">
-        <f>IF(A879="","",E879*Calculator!$B$6+Calculator!$B$37+F879+Calculator!$B$30)</f>
+        <f>IF(A879="","",E879*Calculator!$B$6+Calculator!$C$37+F879+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H879" s="16">
@@ -38137,7 +38153,7 @@
         <v/>
       </c>
       <c r="G880" s="16">
-        <f>IF(A880="","",E880*Calculator!$B$6+Calculator!$B$37+F880+Calculator!$B$30)</f>
+        <f>IF(A880="","",E880*Calculator!$B$6+Calculator!$C$37+F880+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H880" s="16">
@@ -38179,7 +38195,7 @@
         <v/>
       </c>
       <c r="G881" s="16">
-        <f>IF(A881="","",E881*Calculator!$B$6+Calculator!$B$37+F881+Calculator!$B$30)</f>
+        <f>IF(A881="","",E881*Calculator!$B$6+Calculator!$C$37+F881+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H881" s="16">
@@ -38221,7 +38237,7 @@
         <v/>
       </c>
       <c r="G882" s="16">
-        <f>IF(A882="","",E882*Calculator!$B$6+Calculator!$B$37+F882+Calculator!$B$30)</f>
+        <f>IF(A882="","",E882*Calculator!$B$6+Calculator!$C$37+F882+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H882" s="16">
@@ -38263,7 +38279,7 @@
         <v/>
       </c>
       <c r="G883" s="16">
-        <f>IF(A883="","",E883*Calculator!$B$6+Calculator!$B$37+F883+Calculator!$B$30)</f>
+        <f>IF(A883="","",E883*Calculator!$B$6+Calculator!$C$37+F883+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H883" s="16">
@@ -38305,7 +38321,7 @@
         <v/>
       </c>
       <c r="G884" s="16">
-        <f>IF(A884="","",E884*Calculator!$B$6+Calculator!$B$37+F884+Calculator!$B$30)</f>
+        <f>IF(A884="","",E884*Calculator!$B$6+Calculator!$C$37+F884+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H884" s="16">
@@ -38347,7 +38363,7 @@
         <v/>
       </c>
       <c r="G885" s="16">
-        <f>IF(A885="","",E885*Calculator!$B$6+Calculator!$B$37+F885+Calculator!$B$30)</f>
+        <f>IF(A885="","",E885*Calculator!$B$6+Calculator!$C$37+F885+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H885" s="16">
@@ -38389,7 +38405,7 @@
         <v/>
       </c>
       <c r="G886" s="16">
-        <f>IF(A886="","",E886*Calculator!$B$6+Calculator!$B$37+F886+Calculator!$B$30)</f>
+        <f>IF(A886="","",E886*Calculator!$B$6+Calculator!$C$37+F886+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H886" s="16">
@@ -38431,7 +38447,7 @@
         <v/>
       </c>
       <c r="G887" s="16">
-        <f>IF(A887="","",E887*Calculator!$B$6+Calculator!$B$37+F887+Calculator!$B$30)</f>
+        <f>IF(A887="","",E887*Calculator!$B$6+Calculator!$C$37+F887+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H887" s="16">
@@ -38473,7 +38489,7 @@
         <v/>
       </c>
       <c r="G888" s="16">
-        <f>IF(A888="","",E888*Calculator!$B$6+Calculator!$B$37+F888+Calculator!$B$30)</f>
+        <f>IF(A888="","",E888*Calculator!$B$6+Calculator!$C$37+F888+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H888" s="16">
@@ -38515,7 +38531,7 @@
         <v/>
       </c>
       <c r="G889" s="16">
-        <f>IF(A889="","",E889*Calculator!$B$6+Calculator!$B$37+F889+Calculator!$B$30)</f>
+        <f>IF(A889="","",E889*Calculator!$B$6+Calculator!$C$37+F889+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H889" s="16">
@@ -38557,7 +38573,7 @@
         <v/>
       </c>
       <c r="G890" s="16">
-        <f>IF(A890="","",E890*Calculator!$B$6+Calculator!$B$37+F890+Calculator!$B$30)</f>
+        <f>IF(A890="","",E890*Calculator!$B$6+Calculator!$C$37+F890+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H890" s="16">
@@ -38599,7 +38615,7 @@
         <v/>
       </c>
       <c r="G891" s="16">
-        <f>IF(A891="","",E891*Calculator!$B$6+Calculator!$B$37+F891+Calculator!$B$30)</f>
+        <f>IF(A891="","",E891*Calculator!$B$6+Calculator!$C$37+F891+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H891" s="16">
@@ -38641,7 +38657,7 @@
         <v/>
       </c>
       <c r="G892" s="16">
-        <f>IF(A892="","",E892*Calculator!$B$6+Calculator!$B$37+F892+Calculator!$B$30)</f>
+        <f>IF(A892="","",E892*Calculator!$B$6+Calculator!$C$37+F892+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H892" s="16">
@@ -38683,7 +38699,7 @@
         <v/>
       </c>
       <c r="G893" s="16">
-        <f>IF(A893="","",E893*Calculator!$B$6+Calculator!$B$37+F893+Calculator!$B$30)</f>
+        <f>IF(A893="","",E893*Calculator!$B$6+Calculator!$C$37+F893+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H893" s="16">
@@ -38725,7 +38741,7 @@
         <v/>
       </c>
       <c r="G894" s="16">
-        <f>IF(A894="","",E894*Calculator!$B$6+Calculator!$B$37+F894+Calculator!$B$30)</f>
+        <f>IF(A894="","",E894*Calculator!$B$6+Calculator!$C$37+F894+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H894" s="16">
@@ -38767,7 +38783,7 @@
         <v/>
       </c>
       <c r="G895" s="16">
-        <f>IF(A895="","",E895*Calculator!$B$6+Calculator!$B$37+F895+Calculator!$B$30)</f>
+        <f>IF(A895="","",E895*Calculator!$B$6+Calculator!$C$37+F895+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H895" s="16">
@@ -38809,7 +38825,7 @@
         <v/>
       </c>
       <c r="G896" s="16">
-        <f>IF(A896="","",E896*Calculator!$B$6+Calculator!$B$37+F896+Calculator!$B$30)</f>
+        <f>IF(A896="","",E896*Calculator!$B$6+Calculator!$C$37+F896+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H896" s="16">
@@ -38851,7 +38867,7 @@
         <v/>
       </c>
       <c r="G897" s="16">
-        <f>IF(A897="","",E897*Calculator!$B$6+Calculator!$B$37+F897+Calculator!$B$30)</f>
+        <f>IF(A897="","",E897*Calculator!$B$6+Calculator!$C$37+F897+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H897" s="16">
@@ -38893,7 +38909,7 @@
         <v/>
       </c>
       <c r="G898" s="16">
-        <f>IF(A898="","",E898*Calculator!$B$6+Calculator!$B$37+F898+Calculator!$B$30)</f>
+        <f>IF(A898="","",E898*Calculator!$B$6+Calculator!$C$37+F898+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H898" s="16">
@@ -38935,7 +38951,7 @@
         <v/>
       </c>
       <c r="G899" s="16">
-        <f>IF(A899="","",E899*Calculator!$B$6+Calculator!$B$37+F899+Calculator!$B$30)</f>
+        <f>IF(A899="","",E899*Calculator!$B$6+Calculator!$C$37+F899+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H899" s="16">
@@ -38977,7 +38993,7 @@
         <v/>
       </c>
       <c r="G900" s="16">
-        <f>IF(A900="","",E900*Calculator!$B$6+Calculator!$B$37+F900+Calculator!$B$30)</f>
+        <f>IF(A900="","",E900*Calculator!$B$6+Calculator!$C$37+F900+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H900" s="16">
@@ -39019,7 +39035,7 @@
         <v/>
       </c>
       <c r="G901" s="16">
-        <f>IF(A901="","",E901*Calculator!$B$6+Calculator!$B$37+F901+Calculator!$B$30)</f>
+        <f>IF(A901="","",E901*Calculator!$B$6+Calculator!$C$37+F901+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H901" s="16">
@@ -39061,7 +39077,7 @@
         <v/>
       </c>
       <c r="G902" s="16">
-        <f>IF(A902="","",E902*Calculator!$B$6+Calculator!$B$37+F902+Calculator!$B$30)</f>
+        <f>IF(A902="","",E902*Calculator!$B$6+Calculator!$C$37+F902+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H902" s="16">
@@ -39103,7 +39119,7 @@
         <v/>
       </c>
       <c r="G903" s="16">
-        <f>IF(A903="","",E903*Calculator!$B$6+Calculator!$B$37+F903+Calculator!$B$30)</f>
+        <f>IF(A903="","",E903*Calculator!$B$6+Calculator!$C$37+F903+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H903" s="16">
@@ -39145,7 +39161,7 @@
         <v/>
       </c>
       <c r="G904" s="16">
-        <f>IF(A904="","",E904*Calculator!$B$6+Calculator!$B$37+F904+Calculator!$B$30)</f>
+        <f>IF(A904="","",E904*Calculator!$B$6+Calculator!$C$37+F904+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H904" s="16">
@@ -39187,7 +39203,7 @@
         <v/>
       </c>
       <c r="G905" s="16">
-        <f>IF(A905="","",E905*Calculator!$B$6+Calculator!$B$37+F905+Calculator!$B$30)</f>
+        <f>IF(A905="","",E905*Calculator!$B$6+Calculator!$C$37+F905+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H905" s="16">
@@ -39229,7 +39245,7 @@
         <v/>
       </c>
       <c r="G906" s="16">
-        <f>IF(A906="","",E906*Calculator!$B$6+Calculator!$B$37+F906+Calculator!$B$30)</f>
+        <f>IF(A906="","",E906*Calculator!$B$6+Calculator!$C$37+F906+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H906" s="16">
@@ -39271,7 +39287,7 @@
         <v/>
       </c>
       <c r="G907" s="16">
-        <f>IF(A907="","",E907*Calculator!$B$6+Calculator!$B$37+F907+Calculator!$B$30)</f>
+        <f>IF(A907="","",E907*Calculator!$B$6+Calculator!$C$37+F907+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H907" s="16">
@@ -39313,7 +39329,7 @@
         <v/>
       </c>
       <c r="G908" s="16">
-        <f>IF(A908="","",E908*Calculator!$B$6+Calculator!$B$37+F908+Calculator!$B$30)</f>
+        <f>IF(A908="","",E908*Calculator!$B$6+Calculator!$C$37+F908+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H908" s="16">
@@ -39355,7 +39371,7 @@
         <v/>
       </c>
       <c r="G909" s="16">
-        <f>IF(A909="","",E909*Calculator!$B$6+Calculator!$B$37+F909+Calculator!$B$30)</f>
+        <f>IF(A909="","",E909*Calculator!$B$6+Calculator!$C$37+F909+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H909" s="16">
@@ -39397,7 +39413,7 @@
         <v/>
       </c>
       <c r="G910" s="16">
-        <f>IF(A910="","",E910*Calculator!$B$6+Calculator!$B$37+F910+Calculator!$B$30)</f>
+        <f>IF(A910="","",E910*Calculator!$B$6+Calculator!$C$37+F910+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H910" s="16">
@@ -39439,7 +39455,7 @@
         <v/>
       </c>
       <c r="G911" s="16">
-        <f>IF(A911="","",E911*Calculator!$B$6+Calculator!$B$37+F911+Calculator!$B$30)</f>
+        <f>IF(A911="","",E911*Calculator!$B$6+Calculator!$C$37+F911+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H911" s="16">
@@ -39481,7 +39497,7 @@
         <v/>
       </c>
       <c r="G912" s="16">
-        <f>IF(A912="","",E912*Calculator!$B$6+Calculator!$B$37+F912+Calculator!$B$30)</f>
+        <f>IF(A912="","",E912*Calculator!$B$6+Calculator!$C$37+F912+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H912" s="16">
@@ -39523,7 +39539,7 @@
         <v/>
       </c>
       <c r="G913" s="16">
-        <f>IF(A913="","",E913*Calculator!$B$6+Calculator!$B$37+F913+Calculator!$B$30)</f>
+        <f>IF(A913="","",E913*Calculator!$B$6+Calculator!$C$37+F913+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H913" s="16">
@@ -39565,7 +39581,7 @@
         <v/>
       </c>
       <c r="G914" s="16">
-        <f>IF(A914="","",E914*Calculator!$B$6+Calculator!$B$37+F914+Calculator!$B$30)</f>
+        <f>IF(A914="","",E914*Calculator!$B$6+Calculator!$C$37+F914+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H914" s="16">
@@ -39607,7 +39623,7 @@
         <v/>
       </c>
       <c r="G915" s="16">
-        <f>IF(A915="","",E915*Calculator!$B$6+Calculator!$B$37+F915+Calculator!$B$30)</f>
+        <f>IF(A915="","",E915*Calculator!$B$6+Calculator!$C$37+F915+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H915" s="16">
@@ -39649,7 +39665,7 @@
         <v/>
       </c>
       <c r="G916" s="16">
-        <f>IF(A916="","",E916*Calculator!$B$6+Calculator!$B$37+F916+Calculator!$B$30)</f>
+        <f>IF(A916="","",E916*Calculator!$B$6+Calculator!$C$37+F916+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H916" s="16">
@@ -39691,7 +39707,7 @@
         <v/>
       </c>
       <c r="G917" s="16">
-        <f>IF(A917="","",E917*Calculator!$B$6+Calculator!$B$37+F917+Calculator!$B$30)</f>
+        <f>IF(A917="","",E917*Calculator!$B$6+Calculator!$C$37+F917+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H917" s="16">
@@ -39733,7 +39749,7 @@
         <v/>
       </c>
       <c r="G918" s="16">
-        <f>IF(A918="","",E918*Calculator!$B$6+Calculator!$B$37+F918+Calculator!$B$30)</f>
+        <f>IF(A918="","",E918*Calculator!$B$6+Calculator!$C$37+F918+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H918" s="16">
@@ -39775,7 +39791,7 @@
         <v/>
       </c>
       <c r="G919" s="16">
-        <f>IF(A919="","",E919*Calculator!$B$6+Calculator!$B$37+F919+Calculator!$B$30)</f>
+        <f>IF(A919="","",E919*Calculator!$B$6+Calculator!$C$37+F919+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H919" s="16">
@@ -39817,7 +39833,7 @@
         <v/>
       </c>
       <c r="G920" s="16">
-        <f>IF(A920="","",E920*Calculator!$B$6+Calculator!$B$37+F920+Calculator!$B$30)</f>
+        <f>IF(A920="","",E920*Calculator!$B$6+Calculator!$C$37+F920+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H920" s="16">
@@ -39859,7 +39875,7 @@
         <v/>
       </c>
       <c r="G921" s="16">
-        <f>IF(A921="","",E921*Calculator!$B$6+Calculator!$B$37+F921+Calculator!$B$30)</f>
+        <f>IF(A921="","",E921*Calculator!$B$6+Calculator!$C$37+F921+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H921" s="16">
@@ -39901,7 +39917,7 @@
         <v/>
       </c>
       <c r="G922" s="16">
-        <f>IF(A922="","",E922*Calculator!$B$6+Calculator!$B$37+F922+Calculator!$B$30)</f>
+        <f>IF(A922="","",E922*Calculator!$B$6+Calculator!$C$37+F922+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H922" s="16">
@@ -39943,7 +39959,7 @@
         <v/>
       </c>
       <c r="G923" s="16">
-        <f>IF(A923="","",E923*Calculator!$B$6+Calculator!$B$37+F923+Calculator!$B$30)</f>
+        <f>IF(A923="","",E923*Calculator!$B$6+Calculator!$C$37+F923+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H923" s="16">
@@ -39985,7 +40001,7 @@
         <v/>
       </c>
       <c r="G924" s="16">
-        <f>IF(A924="","",E924*Calculator!$B$6+Calculator!$B$37+F924+Calculator!$B$30)</f>
+        <f>IF(A924="","",E924*Calculator!$B$6+Calculator!$C$37+F924+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H924" s="16">
@@ -40027,7 +40043,7 @@
         <v/>
       </c>
       <c r="G925" s="16">
-        <f>IF(A925="","",E925*Calculator!$B$6+Calculator!$B$37+F925+Calculator!$B$30)</f>
+        <f>IF(A925="","",E925*Calculator!$B$6+Calculator!$C$37+F925+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H925" s="16">
@@ -40069,7 +40085,7 @@
         <v/>
       </c>
       <c r="G926" s="16">
-        <f>IF(A926="","",E926*Calculator!$B$6+Calculator!$B$37+F926+Calculator!$B$30)</f>
+        <f>IF(A926="","",E926*Calculator!$B$6+Calculator!$C$37+F926+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H926" s="16">
@@ -40111,7 +40127,7 @@
         <v/>
       </c>
       <c r="G927" s="16">
-        <f>IF(A927="","",E927*Calculator!$B$6+Calculator!$B$37+F927+Calculator!$B$30)</f>
+        <f>IF(A927="","",E927*Calculator!$B$6+Calculator!$C$37+F927+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H927" s="16">
@@ -40153,7 +40169,7 @@
         <v/>
       </c>
       <c r="G928" s="16">
-        <f>IF(A928="","",E928*Calculator!$B$6+Calculator!$B$37+F928+Calculator!$B$30)</f>
+        <f>IF(A928="","",E928*Calculator!$B$6+Calculator!$C$37+F928+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H928" s="16">
@@ -40195,7 +40211,7 @@
         <v/>
       </c>
       <c r="G929" s="16">
-        <f>IF(A929="","",E929*Calculator!$B$6+Calculator!$B$37+F929+Calculator!$B$30)</f>
+        <f>IF(A929="","",E929*Calculator!$B$6+Calculator!$C$37+F929+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H929" s="16">
@@ -40237,7 +40253,7 @@
         <v/>
       </c>
       <c r="G930" s="16">
-        <f>IF(A930="","",E930*Calculator!$B$6+Calculator!$B$37+F930+Calculator!$B$30)</f>
+        <f>IF(A930="","",E930*Calculator!$B$6+Calculator!$C$37+F930+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H930" s="16">
@@ -40279,7 +40295,7 @@
         <v/>
       </c>
       <c r="G931" s="16">
-        <f>IF(A931="","",E931*Calculator!$B$6+Calculator!$B$37+F931+Calculator!$B$30)</f>
+        <f>IF(A931="","",E931*Calculator!$B$6+Calculator!$C$37+F931+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H931" s="16">
@@ -40321,7 +40337,7 @@
         <v/>
       </c>
       <c r="G932" s="16">
-        <f>IF(A932="","",E932*Calculator!$B$6+Calculator!$B$37+F932+Calculator!$B$30)</f>
+        <f>IF(A932="","",E932*Calculator!$B$6+Calculator!$C$37+F932+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H932" s="16">
@@ -40363,7 +40379,7 @@
         <v/>
       </c>
       <c r="G933" s="16">
-        <f>IF(A933="","",E933*Calculator!$B$6+Calculator!$B$37+F933+Calculator!$B$30)</f>
+        <f>IF(A933="","",E933*Calculator!$B$6+Calculator!$C$37+F933+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H933" s="16">
@@ -40405,7 +40421,7 @@
         <v/>
       </c>
       <c r="G934" s="16">
-        <f>IF(A934="","",E934*Calculator!$B$6+Calculator!$B$37+F934+Calculator!$B$30)</f>
+        <f>IF(A934="","",E934*Calculator!$B$6+Calculator!$C$37+F934+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H934" s="16">
@@ -40447,7 +40463,7 @@
         <v/>
       </c>
       <c r="G935" s="16">
-        <f>IF(A935="","",E935*Calculator!$B$6+Calculator!$B$37+F935+Calculator!$B$30)</f>
+        <f>IF(A935="","",E935*Calculator!$B$6+Calculator!$C$37+F935+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H935" s="16">
@@ -40489,7 +40505,7 @@
         <v/>
       </c>
       <c r="G936" s="16">
-        <f>IF(A936="","",E936*Calculator!$B$6+Calculator!$B$37+F936+Calculator!$B$30)</f>
+        <f>IF(A936="","",E936*Calculator!$B$6+Calculator!$C$37+F936+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H936" s="16">
@@ -40531,7 +40547,7 @@
         <v/>
       </c>
       <c r="G937" s="16">
-        <f>IF(A937="","",E937*Calculator!$B$6+Calculator!$B$37+F937+Calculator!$B$30)</f>
+        <f>IF(A937="","",E937*Calculator!$B$6+Calculator!$C$37+F937+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H937" s="16">
@@ -40573,7 +40589,7 @@
         <v/>
       </c>
       <c r="G938" s="16">
-        <f>IF(A938="","",E938*Calculator!$B$6+Calculator!$B$37+F938+Calculator!$B$30)</f>
+        <f>IF(A938="","",E938*Calculator!$B$6+Calculator!$C$37+F938+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H938" s="16">
@@ -40615,7 +40631,7 @@
         <v/>
       </c>
       <c r="G939" s="16">
-        <f>IF(A939="","",E939*Calculator!$B$6+Calculator!$B$37+F939+Calculator!$B$30)</f>
+        <f>IF(A939="","",E939*Calculator!$B$6+Calculator!$C$37+F939+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H939" s="16">
@@ -40657,7 +40673,7 @@
         <v/>
       </c>
       <c r="G940" s="16">
-        <f>IF(A940="","",E940*Calculator!$B$6+Calculator!$B$37+F940+Calculator!$B$30)</f>
+        <f>IF(A940="","",E940*Calculator!$B$6+Calculator!$C$37+F940+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H940" s="16">
@@ -40699,7 +40715,7 @@
         <v/>
       </c>
       <c r="G941" s="16">
-        <f>IF(A941="","",E941*Calculator!$B$6+Calculator!$B$37+F941+Calculator!$B$30)</f>
+        <f>IF(A941="","",E941*Calculator!$B$6+Calculator!$C$37+F941+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H941" s="16">
@@ -40741,7 +40757,7 @@
         <v/>
       </c>
       <c r="G942" s="16">
-        <f>IF(A942="","",E942*Calculator!$B$6+Calculator!$B$37+F942+Calculator!$B$30)</f>
+        <f>IF(A942="","",E942*Calculator!$B$6+Calculator!$C$37+F942+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H942" s="16">
@@ -40783,7 +40799,7 @@
         <v/>
       </c>
       <c r="G943" s="16">
-        <f>IF(A943="","",E943*Calculator!$B$6+Calculator!$B$37+F943+Calculator!$B$30)</f>
+        <f>IF(A943="","",E943*Calculator!$B$6+Calculator!$C$37+F943+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H943" s="16">
@@ -40825,7 +40841,7 @@
         <v/>
       </c>
       <c r="G944" s="16">
-        <f>IF(A944="","",E944*Calculator!$B$6+Calculator!$B$37+F944+Calculator!$B$30)</f>
+        <f>IF(A944="","",E944*Calculator!$B$6+Calculator!$C$37+F944+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H944" s="16">
@@ -40867,7 +40883,7 @@
         <v/>
       </c>
       <c r="G945" s="16">
-        <f>IF(A945="","",E945*Calculator!$B$6+Calculator!$B$37+F945+Calculator!$B$30)</f>
+        <f>IF(A945="","",E945*Calculator!$B$6+Calculator!$C$37+F945+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H945" s="16">
@@ -40909,7 +40925,7 @@
         <v/>
       </c>
       <c r="G946" s="16">
-        <f>IF(A946="","",E946*Calculator!$B$6+Calculator!$B$37+F946+Calculator!$B$30)</f>
+        <f>IF(A946="","",E946*Calculator!$B$6+Calculator!$C$37+F946+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H946" s="16">
@@ -40951,7 +40967,7 @@
         <v/>
       </c>
       <c r="G947" s="16">
-        <f>IF(A947="","",E947*Calculator!$B$6+Calculator!$B$37+F947+Calculator!$B$30)</f>
+        <f>IF(A947="","",E947*Calculator!$B$6+Calculator!$C$37+F947+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H947" s="16">
@@ -40993,7 +41009,7 @@
         <v/>
       </c>
       <c r="G948" s="16">
-        <f>IF(A948="","",E948*Calculator!$B$6+Calculator!$B$37+F948+Calculator!$B$30)</f>
+        <f>IF(A948="","",E948*Calculator!$B$6+Calculator!$C$37+F948+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H948" s="16">
@@ -41035,7 +41051,7 @@
         <v/>
       </c>
       <c r="G949" s="16">
-        <f>IF(A949="","",E949*Calculator!$B$6+Calculator!$B$37+F949+Calculator!$B$30)</f>
+        <f>IF(A949="","",E949*Calculator!$B$6+Calculator!$C$37+F949+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H949" s="16">
@@ -41077,7 +41093,7 @@
         <v/>
       </c>
       <c r="G950" s="16">
-        <f>IF(A950="","",E950*Calculator!$B$6+Calculator!$B$37+F950+Calculator!$B$30)</f>
+        <f>IF(A950="","",E950*Calculator!$B$6+Calculator!$C$37+F950+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H950" s="16">
@@ -41119,7 +41135,7 @@
         <v/>
       </c>
       <c r="G951" s="16">
-        <f>IF(A951="","",E951*Calculator!$B$6+Calculator!$B$37+F951+Calculator!$B$30)</f>
+        <f>IF(A951="","",E951*Calculator!$B$6+Calculator!$C$37+F951+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H951" s="16">
@@ -41161,7 +41177,7 @@
         <v/>
       </c>
       <c r="G952" s="16">
-        <f>IF(A952="","",E952*Calculator!$B$6+Calculator!$B$37+F952+Calculator!$B$30)</f>
+        <f>IF(A952="","",E952*Calculator!$B$6+Calculator!$C$37+F952+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H952" s="16">
@@ -41203,7 +41219,7 @@
         <v/>
       </c>
       <c r="G953" s="16">
-        <f>IF(A953="","",E953*Calculator!$B$6+Calculator!$B$37+F953+Calculator!$B$30)</f>
+        <f>IF(A953="","",E953*Calculator!$B$6+Calculator!$C$37+F953+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H953" s="16">
@@ -41245,7 +41261,7 @@
         <v/>
       </c>
       <c r="G954" s="16">
-        <f>IF(A954="","",E954*Calculator!$B$6+Calculator!$B$37+F954+Calculator!$B$30)</f>
+        <f>IF(A954="","",E954*Calculator!$B$6+Calculator!$C$37+F954+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H954" s="16">
@@ -41287,7 +41303,7 @@
         <v/>
       </c>
       <c r="G955" s="16">
-        <f>IF(A955="","",E955*Calculator!$B$6+Calculator!$B$37+F955+Calculator!$B$30)</f>
+        <f>IF(A955="","",E955*Calculator!$B$6+Calculator!$C$37+F955+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H955" s="16">
@@ -41329,7 +41345,7 @@
         <v/>
       </c>
       <c r="G956" s="16">
-        <f>IF(A956="","",E956*Calculator!$B$6+Calculator!$B$37+F956+Calculator!$B$30)</f>
+        <f>IF(A956="","",E956*Calculator!$B$6+Calculator!$C$37+F956+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H956" s="16">
@@ -41371,7 +41387,7 @@
         <v/>
       </c>
       <c r="G957" s="16">
-        <f>IF(A957="","",E957*Calculator!$B$6+Calculator!$B$37+F957+Calculator!$B$30)</f>
+        <f>IF(A957="","",E957*Calculator!$B$6+Calculator!$C$37+F957+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H957" s="16">
@@ -41413,7 +41429,7 @@
         <v/>
       </c>
       <c r="G958" s="16">
-        <f>IF(A958="","",E958*Calculator!$B$6+Calculator!$B$37+F958+Calculator!$B$30)</f>
+        <f>IF(A958="","",E958*Calculator!$B$6+Calculator!$C$37+F958+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H958" s="16">
@@ -41455,7 +41471,7 @@
         <v/>
       </c>
       <c r="G959" s="16">
-        <f>IF(A959="","",E959*Calculator!$B$6+Calculator!$B$37+F959+Calculator!$B$30)</f>
+        <f>IF(A959="","",E959*Calculator!$B$6+Calculator!$C$37+F959+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H959" s="16">
@@ -41497,7 +41513,7 @@
         <v/>
       </c>
       <c r="G960" s="16">
-        <f>IF(A960="","",E960*Calculator!$B$6+Calculator!$B$37+F960+Calculator!$B$30)</f>
+        <f>IF(A960="","",E960*Calculator!$B$6+Calculator!$C$37+F960+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H960" s="16">
@@ -41539,7 +41555,7 @@
         <v/>
       </c>
       <c r="G961" s="16">
-        <f>IF(A961="","",E961*Calculator!$B$6+Calculator!$B$37+F961+Calculator!$B$30)</f>
+        <f>IF(A961="","",E961*Calculator!$B$6+Calculator!$C$37+F961+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H961" s="16">
@@ -41581,7 +41597,7 @@
         <v/>
       </c>
       <c r="G962" s="16">
-        <f>IF(A962="","",E962*Calculator!$B$6+Calculator!$B$37+F962+Calculator!$B$30)</f>
+        <f>IF(A962="","",E962*Calculator!$B$6+Calculator!$C$37+F962+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H962" s="16">
@@ -41623,7 +41639,7 @@
         <v/>
       </c>
       <c r="G963" s="16">
-        <f>IF(A963="","",E963*Calculator!$B$6+Calculator!$B$37+F963+Calculator!$B$30)</f>
+        <f>IF(A963="","",E963*Calculator!$B$6+Calculator!$C$37+F963+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H963" s="16">
@@ -41665,7 +41681,7 @@
         <v/>
       </c>
       <c r="G964" s="16">
-        <f>IF(A964="","",E964*Calculator!$B$6+Calculator!$B$37+F964+Calculator!$B$30)</f>
+        <f>IF(A964="","",E964*Calculator!$B$6+Calculator!$C$37+F964+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H964" s="16">
@@ -41707,7 +41723,7 @@
         <v/>
       </c>
       <c r="G965" s="16">
-        <f>IF(A965="","",E965*Calculator!$B$6+Calculator!$B$37+F965+Calculator!$B$30)</f>
+        <f>IF(A965="","",E965*Calculator!$B$6+Calculator!$C$37+F965+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H965" s="16">
@@ -41749,7 +41765,7 @@
         <v/>
       </c>
       <c r="G966" s="16">
-        <f>IF(A966="","",E966*Calculator!$B$6+Calculator!$B$37+F966+Calculator!$B$30)</f>
+        <f>IF(A966="","",E966*Calculator!$B$6+Calculator!$C$37+F966+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H966" s="16">
@@ -41791,7 +41807,7 @@
         <v/>
       </c>
       <c r="G967" s="16">
-        <f>IF(A967="","",E967*Calculator!$B$6+Calculator!$B$37+F967+Calculator!$B$30)</f>
+        <f>IF(A967="","",E967*Calculator!$B$6+Calculator!$C$37+F967+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H967" s="16">
@@ -41833,7 +41849,7 @@
         <v/>
       </c>
       <c r="G968" s="16">
-        <f>IF(A968="","",E968*Calculator!$B$6+Calculator!$B$37+F968+Calculator!$B$30)</f>
+        <f>IF(A968="","",E968*Calculator!$B$6+Calculator!$C$37+F968+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H968" s="16">
@@ -41875,7 +41891,7 @@
         <v/>
       </c>
       <c r="G969" s="16">
-        <f>IF(A969="","",E969*Calculator!$B$6+Calculator!$B$37+F969+Calculator!$B$30)</f>
+        <f>IF(A969="","",E969*Calculator!$B$6+Calculator!$C$37+F969+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H969" s="16">
@@ -41917,7 +41933,7 @@
         <v/>
       </c>
       <c r="G970" s="16">
-        <f>IF(A970="","",E970*Calculator!$B$6+Calculator!$B$37+F970+Calculator!$B$30)</f>
+        <f>IF(A970="","",E970*Calculator!$B$6+Calculator!$C$37+F970+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H970" s="16">
@@ -41959,7 +41975,7 @@
         <v/>
       </c>
       <c r="G971" s="16">
-        <f>IF(A971="","",E971*Calculator!$B$6+Calculator!$B$37+F971+Calculator!$B$30)</f>
+        <f>IF(A971="","",E971*Calculator!$B$6+Calculator!$C$37+F971+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H971" s="16">
@@ -42001,7 +42017,7 @@
         <v/>
       </c>
       <c r="G972" s="16">
-        <f>IF(A972="","",E972*Calculator!$B$6+Calculator!$B$37+F972+Calculator!$B$30)</f>
+        <f>IF(A972="","",E972*Calculator!$B$6+Calculator!$C$37+F972+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H972" s="16">
@@ -42043,7 +42059,7 @@
         <v/>
       </c>
       <c r="G973" s="16">
-        <f>IF(A973="","",E973*Calculator!$B$6+Calculator!$B$37+F973+Calculator!$B$30)</f>
+        <f>IF(A973="","",E973*Calculator!$B$6+Calculator!$C$37+F973+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H973" s="16">
@@ -42085,7 +42101,7 @@
         <v/>
       </c>
       <c r="G974" s="16">
-        <f>IF(A974="","",E974*Calculator!$B$6+Calculator!$B$37+F974+Calculator!$B$30)</f>
+        <f>IF(A974="","",E974*Calculator!$B$6+Calculator!$C$37+F974+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H974" s="16">
@@ -42127,7 +42143,7 @@
         <v/>
       </c>
       <c r="G975" s="16">
-        <f>IF(A975="","",E975*Calculator!$B$6+Calculator!$B$37+F975+Calculator!$B$30)</f>
+        <f>IF(A975="","",E975*Calculator!$B$6+Calculator!$C$37+F975+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H975" s="16">
@@ -42169,7 +42185,7 @@
         <v/>
       </c>
       <c r="G976" s="16">
-        <f>IF(A976="","",E976*Calculator!$B$6+Calculator!$B$37+F976+Calculator!$B$30)</f>
+        <f>IF(A976="","",E976*Calculator!$B$6+Calculator!$C$37+F976+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H976" s="16">
@@ -42211,7 +42227,7 @@
         <v/>
       </c>
       <c r="G977" s="16">
-        <f>IF(A977="","",E977*Calculator!$B$6+Calculator!$B$37+F977+Calculator!$B$30)</f>
+        <f>IF(A977="","",E977*Calculator!$B$6+Calculator!$C$37+F977+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H977" s="16">
@@ -42253,7 +42269,7 @@
         <v/>
       </c>
       <c r="G978" s="16">
-        <f>IF(A978="","",E978*Calculator!$B$6+Calculator!$B$37+F978+Calculator!$B$30)</f>
+        <f>IF(A978="","",E978*Calculator!$B$6+Calculator!$C$37+F978+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H978" s="16">
@@ -42295,7 +42311,7 @@
         <v/>
       </c>
       <c r="G979" s="16">
-        <f>IF(A979="","",E979*Calculator!$B$6+Calculator!$B$37+F979+Calculator!$B$30)</f>
+        <f>IF(A979="","",E979*Calculator!$B$6+Calculator!$C$37+F979+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H979" s="16">
@@ -42337,7 +42353,7 @@
         <v/>
       </c>
       <c r="G980" s="16">
-        <f>IF(A980="","",E980*Calculator!$B$6+Calculator!$B$37+F980+Calculator!$B$30)</f>
+        <f>IF(A980="","",E980*Calculator!$B$6+Calculator!$C$37+F980+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H980" s="16">
@@ -42379,7 +42395,7 @@
         <v/>
       </c>
       <c r="G981" s="16">
-        <f>IF(A981="","",E981*Calculator!$B$6+Calculator!$B$37+F981+Calculator!$B$30)</f>
+        <f>IF(A981="","",E981*Calculator!$B$6+Calculator!$C$37+F981+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H981" s="16">
@@ -42421,7 +42437,7 @@
         <v/>
       </c>
       <c r="G982" s="16">
-        <f>IF(A982="","",E982*Calculator!$B$6+Calculator!$B$37+F982+Calculator!$B$30)</f>
+        <f>IF(A982="","",E982*Calculator!$B$6+Calculator!$C$37+F982+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H982" s="16">
@@ -42463,7 +42479,7 @@
         <v/>
       </c>
       <c r="G983" s="16">
-        <f>IF(A983="","",E983*Calculator!$B$6+Calculator!$B$37+F983+Calculator!$B$30)</f>
+        <f>IF(A983="","",E983*Calculator!$B$6+Calculator!$C$37+F983+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H983" s="16">
@@ -42505,7 +42521,7 @@
         <v/>
       </c>
       <c r="G984" s="16">
-        <f>IF(A984="","",E984*Calculator!$B$6+Calculator!$B$37+F984+Calculator!$B$30)</f>
+        <f>IF(A984="","",E984*Calculator!$B$6+Calculator!$C$37+F984+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H984" s="16">
@@ -42547,7 +42563,7 @@
         <v/>
       </c>
       <c r="G985" s="16">
-        <f>IF(A985="","",E985*Calculator!$B$6+Calculator!$B$37+F985+Calculator!$B$30)</f>
+        <f>IF(A985="","",E985*Calculator!$B$6+Calculator!$C$37+F985+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H985" s="16">
@@ -42589,7 +42605,7 @@
         <v/>
       </c>
       <c r="G986" s="16">
-        <f>IF(A986="","",E986*Calculator!$B$6+Calculator!$B$37+F986+Calculator!$B$30)</f>
+        <f>IF(A986="","",E986*Calculator!$B$6+Calculator!$C$37+F986+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H986" s="16">
@@ -42631,7 +42647,7 @@
         <v/>
       </c>
       <c r="G987" s="16">
-        <f>IF(A987="","",E987*Calculator!$B$6+Calculator!$B$37+F987+Calculator!$B$30)</f>
+        <f>IF(A987="","",E987*Calculator!$B$6+Calculator!$C$37+F987+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H987" s="16">
@@ -42673,7 +42689,7 @@
         <v/>
       </c>
       <c r="G988" s="16">
-        <f>IF(A988="","",E988*Calculator!$B$6+Calculator!$B$37+F988+Calculator!$B$30)</f>
+        <f>IF(A988="","",E988*Calculator!$B$6+Calculator!$C$37+F988+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H988" s="16">
@@ -42715,7 +42731,7 @@
         <v/>
       </c>
       <c r="G989" s="16">
-        <f>IF(A989="","",E989*Calculator!$B$6+Calculator!$B$37+F989+Calculator!$B$30)</f>
+        <f>IF(A989="","",E989*Calculator!$B$6+Calculator!$C$37+F989+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H989" s="16">
@@ -42757,7 +42773,7 @@
         <v/>
       </c>
       <c r="G990" s="16">
-        <f>IF(A990="","",E990*Calculator!$B$6+Calculator!$B$37+F990+Calculator!$B$30)</f>
+        <f>IF(A990="","",E990*Calculator!$B$6+Calculator!$C$37+F990+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H990" s="16">
@@ -42799,7 +42815,7 @@
         <v/>
       </c>
       <c r="G991" s="16">
-        <f>IF(A991="","",E991*Calculator!$B$6+Calculator!$B$37+F991+Calculator!$B$30)</f>
+        <f>IF(A991="","",E991*Calculator!$B$6+Calculator!$C$37+F991+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H991" s="16">
@@ -42841,7 +42857,7 @@
         <v/>
       </c>
       <c r="G992" s="16">
-        <f>IF(A992="","",E992*Calculator!$B$6+Calculator!$B$37+F992+Calculator!$B$30)</f>
+        <f>IF(A992="","",E992*Calculator!$B$6+Calculator!$C$37+F992+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H992" s="16">
@@ -42883,7 +42899,7 @@
         <v/>
       </c>
       <c r="G993" s="16">
-        <f>IF(A993="","",E993*Calculator!$B$6+Calculator!$B$37+F993+Calculator!$B$30)</f>
+        <f>IF(A993="","",E993*Calculator!$B$6+Calculator!$C$37+F993+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H993" s="16">
@@ -42925,7 +42941,7 @@
         <v/>
       </c>
       <c r="G994" s="16">
-        <f>IF(A994="","",E994*Calculator!$B$6+Calculator!$B$37+F994+Calculator!$B$30)</f>
+        <f>IF(A994="","",E994*Calculator!$B$6+Calculator!$C$37+F994+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H994" s="16">
@@ -42967,7 +42983,7 @@
         <v/>
       </c>
       <c r="G995" s="16">
-        <f>IF(A995="","",E995*Calculator!$B$6+Calculator!$B$37+F995+Calculator!$B$30)</f>
+        <f>IF(A995="","",E995*Calculator!$B$6+Calculator!$C$37+F995+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H995" s="16">
@@ -43009,7 +43025,7 @@
         <v/>
       </c>
       <c r="G996" s="16">
-        <f>IF(A996="","",E996*Calculator!$B$6+Calculator!$B$37+F996+Calculator!$B$30)</f>
+        <f>IF(A996="","",E996*Calculator!$B$6+Calculator!$C$37+F996+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H996" s="16">
@@ -43051,7 +43067,7 @@
         <v/>
       </c>
       <c r="G997" s="16">
-        <f>IF(A997="","",E997*Calculator!$B$6+Calculator!$B$37+F997+Calculator!$B$30)</f>
+        <f>IF(A997="","",E997*Calculator!$B$6+Calculator!$C$37+F997+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H997" s="16">
@@ -43093,7 +43109,7 @@
         <v/>
       </c>
       <c r="G998" s="16">
-        <f>IF(A998="","",E998*Calculator!$B$6+Calculator!$B$37+F998+Calculator!$B$30)</f>
+        <f>IF(A998="","",E998*Calculator!$B$6+Calculator!$C$37+F998+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H998" s="16">
@@ -43135,7 +43151,7 @@
         <v/>
       </c>
       <c r="G999" s="16">
-        <f>IF(A999="","",E999*Calculator!$B$6+Calculator!$B$37+F999+Calculator!$B$30)</f>
+        <f>IF(A999="","",E999*Calculator!$B$6+Calculator!$C$37+F999+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H999" s="16">
@@ -43177,7 +43193,7 @@
         <v/>
       </c>
       <c r="G1000" s="16">
-        <f>IF(A1000="","",E1000*Calculator!$B$6+Calculator!$B$37+F1000+Calculator!$B$30)</f>
+        <f>IF(A1000="","",E1000*Calculator!$B$6+Calculator!$C$37+F1000+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H1000" s="16">
@@ -43219,7 +43235,7 @@
         <v/>
       </c>
       <c r="G1001" s="16">
-        <f>IF(A1001="","",E1001*Calculator!$B$6+Calculator!$B$37+F1001+Calculator!$B$30)</f>
+        <f>IF(A1001="","",E1001*Calculator!$B$6+Calculator!$C$37+F1001+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H1001" s="16">
@@ -43261,7 +43277,7 @@
         <v/>
       </c>
       <c r="G1002" s="16">
-        <f>IF(A1002="","",E1002*Calculator!$B$6+Calculator!$B$37+F1002+Calculator!$B$30)</f>
+        <f>IF(A1002="","",E1002*Calculator!$B$6+Calculator!$C$37+F1002+Calculator!$B$30)</f>
         <v/>
       </c>
       <c r="H1002" s="16">
@@ -43360,11 +43376,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>At 0% AVA: savings = −(AVA per-call cost + fixed) when AVA is charged on escalations</t>
+          <t>At 0% AVA: savings = IVR fees avoided − (AVA per-call cost + fixed) when AVA is charged on escalations</t>
         </is>
       </c>
       <c r="B4" s="16">
-        <f>-(IF(Calculator!$B$16=1,Calculator!$B$27*Calculator!$B$5*Calculator!$B$15,0)+Calculator!B30)</f>
+        <f>Calculator!$B$27*Calculator!$B$5*Calculator!$B$14-(IF(Calculator!$B$16=1,Calculator!$B$27*Calculator!$B$5*Calculator!$B$15,0)+Calculator!B30)</f>
         <v/>
       </c>
       <c r="C4" s="16">
@@ -43388,7 +43404,7 @@
         </is>
       </c>
       <c r="C5" s="16">
-        <f>INDEX(Ladder!H:H,MATCH(ROUND(Calculator!B54,3),Ladder!A:A,0))</f>
+        <f>INDEX(Ladder!H:H,MATCH(ROUND(Calculator!B55,3),Ladder!A:A,0))</f>
         <v/>
       </c>
       <c r="D5">
@@ -43408,7 +43424,7 @@
         </is>
       </c>
       <c r="C6" s="16">
-        <f>IF(Calculator!B54=0,"n/a",INDEX(Ladder!H:H,MATCH(ROUND(Calculator!B54-0.001,3),Ladder!A:A,0)))</f>
+        <f>IF(Calculator!B55=0,"n/a",INDEX(Ladder!H:H,MATCH(ROUND(Calculator!B55-0.001,3),Ladder!A:A,0)))</f>
         <v/>
       </c>
       <c r="D6">
@@ -43438,7 +43454,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hours chain: labor saved − AVA cost = total cost difference</t>
+          <t>Hours chain: labor saved + IVR avoided − AVA cost = total cost difference</t>
         </is>
       </c>
       <c r="B8" s="16">
@@ -43446,7 +43462,7 @@
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>Calculator!B51</f>
+        <f>Calculator!B52</f>
         <v/>
       </c>
       <c r="D8">

--- a/ava-break-even-check.xlsx
+++ b/ava-break-even-check.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculator" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ladder" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Calculator" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ladder" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Checks" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
